--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128342525</v>
+        <v>128341860</v>
       </c>
       <c r="B8" t="n">
-        <v>79649</v>
+        <v>78789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574323</v>
+        <v>574328</v>
       </c>
       <c r="R8" t="n">
-        <v>7088778</v>
+        <v>7088763</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,9 +1350,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341860</v>
+        <v>128341697</v>
       </c>
       <c r="B9" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,34 +1400,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574328</v>
+        <v>574383</v>
       </c>
       <c r="R9" t="n">
-        <v>7088763</v>
+        <v>7088749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1459,7 +1474,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,44 +1494,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341140</v>
+        <v>128342525</v>
       </c>
       <c r="B10" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,13 +1541,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574438</v>
+        <v>574323</v>
       </c>
       <c r="R10" t="n">
-        <v>7088595</v>
+        <v>7088778</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1554,19 +1574,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,62 +1591,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341697</v>
+        <v>128341140</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574383</v>
+        <v>574438</v>
       </c>
       <c r="R11" t="n">
-        <v>7088749</v>
+        <v>7088595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342847</v>
+        <v>128342434</v>
       </c>
       <c r="B26" t="n">
         <v>92645</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574354</v>
+        <v>574373</v>
       </c>
       <c r="R26" t="n">
-        <v>7088881</v>
+        <v>7088729</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128341564</v>
+        <v>128342391</v>
       </c>
       <c r="B27" t="n">
-        <v>92645</v>
+        <v>91516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574445</v>
+        <v>574371</v>
       </c>
       <c r="R27" t="n">
-        <v>7088593</v>
+        <v>7088729</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342434</v>
+        <v>128342274</v>
       </c>
       <c r="B28" t="n">
         <v>92645</v>
@@ -3347,13 +3347,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574373</v>
+        <v>574276</v>
       </c>
       <c r="R28" t="n">
-        <v>7088729</v>
+        <v>7088904</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3380,9 +3380,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3397,44 +3407,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342391</v>
+        <v>128341678</v>
       </c>
       <c r="B29" t="n">
-        <v>91516</v>
+        <v>78698</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3444,10 +3454,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574371</v>
+        <v>574449</v>
       </c>
       <c r="R29" t="n">
-        <v>7088729</v>
+        <v>7088616</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3506,7 +3516,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128342274</v>
+        <v>128341564</v>
       </c>
       <c r="B30" t="n">
         <v>92645</v>
@@ -3541,13 +3551,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574276</v>
+        <v>574445</v>
       </c>
       <c r="R30" t="n">
-        <v>7088904</v>
+        <v>7088593</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3574,19 +3584,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3601,44 +3601,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128341678</v>
+        <v>128342847</v>
       </c>
       <c r="B31" t="n">
-        <v>78698</v>
+        <v>92645</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574449</v>
+        <v>574354</v>
       </c>
       <c r="R31" t="n">
-        <v>7088616</v>
+        <v>7088881</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3710,32 +3710,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128341686</v>
+        <v>128342815</v>
       </c>
       <c r="B32" t="n">
-        <v>90390</v>
+        <v>92645</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R32" t="n">
-        <v>7088630</v>
+        <v>7088883</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128342815</v>
+        <v>128342782</v>
       </c>
       <c r="B33" t="n">
-        <v>92645</v>
+        <v>92661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574292</v>
+        <v>574280</v>
       </c>
       <c r="R33" t="n">
-        <v>7088883</v>
+        <v>7088852</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3904,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128342782</v>
+        <v>128341686</v>
       </c>
       <c r="B34" t="n">
-        <v>92661</v>
+        <v>90390</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574280</v>
+        <v>574445</v>
       </c>
       <c r="R34" t="n">
-        <v>7088852</v>
+        <v>7088630</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128341663</v>
+        <v>128342012</v>
       </c>
       <c r="B35" t="n">
         <v>92645</v>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574444</v>
+        <v>574415</v>
       </c>
       <c r="R35" t="n">
-        <v>7088610</v>
+        <v>7088716</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128342012</v>
+        <v>128341929</v>
       </c>
       <c r="B36" t="n">
         <v>92645</v>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574415</v>
+        <v>574406</v>
       </c>
       <c r="R36" t="n">
-        <v>7088716</v>
+        <v>7088725</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128341929</v>
+        <v>128341248</v>
       </c>
       <c r="B37" t="n">
         <v>92645</v>
@@ -4230,13 +4230,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574406</v>
+        <v>574418</v>
       </c>
       <c r="R37" t="n">
-        <v>7088725</v>
+        <v>7088658</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4263,9 +4263,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4280,19 +4290,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128341248</v>
+        <v>128342804</v>
       </c>
       <c r="B38" t="n">
         <v>92645</v>
@@ -4327,13 +4337,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574418</v>
+        <v>574290</v>
       </c>
       <c r="R38" t="n">
-        <v>7088658</v>
+        <v>7088881</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4360,19 +4370,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4387,12 +4387,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4593,7 +4593,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128342804</v>
+        <v>128341663</v>
       </c>
       <c r="B41" t="n">
         <v>92645</v>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574290</v>
+        <v>574444</v>
       </c>
       <c r="R41" t="n">
-        <v>7088881</v>
+        <v>7088610</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341658</v>
+        <v>128341543</v>
       </c>
       <c r="B53" t="n">
-        <v>78698</v>
+        <v>80170</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
         <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088595</v>
+        <v>7088593</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341543</v>
+        <v>128342561</v>
       </c>
       <c r="B54" t="n">
-        <v>80170</v>
+        <v>79649</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R54" t="n">
-        <v>7088593</v>
+        <v>7088790</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342561</v>
+        <v>128342438</v>
       </c>
       <c r="B55" t="n">
-        <v>79649</v>
+        <v>78789</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574312</v>
+        <v>574373</v>
       </c>
       <c r="R55" t="n">
-        <v>7088790</v>
+        <v>7088729</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342438</v>
+        <v>128342351</v>
       </c>
       <c r="B56" t="n">
-        <v>78789</v>
+        <v>92649</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574373</v>
+        <v>574372</v>
       </c>
       <c r="R56" t="n">
-        <v>7088729</v>
+        <v>7088765</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342351</v>
+        <v>128342751</v>
       </c>
       <c r="B57" t="n">
-        <v>92649</v>
+        <v>78698</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574372</v>
+        <v>574291</v>
       </c>
       <c r="R57" t="n">
-        <v>7088765</v>
+        <v>7088844</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128342751</v>
+        <v>128341658</v>
       </c>
       <c r="B58" t="n">
         <v>78698</v>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088844</v>
+        <v>7088595</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -8165,6 +8165,207 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128342186</v>
+      </c>
+      <c r="B76" t="n">
+        <v>92060</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>757</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hapalopilus aurantiacus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>574387</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7088758</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128355111</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Långvattentjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>574244</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7088922</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Fjällsjö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341860</v>
+        <v>128342525</v>
       </c>
       <c r="B8" t="n">
-        <v>78789</v>
+        <v>79649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574328</v>
+        <v>574323</v>
       </c>
       <c r="R8" t="n">
-        <v>7088763</v>
+        <v>7088778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,19 +1350,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,22 +1367,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341697</v>
+        <v>128341860</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1390,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574383</v>
+        <v>574328</v>
       </c>
       <c r="R9" t="n">
-        <v>7088749</v>
+        <v>7088763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1449,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,12 +1459,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,44 +1474,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128342525</v>
+        <v>128341140</v>
       </c>
       <c r="B10" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1521,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574323</v>
+        <v>574438</v>
       </c>
       <c r="R10" t="n">
-        <v>7088778</v>
+        <v>7088595</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,9 +1554,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,57 +1581,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341140</v>
+        <v>128341697</v>
       </c>
       <c r="B11" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574438</v>
+        <v>574383</v>
       </c>
       <c r="R11" t="n">
-        <v>7088595</v>
+        <v>7088749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128342806</v>
+        <v>128341749</v>
       </c>
       <c r="B13" t="n">
-        <v>80134</v>
+        <v>78789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574452</v>
+        <v>574358</v>
       </c>
       <c r="R13" t="n">
-        <v>7088593</v>
+        <v>7088744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128341749</v>
+        <v>128342806</v>
       </c>
       <c r="B15" t="n">
-        <v>78789</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574358</v>
+        <v>574452</v>
       </c>
       <c r="R15" t="n">
-        <v>7088744</v>
+        <v>7088593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,50 +2128,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341646</v>
+        <v>128342757</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R16" t="n">
-        <v>7088594</v>
+        <v>7088843</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2204,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,32 +2225,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341724</v>
+        <v>128341886</v>
       </c>
       <c r="B17" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574435</v>
+        <v>574321</v>
       </c>
       <c r="R17" t="n">
-        <v>7088666</v>
+        <v>7088769</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2303,9 +2293,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341740</v>
+        <v>128341807</v>
       </c>
       <c r="B18" t="n">
-        <v>79649</v>
+        <v>79031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574418</v>
+        <v>574435</v>
       </c>
       <c r="R18" t="n">
-        <v>7088654</v>
+        <v>7088661</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,48 +2429,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341886</v>
+        <v>128341646</v>
       </c>
       <c r="B19" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574321</v>
+        <v>574445</v>
       </c>
       <c r="R19" t="n">
-        <v>7088769</v>
+        <v>7088594</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2497,19 +2502,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:37</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341807</v>
+        <v>128341724</v>
       </c>
       <c r="B20" t="n">
-        <v>79031</v>
+        <v>79649</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
         <v>574435</v>
       </c>
       <c r="R20" t="n">
-        <v>7088661</v>
+        <v>7088666</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342757</v>
+        <v>128341740</v>
       </c>
       <c r="B21" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574291</v>
+        <v>574418</v>
       </c>
       <c r="R21" t="n">
-        <v>7088843</v>
+        <v>7088654</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3710,32 +3710,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128342815</v>
+        <v>128342782</v>
       </c>
       <c r="B32" t="n">
-        <v>92645</v>
+        <v>92661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574292</v>
+        <v>574280</v>
       </c>
       <c r="R32" t="n">
-        <v>7088883</v>
+        <v>7088852</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128342782</v>
+        <v>128341686</v>
       </c>
       <c r="B33" t="n">
-        <v>92661</v>
+        <v>90390</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,21 +3818,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574280</v>
+        <v>574445</v>
       </c>
       <c r="R33" t="n">
-        <v>7088852</v>
+        <v>7088630</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3904,32 +3904,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128341686</v>
+        <v>128342815</v>
       </c>
       <c r="B34" t="n">
-        <v>90390</v>
+        <v>92645</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R34" t="n">
-        <v>7088630</v>
+        <v>7088883</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128342904</v>
+        <v>128341959</v>
       </c>
       <c r="B42" t="n">
         <v>92645</v>
@@ -4725,13 +4725,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574370</v>
+        <v>574292</v>
       </c>
       <c r="R42" t="n">
-        <v>7088775</v>
+        <v>7088836</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4758,9 +4758,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4775,57 +4785,62 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341959</v>
+        <v>128341748</v>
       </c>
       <c r="B43" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574292</v>
+        <v>574361</v>
       </c>
       <c r="R43" t="n">
-        <v>7088836</v>
+        <v>7088768</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4857,7 +4872,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4867,7 +4882,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4882,65 +4902,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128341748</v>
+        <v>128342904</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574361</v>
+        <v>574370</v>
       </c>
       <c r="R44" t="n">
-        <v>7088768</v>
+        <v>7088775</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4967,24 +4982,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,12 +4999,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341543</v>
+        <v>128341658</v>
       </c>
       <c r="B53" t="n">
-        <v>80170</v>
+        <v>78698</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
         <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088593</v>
+        <v>7088595</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342561</v>
+        <v>128341543</v>
       </c>
       <c r="B54" t="n">
-        <v>79649</v>
+        <v>80170</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574312</v>
+        <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088790</v>
+        <v>7088593</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342438</v>
+        <v>128342561</v>
       </c>
       <c r="B55" t="n">
-        <v>78789</v>
+        <v>79649</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574373</v>
+        <v>574312</v>
       </c>
       <c r="R55" t="n">
-        <v>7088729</v>
+        <v>7088790</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342351</v>
+        <v>128342438</v>
       </c>
       <c r="B56" t="n">
-        <v>92649</v>
+        <v>78789</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574372</v>
+        <v>574373</v>
       </c>
       <c r="R56" t="n">
-        <v>7088765</v>
+        <v>7088729</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342751</v>
+        <v>128342351</v>
       </c>
       <c r="B57" t="n">
-        <v>78698</v>
+        <v>92649</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574291</v>
+        <v>574372</v>
       </c>
       <c r="R57" t="n">
-        <v>7088844</v>
+        <v>7088765</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341658</v>
+        <v>128342751</v>
       </c>
       <c r="B58" t="n">
         <v>78698</v>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R58" t="n">
-        <v>7088595</v>
+        <v>7088844</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7423,10 +7423,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341109</v>
+        <v>128341878</v>
       </c>
       <c r="B69" t="n">
-        <v>57672</v>
+        <v>79649</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7434,39 +7434,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574429</v>
+        <v>574329</v>
       </c>
       <c r="R69" t="n">
-        <v>7088591</v>
+        <v>7088770</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7498,7 +7493,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7508,12 +7503,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7528,44 +7518,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128341878</v>
+        <v>128342397</v>
       </c>
       <c r="B70" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7575,10 +7565,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574329</v>
+        <v>574294</v>
       </c>
       <c r="R70" t="n">
-        <v>7088770</v>
+        <v>7088921</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7610,7 +7600,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7620,7 +7610,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7635,57 +7625,62 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128342397</v>
+        <v>128341109</v>
       </c>
       <c r="B71" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574294</v>
+        <v>574429</v>
       </c>
       <c r="R71" t="n">
-        <v>7088921</v>
+        <v>7088591</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,7 +7712,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7727,7 +7722,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342191</v>
+        <v>128342785</v>
       </c>
       <c r="B2" t="n">
-        <v>92639</v>
+        <v>79649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574279</v>
+        <v>574275</v>
       </c>
       <c r="R2" t="n">
-        <v>7088861</v>
+        <v>7088862</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,60 +760,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128341917</v>
+        <v>128342842</v>
       </c>
       <c r="B3" t="n">
-        <v>78789</v>
+        <v>56864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574334</v>
+        <v>574354</v>
       </c>
       <c r="R3" t="n">
-        <v>7088809</v>
+        <v>7088880</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,19 +845,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +862,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342277</v>
+        <v>128342930</v>
       </c>
       <c r="B4" t="n">
-        <v>78698</v>
+        <v>92661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574382</v>
+        <v>574400</v>
       </c>
       <c r="R4" t="n">
-        <v>7088759</v>
+        <v>7088743</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342785</v>
+        <v>128342191</v>
       </c>
       <c r="B5" t="n">
-        <v>79649</v>
+        <v>92639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1006,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574275</v>
+        <v>574279</v>
       </c>
       <c r="R5" t="n">
-        <v>7088862</v>
+        <v>7088861</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,9 +1039,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1066,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128342842</v>
+        <v>128341917</v>
       </c>
       <c r="B6" t="n">
-        <v>56864</v>
+        <v>78789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574354</v>
+        <v>574334</v>
       </c>
       <c r="R6" t="n">
-        <v>7088880</v>
+        <v>7088809</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,9 +1146,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,22 +1173,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342930</v>
+        <v>128342277</v>
       </c>
       <c r="B7" t="n">
-        <v>92661</v>
+        <v>78698</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574400</v>
+        <v>574382</v>
       </c>
       <c r="R7" t="n">
-        <v>7088743</v>
+        <v>7088759</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342434</v>
+        <v>128341564</v>
       </c>
       <c r="B26" t="n">
         <v>92645</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574373</v>
+        <v>574445</v>
       </c>
       <c r="R26" t="n">
-        <v>7088729</v>
+        <v>7088593</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342391</v>
+        <v>128342434</v>
       </c>
       <c r="B27" t="n">
-        <v>91516</v>
+        <v>92645</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574371</v>
+        <v>574373</v>
       </c>
       <c r="R27" t="n">
         <v>7088729</v>
@@ -3312,32 +3312,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342274</v>
+        <v>128342391</v>
       </c>
       <c r="B28" t="n">
-        <v>92645</v>
+        <v>91516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3347,13 +3347,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574276</v>
+        <v>574371</v>
       </c>
       <c r="R28" t="n">
-        <v>7088904</v>
+        <v>7088729</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3380,19 +3380,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3407,44 +3397,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128341678</v>
+        <v>128342274</v>
       </c>
       <c r="B29" t="n">
-        <v>78698</v>
+        <v>92645</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3454,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574449</v>
+        <v>574276</v>
       </c>
       <c r="R29" t="n">
-        <v>7088616</v>
+        <v>7088904</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3487,9 +3477,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3504,44 +3504,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128341564</v>
+        <v>128341678</v>
       </c>
       <c r="B30" t="n">
-        <v>92645</v>
+        <v>78698</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574445</v>
+        <v>574449</v>
       </c>
       <c r="R30" t="n">
-        <v>7088593</v>
+        <v>7088616</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342400</v>
+        <v>128342176</v>
       </c>
       <c r="B65" t="n">
-        <v>92838</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,37 +7016,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574381</v>
+        <v>574286</v>
       </c>
       <c r="R65" t="n">
-        <v>7088725</v>
+        <v>7088863</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,9 +7078,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7090,22 +7110,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128342176</v>
+        <v>128341715</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>92838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7113,42 +7133,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574286</v>
+        <v>574446</v>
       </c>
       <c r="R66" t="n">
-        <v>7088863</v>
+        <v>7088674</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7175,24 +7190,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7207,19 +7207,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128341715</v>
+        <v>128342400</v>
       </c>
       <c r="B67" t="n">
         <v>92838</v>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574446</v>
+        <v>574381</v>
       </c>
       <c r="R67" t="n">
-        <v>7088674</v>
+        <v>7088725</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7423,10 +7423,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341878</v>
+        <v>128341109</v>
       </c>
       <c r="B69" t="n">
-        <v>79649</v>
+        <v>57672</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7434,34 +7434,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574329</v>
+        <v>574429</v>
       </c>
       <c r="R69" t="n">
-        <v>7088770</v>
+        <v>7088591</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,7 +7498,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7503,7 +7508,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7518,44 +7528,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128342397</v>
+        <v>128341878</v>
       </c>
       <c r="B70" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7565,10 +7575,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574294</v>
+        <v>574329</v>
       </c>
       <c r="R70" t="n">
-        <v>7088921</v>
+        <v>7088770</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7600,7 +7610,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7610,7 +7620,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7625,62 +7635,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128341109</v>
+        <v>128342397</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574429</v>
+        <v>574294</v>
       </c>
       <c r="R71" t="n">
-        <v>7088591</v>
+        <v>7088921</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7712,7 +7717,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7722,12 +7727,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7754,32 +7754,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128341813</v>
+        <v>128342408</v>
       </c>
       <c r="B72" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7789,10 +7789,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574445</v>
+        <v>574379</v>
       </c>
       <c r="R72" t="n">
-        <v>7088668</v>
+        <v>7088725</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128341787</v>
+        <v>128342337</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>92639</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7862,39 +7862,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574356</v>
+        <v>574241</v>
       </c>
       <c r="R73" t="n">
-        <v>7088756</v>
+        <v>7088939</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7926,7 +7921,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7936,7 +7931,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7963,32 +7958,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128342408</v>
+        <v>128341813</v>
       </c>
       <c r="B74" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7998,10 +7993,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574379</v>
+        <v>574445</v>
       </c>
       <c r="R74" t="n">
-        <v>7088725</v>
+        <v>7088668</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8060,10 +8055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128342337</v>
+        <v>128341787</v>
       </c>
       <c r="B75" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8071,34 +8066,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574241</v>
+        <v>574356</v>
       </c>
       <c r="R75" t="n">
-        <v>7088939</v>
+        <v>7088756</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128342525</v>
+        <v>128341860</v>
       </c>
       <c r="B8" t="n">
-        <v>79649</v>
+        <v>78789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574323</v>
+        <v>574328</v>
       </c>
       <c r="R8" t="n">
-        <v>7088778</v>
+        <v>7088763</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,9 +1350,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341860</v>
+        <v>128341697</v>
       </c>
       <c r="B9" t="n">
-        <v>78789</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,34 +1400,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574328</v>
+        <v>574383</v>
       </c>
       <c r="R9" t="n">
-        <v>7088763</v>
+        <v>7088749</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1464,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1459,7 +1474,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,12 +1494,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1593,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341697</v>
+        <v>128342525</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>79649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,42 +1624,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574383</v>
+        <v>574323</v>
       </c>
       <c r="R11" t="n">
-        <v>7088749</v>
+        <v>7088778</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,24 +1681,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128341749</v>
+        <v>128342806</v>
       </c>
       <c r="B13" t="n">
-        <v>78789</v>
+        <v>80134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574358</v>
+        <v>574452</v>
       </c>
       <c r="R13" t="n">
-        <v>7088744</v>
+        <v>7088593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342806</v>
+        <v>128341749</v>
       </c>
       <c r="B15" t="n">
-        <v>80134</v>
+        <v>78789</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574452</v>
+        <v>574358</v>
       </c>
       <c r="R15" t="n">
-        <v>7088593</v>
+        <v>7088744</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,45 +2128,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128342757</v>
+        <v>128341646</v>
       </c>
       <c r="B16" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R16" t="n">
-        <v>7088843</v>
+        <v>7088594</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2199,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,32 +2235,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341886</v>
+        <v>128341724</v>
       </c>
       <c r="B17" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2270,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574321</v>
+        <v>574435</v>
       </c>
       <c r="R17" t="n">
-        <v>7088769</v>
+        <v>7088666</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2293,19 +2303,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341807</v>
+        <v>128341740</v>
       </c>
       <c r="B18" t="n">
-        <v>79031</v>
+        <v>79649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574435</v>
+        <v>574418</v>
       </c>
       <c r="R18" t="n">
-        <v>7088661</v>
+        <v>7088654</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,53 +2429,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341646</v>
+        <v>128341886</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574445</v>
+        <v>574321</v>
       </c>
       <c r="R19" t="n">
-        <v>7088594</v>
+        <v>7088769</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2502,14 +2497,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341724</v>
+        <v>128341807</v>
       </c>
       <c r="B20" t="n">
-        <v>79649</v>
+        <v>79031</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
         <v>574435</v>
       </c>
       <c r="R20" t="n">
-        <v>7088666</v>
+        <v>7088661</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341740</v>
+        <v>128342757</v>
       </c>
       <c r="B21" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574418</v>
+        <v>574291</v>
       </c>
       <c r="R21" t="n">
-        <v>7088654</v>
+        <v>7088843</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341658</v>
+        <v>128341543</v>
       </c>
       <c r="B53" t="n">
-        <v>78698</v>
+        <v>80170</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
         <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088595</v>
+        <v>7088593</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341543</v>
+        <v>128342561</v>
       </c>
       <c r="B54" t="n">
-        <v>80170</v>
+        <v>79649</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R54" t="n">
-        <v>7088593</v>
+        <v>7088790</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342561</v>
+        <v>128342438</v>
       </c>
       <c r="B55" t="n">
-        <v>79649</v>
+        <v>78789</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574312</v>
+        <v>574373</v>
       </c>
       <c r="R55" t="n">
-        <v>7088790</v>
+        <v>7088729</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342438</v>
+        <v>128342351</v>
       </c>
       <c r="B56" t="n">
-        <v>78789</v>
+        <v>92649</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574373</v>
+        <v>574372</v>
       </c>
       <c r="R56" t="n">
-        <v>7088729</v>
+        <v>7088765</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342351</v>
+        <v>128342751</v>
       </c>
       <c r="B57" t="n">
-        <v>92649</v>
+        <v>78698</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574372</v>
+        <v>574291</v>
       </c>
       <c r="R57" t="n">
-        <v>7088765</v>
+        <v>7088844</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128342751</v>
+        <v>128341658</v>
       </c>
       <c r="B58" t="n">
         <v>78698</v>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088844</v>
+        <v>7088595</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6389,10 +6389,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128342812</v>
+        <v>128341588</v>
       </c>
       <c r="B59" t="n">
-        <v>80163</v>
+        <v>92645</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6400,21 +6400,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574292</v>
+        <v>574445</v>
       </c>
       <c r="R59" t="n">
-        <v>7088883</v>
+        <v>7088594</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6486,32 +6486,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128342771</v>
+        <v>128342812</v>
       </c>
       <c r="B60" t="n">
-        <v>90390</v>
+        <v>80163</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574281</v>
+        <v>574292</v>
       </c>
       <c r="R60" t="n">
-        <v>7088848</v>
+        <v>7088883</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342667</v>
+        <v>128342771</v>
       </c>
       <c r="B61" t="n">
-        <v>92645</v>
+        <v>90390</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574390</v>
+        <v>574281</v>
       </c>
       <c r="R61" t="n">
-        <v>7088726</v>
+        <v>7088848</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6651,19 +6651,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6678,19 +6668,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128341588</v>
+        <v>128342667</v>
       </c>
       <c r="B62" t="n">
         <v>92645</v>
@@ -6725,13 +6715,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574445</v>
+        <v>574390</v>
       </c>
       <c r="R62" t="n">
-        <v>7088594</v>
+        <v>7088726</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6758,9 +6748,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6775,12 +6775,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342176</v>
+        <v>128342400</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>92838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,42 +7016,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574286</v>
+        <v>574381</v>
       </c>
       <c r="R65" t="n">
-        <v>7088863</v>
+        <v>7088725</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7078,24 +7073,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7110,22 +7090,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128341715</v>
+        <v>128342176</v>
       </c>
       <c r="B66" t="n">
-        <v>92838</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7133,37 +7113,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574446</v>
+        <v>574286</v>
       </c>
       <c r="R66" t="n">
-        <v>7088674</v>
+        <v>7088863</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7190,9 +7175,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7207,19 +7207,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128342400</v>
+        <v>128341715</v>
       </c>
       <c r="B67" t="n">
         <v>92838</v>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574381</v>
+        <v>574446</v>
       </c>
       <c r="R67" t="n">
-        <v>7088725</v>
+        <v>7088674</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7423,10 +7423,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341109</v>
+        <v>128341878</v>
       </c>
       <c r="B69" t="n">
-        <v>57672</v>
+        <v>79649</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7434,39 +7434,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574429</v>
+        <v>574329</v>
       </c>
       <c r="R69" t="n">
-        <v>7088591</v>
+        <v>7088770</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7498,7 +7493,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7508,12 +7503,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7528,44 +7518,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128341878</v>
+        <v>128342397</v>
       </c>
       <c r="B70" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7575,10 +7565,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574329</v>
+        <v>574294</v>
       </c>
       <c r="R70" t="n">
-        <v>7088770</v>
+        <v>7088921</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7610,7 +7600,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7620,7 +7610,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7635,57 +7625,62 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128342397</v>
+        <v>128341109</v>
       </c>
       <c r="B71" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574294</v>
+        <v>574429</v>
       </c>
       <c r="R71" t="n">
-        <v>7088921</v>
+        <v>7088591</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,7 +7712,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7727,7 +7722,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7754,32 +7754,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128342408</v>
+        <v>128341813</v>
       </c>
       <c r="B72" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7789,10 +7789,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574379</v>
+        <v>574445</v>
       </c>
       <c r="R72" t="n">
-        <v>7088725</v>
+        <v>7088668</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128342337</v>
+        <v>128341787</v>
       </c>
       <c r="B73" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7862,34 +7862,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574241</v>
+        <v>574356</v>
       </c>
       <c r="R73" t="n">
-        <v>7088939</v>
+        <v>7088756</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7921,7 +7926,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7931,7 +7936,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7958,32 +7963,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128341813</v>
+        <v>128342408</v>
       </c>
       <c r="B74" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7993,10 +7998,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574445</v>
+        <v>574379</v>
       </c>
       <c r="R74" t="n">
-        <v>7088668</v>
+        <v>7088725</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8055,10 +8060,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128341787</v>
+        <v>128342337</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>92639</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8066,39 +8071,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574356</v>
+        <v>574241</v>
       </c>
       <c r="R75" t="n">
-        <v>7088756</v>
+        <v>7088939</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128342806</v>
+        <v>128341749</v>
       </c>
       <c r="B13" t="n">
-        <v>80134</v>
+        <v>78789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574452</v>
+        <v>574358</v>
       </c>
       <c r="R13" t="n">
-        <v>7088593</v>
+        <v>7088744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128341749</v>
+        <v>128342806</v>
       </c>
       <c r="B15" t="n">
-        <v>78789</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574358</v>
+        <v>574452</v>
       </c>
       <c r="R15" t="n">
-        <v>7088744</v>
+        <v>7088593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,50 +2128,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341646</v>
+        <v>128342757</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R16" t="n">
-        <v>7088594</v>
+        <v>7088843</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2204,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,32 +2225,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341724</v>
+        <v>128341886</v>
       </c>
       <c r="B17" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574435</v>
+        <v>574321</v>
       </c>
       <c r="R17" t="n">
-        <v>7088666</v>
+        <v>7088769</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2303,9 +2293,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341740</v>
+        <v>128341807</v>
       </c>
       <c r="B18" t="n">
-        <v>79649</v>
+        <v>79031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574418</v>
+        <v>574435</v>
       </c>
       <c r="R18" t="n">
-        <v>7088654</v>
+        <v>7088661</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,48 +2429,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341886</v>
+        <v>128341646</v>
       </c>
       <c r="B19" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574321</v>
+        <v>574445</v>
       </c>
       <c r="R19" t="n">
-        <v>7088769</v>
+        <v>7088594</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2497,19 +2502,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:37</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341807</v>
+        <v>128341724</v>
       </c>
       <c r="B20" t="n">
-        <v>79031</v>
+        <v>79649</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
         <v>574435</v>
       </c>
       <c r="R20" t="n">
-        <v>7088661</v>
+        <v>7088666</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342757</v>
+        <v>128341740</v>
       </c>
       <c r="B21" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574291</v>
+        <v>574418</v>
       </c>
       <c r="R21" t="n">
-        <v>7088843</v>
+        <v>7088654</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128342664</v>
+        <v>128341581</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>78698</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,42 +5119,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574390</v>
+        <v>574445</v>
       </c>
       <c r="R46" t="n">
-        <v>7088731</v>
+        <v>7088593</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5181,24 +5176,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5213,22 +5193,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128341581</v>
+        <v>128341946</v>
       </c>
       <c r="B47" t="n">
-        <v>78698</v>
+        <v>79649</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5236,21 +5216,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5260,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574445</v>
+        <v>574406</v>
       </c>
       <c r="R47" t="n">
-        <v>7088593</v>
+        <v>7088724</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5322,10 +5302,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128341946</v>
+        <v>128342664</v>
       </c>
       <c r="B48" t="n">
-        <v>79649</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5333,37 +5313,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574406</v>
+        <v>574390</v>
       </c>
       <c r="R48" t="n">
-        <v>7088724</v>
+        <v>7088731</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5390,9 +5375,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5407,12 +5407,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341543</v>
+        <v>128341658</v>
       </c>
       <c r="B53" t="n">
-        <v>80170</v>
+        <v>78698</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
         <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088593</v>
+        <v>7088595</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342561</v>
+        <v>128341543</v>
       </c>
       <c r="B54" t="n">
-        <v>79649</v>
+        <v>80170</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574312</v>
+        <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088790</v>
+        <v>7088593</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342438</v>
+        <v>128342561</v>
       </c>
       <c r="B55" t="n">
-        <v>78789</v>
+        <v>79649</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574373</v>
+        <v>574312</v>
       </c>
       <c r="R55" t="n">
-        <v>7088729</v>
+        <v>7088790</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342351</v>
+        <v>128342438</v>
       </c>
       <c r="B56" t="n">
-        <v>92649</v>
+        <v>78789</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574372</v>
+        <v>574373</v>
       </c>
       <c r="R56" t="n">
-        <v>7088765</v>
+        <v>7088729</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342751</v>
+        <v>128342351</v>
       </c>
       <c r="B57" t="n">
-        <v>78698</v>
+        <v>92649</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574291</v>
+        <v>574372</v>
       </c>
       <c r="R57" t="n">
-        <v>7088844</v>
+        <v>7088765</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,7 +6292,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341658</v>
+        <v>128342751</v>
       </c>
       <c r="B58" t="n">
         <v>78698</v>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R58" t="n">
-        <v>7088595</v>
+        <v>7088844</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6389,10 +6389,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128341588</v>
+        <v>128342812</v>
       </c>
       <c r="B59" t="n">
-        <v>92645</v>
+        <v>80163</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6400,21 +6400,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R59" t="n">
-        <v>7088594</v>
+        <v>7088883</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6486,32 +6486,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128342812</v>
+        <v>128342771</v>
       </c>
       <c r="B60" t="n">
-        <v>80163</v>
+        <v>90390</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574292</v>
+        <v>574281</v>
       </c>
       <c r="R60" t="n">
-        <v>7088883</v>
+        <v>7088848</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6583,32 +6583,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342771</v>
+        <v>128342667</v>
       </c>
       <c r="B61" t="n">
-        <v>90390</v>
+        <v>92645</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574281</v>
+        <v>574390</v>
       </c>
       <c r="R61" t="n">
-        <v>7088848</v>
+        <v>7088726</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6651,9 +6651,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6668,19 +6678,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128342667</v>
+        <v>128341588</v>
       </c>
       <c r="B62" t="n">
         <v>92645</v>
@@ -6715,13 +6725,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574390</v>
+        <v>574445</v>
       </c>
       <c r="R62" t="n">
-        <v>7088726</v>
+        <v>7088594</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6748,19 +6758,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6775,12 +6775,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342400</v>
+        <v>128342176</v>
       </c>
       <c r="B65" t="n">
-        <v>92838</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,37 +7016,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574381</v>
+        <v>574286</v>
       </c>
       <c r="R65" t="n">
-        <v>7088725</v>
+        <v>7088863</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,9 +7078,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7090,22 +7110,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128342176</v>
+        <v>128341715</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>92838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7113,42 +7133,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574286</v>
+        <v>574446</v>
       </c>
       <c r="R66" t="n">
-        <v>7088863</v>
+        <v>7088674</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7175,24 +7190,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7207,19 +7207,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128341715</v>
+        <v>128342400</v>
       </c>
       <c r="B67" t="n">
         <v>92838</v>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574446</v>
+        <v>574381</v>
       </c>
       <c r="R67" t="n">
-        <v>7088674</v>
+        <v>7088725</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7423,10 +7423,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341878</v>
+        <v>128341109</v>
       </c>
       <c r="B69" t="n">
-        <v>79649</v>
+        <v>57672</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7434,34 +7434,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574329</v>
+        <v>574429</v>
       </c>
       <c r="R69" t="n">
-        <v>7088770</v>
+        <v>7088591</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,7 +7498,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7503,7 +7508,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7518,44 +7528,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128342397</v>
+        <v>128341878</v>
       </c>
       <c r="B70" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7565,10 +7575,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574294</v>
+        <v>574329</v>
       </c>
       <c r="R70" t="n">
-        <v>7088921</v>
+        <v>7088770</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7600,7 +7610,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7610,7 +7620,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7625,62 +7635,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128341109</v>
+        <v>128342397</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574429</v>
+        <v>574294</v>
       </c>
       <c r="R71" t="n">
-        <v>7088591</v>
+        <v>7088921</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7712,7 +7717,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7722,12 +7727,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7754,32 +7754,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128341813</v>
+        <v>128342408</v>
       </c>
       <c r="B72" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7789,10 +7789,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574445</v>
+        <v>574379</v>
       </c>
       <c r="R72" t="n">
-        <v>7088668</v>
+        <v>7088725</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128341787</v>
+        <v>128342337</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>92639</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7862,39 +7862,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574356</v>
+        <v>574241</v>
       </c>
       <c r="R73" t="n">
-        <v>7088756</v>
+        <v>7088939</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7926,7 +7921,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7936,7 +7931,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7963,32 +7958,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128342408</v>
+        <v>128341813</v>
       </c>
       <c r="B74" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7998,10 +7993,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574379</v>
+        <v>574445</v>
       </c>
       <c r="R74" t="n">
-        <v>7088725</v>
+        <v>7088668</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8060,10 +8055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128342337</v>
+        <v>128341787</v>
       </c>
       <c r="B75" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8071,34 +8066,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574241</v>
+        <v>574356</v>
       </c>
       <c r="R75" t="n">
-        <v>7088939</v>
+        <v>7088756</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341860</v>
+        <v>128342525</v>
       </c>
       <c r="B8" t="n">
-        <v>78789</v>
+        <v>79649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574328</v>
+        <v>574323</v>
       </c>
       <c r="R8" t="n">
-        <v>7088763</v>
+        <v>7088778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,19 +1350,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,22 +1367,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341697</v>
+        <v>128341860</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>78789</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,39 +1390,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574383</v>
+        <v>574328</v>
       </c>
       <c r="R9" t="n">
-        <v>7088749</v>
+        <v>7088763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1449,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1474,12 +1459,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,12 +1474,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1613,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128342525</v>
+        <v>128341697</v>
       </c>
       <c r="B11" t="n">
-        <v>79649</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,37 +1604,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574323</v>
+        <v>574383</v>
       </c>
       <c r="R11" t="n">
-        <v>7088778</v>
+        <v>7088749</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1681,9 +1666,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2128,45 +2128,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128342757</v>
+        <v>128341646</v>
       </c>
       <c r="B16" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R16" t="n">
-        <v>7088843</v>
+        <v>7088594</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2199,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,32 +2235,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341886</v>
+        <v>128341724</v>
       </c>
       <c r="B17" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2270,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574321</v>
+        <v>574435</v>
       </c>
       <c r="R17" t="n">
-        <v>7088769</v>
+        <v>7088666</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2293,19 +2303,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341807</v>
+        <v>128341740</v>
       </c>
       <c r="B18" t="n">
-        <v>79031</v>
+        <v>79649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574435</v>
+        <v>574418</v>
       </c>
       <c r="R18" t="n">
-        <v>7088661</v>
+        <v>7088654</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,53 +2429,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341646</v>
+        <v>128341886</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574445</v>
+        <v>574321</v>
       </c>
       <c r="R19" t="n">
-        <v>7088594</v>
+        <v>7088769</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2502,14 +2497,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341724</v>
+        <v>128341807</v>
       </c>
       <c r="B20" t="n">
-        <v>79649</v>
+        <v>79031</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
         <v>574435</v>
       </c>
       <c r="R20" t="n">
-        <v>7088666</v>
+        <v>7088661</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,32 +2633,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341740</v>
+        <v>128342757</v>
       </c>
       <c r="B21" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574418</v>
+        <v>574291</v>
       </c>
       <c r="R21" t="n">
-        <v>7088654</v>
+        <v>7088843</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128341564</v>
+        <v>128342847</v>
       </c>
       <c r="B26" t="n">
         <v>92645</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574445</v>
+        <v>574354</v>
       </c>
       <c r="R26" t="n">
-        <v>7088593</v>
+        <v>7088881</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,7 +3215,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342434</v>
+        <v>128341564</v>
       </c>
       <c r="B27" t="n">
         <v>92645</v>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574373</v>
+        <v>574445</v>
       </c>
       <c r="R27" t="n">
-        <v>7088729</v>
+        <v>7088593</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,32 +3312,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342391</v>
+        <v>128342434</v>
       </c>
       <c r="B28" t="n">
-        <v>91516</v>
+        <v>92645</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574371</v>
+        <v>574373</v>
       </c>
       <c r="R28" t="n">
         <v>7088729</v>
@@ -3409,32 +3409,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342274</v>
+        <v>128342391</v>
       </c>
       <c r="B29" t="n">
-        <v>92645</v>
+        <v>91516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574276</v>
+        <v>574371</v>
       </c>
       <c r="R29" t="n">
-        <v>7088904</v>
+        <v>7088729</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3477,19 +3477,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3504,44 +3494,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128341678</v>
+        <v>128342274</v>
       </c>
       <c r="B30" t="n">
-        <v>78698</v>
+        <v>92645</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,13 +3541,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574449</v>
+        <v>574276</v>
       </c>
       <c r="R30" t="n">
-        <v>7088616</v>
+        <v>7088904</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3584,9 +3574,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3601,44 +3601,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128342847</v>
+        <v>128341678</v>
       </c>
       <c r="B31" t="n">
-        <v>92645</v>
+        <v>78698</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574354</v>
+        <v>574449</v>
       </c>
       <c r="R31" t="n">
-        <v>7088881</v>
+        <v>7088616</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128342782</v>
+        <v>128341686</v>
       </c>
       <c r="B32" t="n">
-        <v>92661</v>
+        <v>90390</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3721,21 +3721,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574280</v>
+        <v>574445</v>
       </c>
       <c r="R32" t="n">
-        <v>7088852</v>
+        <v>7088630</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128341686</v>
+        <v>128342815</v>
       </c>
       <c r="B33" t="n">
-        <v>90390</v>
+        <v>92645</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R33" t="n">
-        <v>7088630</v>
+        <v>7088883</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3904,32 +3904,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128342815</v>
+        <v>128342782</v>
       </c>
       <c r="B34" t="n">
-        <v>92645</v>
+        <v>92661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574292</v>
+        <v>574280</v>
       </c>
       <c r="R34" t="n">
-        <v>7088883</v>
+        <v>7088852</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4797,53 +4797,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341748</v>
+        <v>128342904</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>92645</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574361</v>
+        <v>574370</v>
       </c>
       <c r="R43" t="n">
-        <v>7088768</v>
+        <v>7088775</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4870,24 +4865,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4902,60 +4882,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128342904</v>
+        <v>128341748</v>
       </c>
       <c r="B44" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574370</v>
+        <v>574361</v>
       </c>
       <c r="R44" t="n">
-        <v>7088775</v>
+        <v>7088768</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4982,9 +4967,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,12 +4999,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341658</v>
+        <v>128341543</v>
       </c>
       <c r="B53" t="n">
-        <v>78698</v>
+        <v>80170</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5845,7 +5845,7 @@
         <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088595</v>
+        <v>7088593</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341543</v>
+        <v>128341658</v>
       </c>
       <c r="B54" t="n">
-        <v>80170</v>
+        <v>78698</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
         <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088593</v>
+        <v>7088595</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342176</v>
+        <v>128342400</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>92838</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,42 +7016,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574286</v>
+        <v>574381</v>
       </c>
       <c r="R65" t="n">
-        <v>7088863</v>
+        <v>7088725</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7078,24 +7073,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7110,22 +7090,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128341715</v>
+        <v>128342176</v>
       </c>
       <c r="B66" t="n">
-        <v>92838</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7133,37 +7113,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574446</v>
+        <v>574286</v>
       </c>
       <c r="R66" t="n">
-        <v>7088674</v>
+        <v>7088863</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7190,9 +7175,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7207,19 +7207,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128342400</v>
+        <v>128341715</v>
       </c>
       <c r="B67" t="n">
         <v>92838</v>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574381</v>
+        <v>574446</v>
       </c>
       <c r="R67" t="n">
-        <v>7088725</v>
+        <v>7088674</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7423,10 +7423,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341109</v>
+        <v>128341878</v>
       </c>
       <c r="B69" t="n">
-        <v>57672</v>
+        <v>79649</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7434,39 +7434,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574429</v>
+        <v>574329</v>
       </c>
       <c r="R69" t="n">
-        <v>7088591</v>
+        <v>7088770</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7498,7 +7493,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7508,12 +7503,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7528,44 +7518,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128341878</v>
+        <v>128342397</v>
       </c>
       <c r="B70" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7575,10 +7565,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574329</v>
+        <v>574294</v>
       </c>
       <c r="R70" t="n">
-        <v>7088770</v>
+        <v>7088921</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7610,7 +7600,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7620,7 +7610,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7635,57 +7625,62 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128342397</v>
+        <v>128341109</v>
       </c>
       <c r="B71" t="n">
-        <v>92645</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574294</v>
+        <v>574429</v>
       </c>
       <c r="R71" t="n">
-        <v>7088921</v>
+        <v>7088591</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,7 +7712,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7727,7 +7722,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7754,32 +7754,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128342408</v>
+        <v>128341813</v>
       </c>
       <c r="B72" t="n">
-        <v>79649</v>
+        <v>92645</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7789,10 +7789,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574379</v>
+        <v>574445</v>
       </c>
       <c r="R72" t="n">
-        <v>7088725</v>
+        <v>7088668</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128342337</v>
+        <v>128341787</v>
       </c>
       <c r="B73" t="n">
-        <v>92639</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7862,34 +7862,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574241</v>
+        <v>574356</v>
       </c>
       <c r="R73" t="n">
-        <v>7088939</v>
+        <v>7088756</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7921,7 +7926,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7931,7 +7936,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7958,32 +7963,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128341813</v>
+        <v>128342408</v>
       </c>
       <c r="B74" t="n">
-        <v>92645</v>
+        <v>79649</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7993,10 +7998,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574445</v>
+        <v>574379</v>
       </c>
       <c r="R74" t="n">
-        <v>7088668</v>
+        <v>7088725</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8055,10 +8060,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128341787</v>
+        <v>128342337</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>92639</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8066,39 +8071,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574356</v>
+        <v>574241</v>
       </c>
       <c r="R75" t="n">
-        <v>7088756</v>
+        <v>7088939</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342785</v>
+        <v>128342930</v>
       </c>
       <c r="B2" t="n">
-        <v>79649</v>
+        <v>92666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574275</v>
+        <v>574400</v>
       </c>
       <c r="R2" t="n">
-        <v>7088862</v>
+        <v>7088743</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128342842</v>
+        <v>128342785</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>79650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574354</v>
+        <v>574275</v>
       </c>
       <c r="R3" t="n">
-        <v>7088880</v>
+        <v>7088862</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342930</v>
+        <v>128342277</v>
       </c>
       <c r="B4" t="n">
-        <v>92661</v>
+        <v>78699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574400</v>
+        <v>574382</v>
       </c>
       <c r="R4" t="n">
-        <v>7088743</v>
+        <v>7088759</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,7 +969,7 @@
         <v>128342191</v>
       </c>
       <c r="B5" t="n">
-        <v>92639</v>
+        <v>92644</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,48 +1073,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128341917</v>
+        <v>128342842</v>
       </c>
       <c r="B6" t="n">
-        <v>78789</v>
+        <v>56864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574334</v>
+        <v>574354</v>
       </c>
       <c r="R6" t="n">
-        <v>7088809</v>
+        <v>7088880</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1146,19 +1146,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,22 +1163,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342277</v>
+        <v>128341917</v>
       </c>
       <c r="B7" t="n">
-        <v>78698</v>
+        <v>78790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,13 +1210,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574382</v>
+        <v>574334</v>
       </c>
       <c r="R7" t="n">
-        <v>7088759</v>
+        <v>7088809</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1253,9 +1243,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,44 +1270,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128342525</v>
+        <v>128341140</v>
       </c>
       <c r="B8" t="n">
-        <v>79649</v>
+        <v>92650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574323</v>
+        <v>574438</v>
       </c>
       <c r="R8" t="n">
-        <v>7088778</v>
+        <v>7088595</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,9 +1350,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341860</v>
+        <v>128342525</v>
       </c>
       <c r="B9" t="n">
-        <v>78789</v>
+        <v>79650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,13 +1424,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574328</v>
+        <v>574323</v>
       </c>
       <c r="R9" t="n">
-        <v>7088763</v>
+        <v>7088778</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1447,19 +1457,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,57 +1474,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341140</v>
+        <v>128341697</v>
       </c>
       <c r="B10" t="n">
-        <v>92645</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574438</v>
+        <v>574383</v>
       </c>
       <c r="R10" t="n">
-        <v>7088595</v>
+        <v>7088749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1561,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1566,7 +1571,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341697</v>
+        <v>128341860</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>78790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,39 +1614,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574383</v>
+        <v>574328</v>
       </c>
       <c r="R11" t="n">
-        <v>7088749</v>
+        <v>7088763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
         <v>128342361</v>
       </c>
       <c r="B12" t="n">
-        <v>92639</v>
+        <v>92644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128341749</v>
+        <v>128342299</v>
       </c>
       <c r="B13" t="n">
-        <v>78789</v>
+        <v>92666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574358</v>
+        <v>574373</v>
       </c>
       <c r="R13" t="n">
-        <v>7088744</v>
+        <v>7088753</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,19 +1885,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:26</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,22 +1902,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128342299</v>
+        <v>128342806</v>
       </c>
       <c r="B14" t="n">
-        <v>92661</v>
+        <v>80135</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1949,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574373</v>
+        <v>574452</v>
       </c>
       <c r="R14" t="n">
-        <v>7088753</v>
+        <v>7088593</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,9 +1982,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342806</v>
+        <v>128341749</v>
       </c>
       <c r="B15" t="n">
-        <v>80134</v>
+        <v>78790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574452</v>
+        <v>574358</v>
       </c>
       <c r="R15" t="n">
-        <v>7088593</v>
+        <v>7088744</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,50 +2128,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341646</v>
+        <v>128342757</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R16" t="n">
-        <v>7088594</v>
+        <v>7088843</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2204,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,32 +2225,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341724</v>
+        <v>128341886</v>
       </c>
       <c r="B17" t="n">
-        <v>79649</v>
+        <v>92650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574435</v>
+        <v>574321</v>
       </c>
       <c r="R17" t="n">
-        <v>7088666</v>
+        <v>7088769</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2303,9 +2293,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341740</v>
+        <v>128341807</v>
       </c>
       <c r="B18" t="n">
-        <v>79649</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574418</v>
+        <v>574435</v>
       </c>
       <c r="R18" t="n">
-        <v>7088654</v>
+        <v>7088661</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,32 +2429,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341886</v>
+        <v>128341724</v>
       </c>
       <c r="B19" t="n">
-        <v>92645</v>
+        <v>79650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574321</v>
+        <v>574435</v>
       </c>
       <c r="R19" t="n">
-        <v>7088769</v>
+        <v>7088666</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2497,19 +2497,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2514,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341807</v>
+        <v>128341740</v>
       </c>
       <c r="B20" t="n">
-        <v>79031</v>
+        <v>79650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574435</v>
+        <v>574418</v>
       </c>
       <c r="R20" t="n">
-        <v>7088661</v>
+        <v>7088654</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,45 +2623,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128342757</v>
+        <v>128341646</v>
       </c>
       <c r="B21" t="n">
-        <v>92645</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R21" t="n">
-        <v>7088843</v>
+        <v>7088594</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2704,6 +2699,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,7 +2733,7 @@
         <v>128342521</v>
       </c>
       <c r="B22" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128342284</v>
       </c>
       <c r="B23" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,32 +2924,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342655</v>
+        <v>128342754</v>
       </c>
       <c r="B24" t="n">
-        <v>90158</v>
+        <v>79650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574282</v>
+        <v>574291</v>
       </c>
       <c r="R24" t="n">
-        <v>7088807</v>
+        <v>7088845</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342754</v>
+        <v>128342655</v>
       </c>
       <c r="B25" t="n">
-        <v>79649</v>
+        <v>90161</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574291</v>
+        <v>574282</v>
       </c>
       <c r="R25" t="n">
-        <v>7088845</v>
+        <v>7088807</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342847</v>
+        <v>128341678</v>
       </c>
       <c r="B26" t="n">
-        <v>92645</v>
+        <v>78699</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574354</v>
+        <v>574449</v>
       </c>
       <c r="R26" t="n">
-        <v>7088881</v>
+        <v>7088616</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128341564</v>
+        <v>128342434</v>
       </c>
       <c r="B27" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574445</v>
+        <v>574373</v>
       </c>
       <c r="R27" t="n">
-        <v>7088593</v>
+        <v>7088729</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342434</v>
+        <v>128342847</v>
       </c>
       <c r="B28" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574373</v>
+        <v>574354</v>
       </c>
       <c r="R28" t="n">
-        <v>7088729</v>
+        <v>7088881</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3409,32 +3409,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342391</v>
+        <v>128341564</v>
       </c>
       <c r="B29" t="n">
-        <v>91516</v>
+        <v>92650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574371</v>
+        <v>574445</v>
       </c>
       <c r="R29" t="n">
-        <v>7088729</v>
+        <v>7088593</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3509,7 +3509,7 @@
         <v>128342274</v>
       </c>
       <c r="B30" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3613,32 +3613,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128341678</v>
+        <v>128342391</v>
       </c>
       <c r="B31" t="n">
-        <v>78698</v>
+        <v>91521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574449</v>
+        <v>574371</v>
       </c>
       <c r="R31" t="n">
-        <v>7088616</v>
+        <v>7088729</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3713,7 +3713,7 @@
         <v>128341686</v>
       </c>
       <c r="B32" t="n">
-        <v>90390</v>
+        <v>90393</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128342815</v>
+        <v>128342782</v>
       </c>
       <c r="B33" t="n">
-        <v>92645</v>
+        <v>92666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574292</v>
+        <v>574280</v>
       </c>
       <c r="R33" t="n">
-        <v>7088883</v>
+        <v>7088852</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3904,32 +3904,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128342782</v>
+        <v>128342815</v>
       </c>
       <c r="B34" t="n">
-        <v>92661</v>
+        <v>92650</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574280</v>
+        <v>574292</v>
       </c>
       <c r="R34" t="n">
-        <v>7088852</v>
+        <v>7088883</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4001,32 +4001,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128342012</v>
+        <v>128342574</v>
       </c>
       <c r="B35" t="n">
-        <v>92645</v>
+        <v>78699</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574415</v>
+        <v>574308</v>
       </c>
       <c r="R35" t="n">
-        <v>7088716</v>
+        <v>7088789</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128341929</v>
+        <v>128341248</v>
       </c>
       <c r="B36" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574406</v>
+        <v>574418</v>
       </c>
       <c r="R36" t="n">
-        <v>7088725</v>
+        <v>7088658</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4166,9 +4166,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,22 +4193,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128341248</v>
+        <v>128341663</v>
       </c>
       <c r="B37" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4230,13 +4240,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574418</v>
+        <v>574444</v>
       </c>
       <c r="R37" t="n">
-        <v>7088658</v>
+        <v>7088610</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4263,19 +4273,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4290,12 +4290,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4305,7 +4305,7 @@
         <v>128342804</v>
       </c>
       <c r="B38" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4399,32 +4399,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128342574</v>
+        <v>128342012</v>
       </c>
       <c r="B39" t="n">
-        <v>78698</v>
+        <v>92650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574308</v>
+        <v>574415</v>
       </c>
       <c r="R39" t="n">
-        <v>7088789</v>
+        <v>7088716</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128342578</v>
+        <v>128341929</v>
       </c>
       <c r="B40" t="n">
-        <v>79649</v>
+        <v>92650</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574309</v>
+        <v>574406</v>
       </c>
       <c r="R40" t="n">
-        <v>7088787</v>
+        <v>7088725</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128341663</v>
+        <v>128342578</v>
       </c>
       <c r="B41" t="n">
-        <v>92645</v>
+        <v>79650</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574444</v>
+        <v>574309</v>
       </c>
       <c r="R41" t="n">
-        <v>7088610</v>
+        <v>7088787</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4693,7 +4693,7 @@
         <v>128341959</v>
       </c>
       <c r="B42" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>128342904</v>
       </c>
       <c r="B43" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>128341748</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128342466</v>
+        <v>128341581</v>
       </c>
       <c r="B45" t="n">
-        <v>92661</v>
+        <v>78699</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574352</v>
+        <v>574445</v>
       </c>
       <c r="R45" t="n">
-        <v>7088735</v>
+        <v>7088593</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128341581</v>
+        <v>128342466</v>
       </c>
       <c r="B46" t="n">
-        <v>78698</v>
+        <v>92666</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574445</v>
+        <v>574352</v>
       </c>
       <c r="R46" t="n">
-        <v>7088593</v>
+        <v>7088735</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5208,7 +5208,7 @@
         <v>128341946</v>
       </c>
       <c r="B47" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128342664</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,32 +5419,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128342246</v>
+        <v>128342880</v>
       </c>
       <c r="B49" t="n">
-        <v>92645</v>
+        <v>79650</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574397</v>
+        <v>574359</v>
       </c>
       <c r="R49" t="n">
-        <v>7088752</v>
+        <v>7088849</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5516,32 +5516,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342358</v>
+        <v>128342246</v>
       </c>
       <c r="B50" t="n">
-        <v>90390</v>
+        <v>92650</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574372</v>
+        <v>574397</v>
       </c>
       <c r="R50" t="n">
-        <v>7088765</v>
+        <v>7088752</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342880</v>
+        <v>128342358</v>
       </c>
       <c r="B51" t="n">
-        <v>79649</v>
+        <v>90393</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5624,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574359</v>
+        <v>574372</v>
       </c>
       <c r="R51" t="n">
-        <v>7088849</v>
+        <v>7088765</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5713,7 +5713,7 @@
         <v>128342898</v>
       </c>
       <c r="B52" t="n">
-        <v>91320</v>
+        <v>91325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341543</v>
+        <v>128342351</v>
       </c>
       <c r="B53" t="n">
-        <v>80170</v>
+        <v>92654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574372</v>
       </c>
       <c r="R53" t="n">
-        <v>7088593</v>
+        <v>7088765</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341658</v>
+        <v>128342561</v>
       </c>
       <c r="B54" t="n">
-        <v>78698</v>
+        <v>79650</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,21 +5915,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R54" t="n">
-        <v>7088595</v>
+        <v>7088790</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,32 +6001,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342561</v>
+        <v>128341543</v>
       </c>
       <c r="B55" t="n">
-        <v>79649</v>
+        <v>80171</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574312</v>
+        <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088790</v>
+        <v>7088593</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6101,7 +6101,7 @@
         <v>128342438</v>
       </c>
       <c r="B56" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342351</v>
+        <v>128341658</v>
       </c>
       <c r="B57" t="n">
-        <v>92649</v>
+        <v>78699</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574372</v>
+        <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088765</v>
+        <v>7088595</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6295,7 +6295,7 @@
         <v>128342751</v>
       </c>
       <c r="B58" t="n">
-        <v>78698</v>
+        <v>78699</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,10 +6389,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128342812</v>
+        <v>128341588</v>
       </c>
       <c r="B59" t="n">
-        <v>80163</v>
+        <v>92650</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6400,21 +6400,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574292</v>
+        <v>574445</v>
       </c>
       <c r="R59" t="n">
-        <v>7088883</v>
+        <v>7088594</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6486,32 +6486,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128342771</v>
+        <v>128342667</v>
       </c>
       <c r="B60" t="n">
-        <v>90390</v>
+        <v>92650</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574281</v>
+        <v>574390</v>
       </c>
       <c r="R60" t="n">
-        <v>7088848</v>
+        <v>7088726</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6554,9 +6554,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6571,44 +6581,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342667</v>
+        <v>128342771</v>
       </c>
       <c r="B61" t="n">
-        <v>92645</v>
+        <v>90393</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,13 +6628,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574390</v>
+        <v>574281</v>
       </c>
       <c r="R61" t="n">
-        <v>7088726</v>
+        <v>7088848</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6651,19 +6661,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6678,22 +6678,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128341588</v>
+        <v>128342812</v>
       </c>
       <c r="B62" t="n">
-        <v>92645</v>
+        <v>80164</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6701,21 +6701,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R62" t="n">
-        <v>7088594</v>
+        <v>7088883</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6787,10 +6787,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128341482</v>
+        <v>128341312</v>
       </c>
       <c r="B63" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6816,19 +6816,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574408</v>
+        <v>574418</v>
       </c>
       <c r="R63" t="n">
-        <v>7088736</v>
+        <v>7088693</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6860,7 +6857,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6870,7 +6867,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6879,7 +6876,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6898,10 +6894,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128341312</v>
+        <v>128341482</v>
       </c>
       <c r="B64" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6927,16 +6923,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574418</v>
+        <v>574408</v>
       </c>
       <c r="R64" t="n">
-        <v>7088693</v>
+        <v>7088736</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6968,7 +6967,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -6978,7 +6977,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6987,6 +6986,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>128342400</v>
       </c>
       <c r="B65" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7102,10 +7102,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128342176</v>
+        <v>128341715</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>92843</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7113,42 +7113,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574286</v>
+        <v>574446</v>
       </c>
       <c r="R66" t="n">
-        <v>7088863</v>
+        <v>7088674</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7175,24 +7170,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7207,22 +7187,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128341715</v>
+        <v>128342176</v>
       </c>
       <c r="B67" t="n">
-        <v>92838</v>
+        <v>57673</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7230,37 +7210,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574446</v>
+        <v>574286</v>
       </c>
       <c r="R67" t="n">
-        <v>7088674</v>
+        <v>7088863</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7287,9 +7272,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7304,12 +7304,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7319,7 +7319,7 @@
         <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>80163</v>
+        <v>80164</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7423,32 +7423,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341878</v>
+        <v>128342397</v>
       </c>
       <c r="B69" t="n">
-        <v>79649</v>
+        <v>92650</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574329</v>
+        <v>574294</v>
       </c>
       <c r="R69" t="n">
-        <v>7088770</v>
+        <v>7088921</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7518,44 +7518,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128342397</v>
+        <v>128341878</v>
       </c>
       <c r="B70" t="n">
-        <v>92645</v>
+        <v>79650</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574294</v>
+        <v>574329</v>
       </c>
       <c r="R70" t="n">
-        <v>7088921</v>
+        <v>7088770</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7625,12 +7625,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7640,7 +7640,7 @@
         <v>128341109</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>128341813</v>
       </c>
       <c r="B72" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7851,10 +7851,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128341787</v>
+        <v>128342337</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>92644</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7862,39 +7862,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574356</v>
+        <v>574241</v>
       </c>
       <c r="R73" t="n">
-        <v>7088756</v>
+        <v>7088939</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7926,7 +7921,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7936,7 +7931,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7963,10 +7958,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128342408</v>
+        <v>128341787</v>
       </c>
       <c r="B74" t="n">
-        <v>79649</v>
+        <v>57673</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7974,37 +7969,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574379</v>
+        <v>574356</v>
       </c>
       <c r="R74" t="n">
-        <v>7088725</v>
+        <v>7088756</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8031,9 +8031,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8048,22 +8058,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128342337</v>
+        <v>128342408</v>
       </c>
       <c r="B75" t="n">
-        <v>92639</v>
+        <v>79650</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8071,21 +8081,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8095,13 +8105,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574241</v>
+        <v>574379</v>
       </c>
       <c r="R75" t="n">
-        <v>7088939</v>
+        <v>7088725</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8128,19 +8138,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8155,12 +8155,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
         <v>128342186</v>
       </c>
       <c r="B76" t="n">
-        <v>92060</v>
+        <v>92065</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>128355111</v>
       </c>
       <c r="B77" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -2128,45 +2128,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128342757</v>
+        <v>128341646</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>57673</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R16" t="n">
-        <v>7088843</v>
+        <v>7088594</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2199,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341886</v>
+        <v>128342757</v>
       </c>
       <c r="B17" t="n">
         <v>92650</v>
@@ -2260,13 +2270,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574321</v>
+        <v>574291</v>
       </c>
       <c r="R17" t="n">
-        <v>7088769</v>
+        <v>7088843</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2293,19 +2303,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,44 +2320,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341807</v>
+        <v>128341886</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574435</v>
+        <v>574321</v>
       </c>
       <c r="R18" t="n">
-        <v>7088661</v>
+        <v>7088769</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,9 +2400,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2417,12 +2427,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2623,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341646</v>
+        <v>128341807</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,39 +2644,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574445</v>
+        <v>574435</v>
       </c>
       <c r="R21" t="n">
-        <v>7088594</v>
+        <v>7088661</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2699,11 +2704,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342930</v>
+        <v>128342277</v>
       </c>
       <c r="B2" t="n">
-        <v>92666</v>
+        <v>78749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574400</v>
+        <v>574382</v>
       </c>
       <c r="R2" t="n">
-        <v>7088743</v>
+        <v>7088759</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128342785</v>
+        <v>128342191</v>
       </c>
       <c r="B3" t="n">
-        <v>79650</v>
+        <v>92736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574275</v>
+        <v>574279</v>
       </c>
       <c r="R3" t="n">
-        <v>7088862</v>
+        <v>7088861</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,9 +840,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342277</v>
+        <v>128342930</v>
       </c>
       <c r="B4" t="n">
-        <v>78699</v>
+        <v>92758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574382</v>
+        <v>574400</v>
       </c>
       <c r="R4" t="n">
-        <v>7088759</v>
+        <v>7088743</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342191</v>
+        <v>128342785</v>
       </c>
       <c r="B5" t="n">
-        <v>92644</v>
+        <v>79702</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1011,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574279</v>
+        <v>574275</v>
       </c>
       <c r="R5" t="n">
-        <v>7088861</v>
+        <v>7088862</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1034,19 +1044,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,65 +1061,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128342842</v>
+        <v>128341917</v>
       </c>
       <c r="B6" t="n">
-        <v>56864</v>
+        <v>78840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574354</v>
+        <v>574334</v>
       </c>
       <c r="R6" t="n">
-        <v>7088880</v>
+        <v>7088809</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1146,9 +1141,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1163,60 +1168,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128341917</v>
+        <v>128342842</v>
       </c>
       <c r="B7" t="n">
-        <v>78790</v>
+        <v>56876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574334</v>
+        <v>574354</v>
       </c>
       <c r="R7" t="n">
-        <v>7088809</v>
+        <v>7088880</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1243,19 +1253,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,44 +1270,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341140</v>
+        <v>128342525</v>
       </c>
       <c r="B8" t="n">
-        <v>92650</v>
+        <v>79702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574438</v>
+        <v>574323</v>
       </c>
       <c r="R8" t="n">
-        <v>7088595</v>
+        <v>7088778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,19 +1350,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,22 +1367,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128342525</v>
+        <v>128341860</v>
       </c>
       <c r="B9" t="n">
-        <v>79650</v>
+        <v>78840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1390,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,13 +1414,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574323</v>
+        <v>574328</v>
       </c>
       <c r="R9" t="n">
-        <v>7088778</v>
+        <v>7088763</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1457,9 +1447,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,62 +1474,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341697</v>
+        <v>128341140</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574383</v>
+        <v>574438</v>
       </c>
       <c r="R10" t="n">
-        <v>7088749</v>
+        <v>7088595</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,7 +1556,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1571,12 +1566,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341860</v>
+        <v>128341697</v>
       </c>
       <c r="B11" t="n">
-        <v>78790</v>
+        <v>57685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,34 +1604,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574328</v>
+        <v>574383</v>
       </c>
       <c r="R11" t="n">
-        <v>7088763</v>
+        <v>7088749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342361</v>
+        <v>128342299</v>
       </c>
       <c r="B12" t="n">
-        <v>92644</v>
+        <v>92758</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574230</v>
+        <v>574373</v>
       </c>
       <c r="R12" t="n">
-        <v>7088918</v>
+        <v>7088753</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1778,19 +1778,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128342299</v>
+        <v>128341749</v>
       </c>
       <c r="B13" t="n">
-        <v>92666</v>
+        <v>78840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574373</v>
+        <v>574358</v>
       </c>
       <c r="R13" t="n">
-        <v>7088753</v>
+        <v>7088744</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,9 +1875,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,12 +1902,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
         <v>128342806</v>
       </c>
       <c r="B14" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128341749</v>
+        <v>128342361</v>
       </c>
       <c r="B15" t="n">
-        <v>78790</v>
+        <v>92736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574358</v>
+        <v>574230</v>
       </c>
       <c r="R15" t="n">
-        <v>7088744</v>
+        <v>7088918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,62 +2116,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341646</v>
+        <v>128342757</v>
       </c>
       <c r="B16" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R16" t="n">
-        <v>7088594</v>
+        <v>7088843</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2204,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128342757</v>
+        <v>128341886</v>
       </c>
       <c r="B17" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2270,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574291</v>
+        <v>574321</v>
       </c>
       <c r="R17" t="n">
-        <v>7088843</v>
+        <v>7088769</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2303,9 +2293,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,60 +2320,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341886</v>
+        <v>128341646</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574321</v>
+        <v>574445</v>
       </c>
       <c r="R18" t="n">
-        <v>7088769</v>
+        <v>7088594</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,19 +2405,14 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:37</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,12 +2427,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2442,7 +2442,7 @@
         <v>128341724</v>
       </c>
       <c r="B19" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341740</v>
+        <v>128341807</v>
       </c>
       <c r="B20" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574418</v>
+        <v>574435</v>
       </c>
       <c r="R20" t="n">
-        <v>7088654</v>
+        <v>7088661</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341807</v>
+        <v>128341740</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79702</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574435</v>
+        <v>574418</v>
       </c>
       <c r="R21" t="n">
-        <v>7088661</v>
+        <v>7088654</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2733,7 +2733,7 @@
         <v>128342521</v>
       </c>
       <c r="B22" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128342284</v>
       </c>
       <c r="B23" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>128342754</v>
       </c>
       <c r="B24" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>128342655</v>
       </c>
       <c r="B25" t="n">
-        <v>90161</v>
+        <v>90253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128341678</v>
+        <v>128342391</v>
       </c>
       <c r="B26" t="n">
-        <v>78699</v>
+        <v>91613</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574449</v>
+        <v>574371</v>
       </c>
       <c r="R26" t="n">
-        <v>7088616</v>
+        <v>7088729</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342434</v>
+        <v>128341678</v>
       </c>
       <c r="B27" t="n">
-        <v>92650</v>
+        <v>78749</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574373</v>
+        <v>574449</v>
       </c>
       <c r="R27" t="n">
-        <v>7088729</v>
+        <v>7088616</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342847</v>
+        <v>128342434</v>
       </c>
       <c r="B28" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574354</v>
+        <v>574373</v>
       </c>
       <c r="R28" t="n">
-        <v>7088881</v>
+        <v>7088729</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128341564</v>
+        <v>128342847</v>
       </c>
       <c r="B29" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574445</v>
+        <v>574354</v>
       </c>
       <c r="R29" t="n">
-        <v>7088593</v>
+        <v>7088881</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3506,10 +3506,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128342274</v>
+        <v>128341564</v>
       </c>
       <c r="B30" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574276</v>
+        <v>574445</v>
       </c>
       <c r="R30" t="n">
-        <v>7088904</v>
+        <v>7088593</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3574,19 +3574,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3601,44 +3591,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128342391</v>
+        <v>128342274</v>
       </c>
       <c r="B31" t="n">
-        <v>91521</v>
+        <v>92742</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,13 +3638,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574371</v>
+        <v>574276</v>
       </c>
       <c r="R31" t="n">
-        <v>7088729</v>
+        <v>7088904</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3681,9 +3671,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3698,12 +3698,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
         <v>128341686</v>
       </c>
       <c r="B32" t="n">
-        <v>90393</v>
+        <v>90485</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>128342782</v>
       </c>
       <c r="B33" t="n">
-        <v>92666</v>
+        <v>92758</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128342815</v>
       </c>
       <c r="B34" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4001,10 +4001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128342574</v>
+        <v>128342578</v>
       </c>
       <c r="B35" t="n">
-        <v>78699</v>
+        <v>79702</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,21 +4012,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574308</v>
+        <v>574309</v>
       </c>
       <c r="R35" t="n">
-        <v>7088789</v>
+        <v>7088787</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,7 +4101,7 @@
         <v>128341248</v>
       </c>
       <c r="B36" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>128341663</v>
       </c>
       <c r="B37" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>128342804</v>
       </c>
       <c r="B38" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>128342012</v>
       </c>
       <c r="B39" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>128341929</v>
       </c>
       <c r="B40" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128342578</v>
+        <v>128342574</v>
       </c>
       <c r="B41" t="n">
-        <v>79650</v>
+        <v>78749</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4604,21 +4604,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574309</v>
+        <v>574308</v>
       </c>
       <c r="R41" t="n">
-        <v>7088787</v>
+        <v>7088789</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4690,45 +4690,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128341959</v>
+        <v>128341748</v>
       </c>
       <c r="B42" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574292</v>
+        <v>574361</v>
       </c>
       <c r="R42" t="n">
-        <v>7088836</v>
+        <v>7088768</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4760,7 +4765,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4770,7 +4775,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4785,22 +4795,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128342904</v>
+        <v>128341959</v>
       </c>
       <c r="B43" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4832,13 +4842,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574370</v>
+        <v>574292</v>
       </c>
       <c r="R43" t="n">
-        <v>7088775</v>
+        <v>7088836</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4865,9 +4875,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4882,65 +4902,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128341748</v>
+        <v>128342904</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574361</v>
+        <v>574370</v>
       </c>
       <c r="R44" t="n">
-        <v>7088768</v>
+        <v>7088775</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4967,24 +4982,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,22 +4999,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128341581</v>
+        <v>128342466</v>
       </c>
       <c r="B45" t="n">
-        <v>78699</v>
+        <v>92758</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574445</v>
+        <v>574352</v>
       </c>
       <c r="R45" t="n">
-        <v>7088593</v>
+        <v>7088735</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128342466</v>
+        <v>128341946</v>
       </c>
       <c r="B46" t="n">
-        <v>92666</v>
+        <v>79702</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574352</v>
+        <v>574406</v>
       </c>
       <c r="R46" t="n">
-        <v>7088735</v>
+        <v>7088724</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128341946</v>
+        <v>128341581</v>
       </c>
       <c r="B47" t="n">
-        <v>79650</v>
+        <v>78749</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,21 +5216,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574406</v>
+        <v>574445</v>
       </c>
       <c r="R47" t="n">
-        <v>7088724</v>
+        <v>7088593</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5305,7 +5305,7 @@
         <v>128342664</v>
       </c>
       <c r="B48" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5419,32 +5419,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128342880</v>
+        <v>128342246</v>
       </c>
       <c r="B49" t="n">
-        <v>79650</v>
+        <v>92742</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574359</v>
+        <v>574397</v>
       </c>
       <c r="R49" t="n">
-        <v>7088849</v>
+        <v>7088752</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5516,32 +5516,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342246</v>
+        <v>128342358</v>
       </c>
       <c r="B50" t="n">
-        <v>92650</v>
+        <v>90485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574397</v>
+        <v>574372</v>
       </c>
       <c r="R50" t="n">
-        <v>7088752</v>
+        <v>7088765</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342358</v>
+        <v>128342880</v>
       </c>
       <c r="B51" t="n">
-        <v>90393</v>
+        <v>79702</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5624,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574372</v>
+        <v>574359</v>
       </c>
       <c r="R51" t="n">
-        <v>7088765</v>
+        <v>7088849</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5713,7 +5713,7 @@
         <v>128342898</v>
       </c>
       <c r="B52" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128342351</v>
+        <v>128342561</v>
       </c>
       <c r="B53" t="n">
-        <v>92654</v>
+        <v>79702</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574372</v>
+        <v>574312</v>
       </c>
       <c r="R53" t="n">
-        <v>7088765</v>
+        <v>7088790</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342561</v>
+        <v>128342438</v>
       </c>
       <c r="B54" t="n">
-        <v>79650</v>
+        <v>78840</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,21 +5915,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574312</v>
+        <v>574373</v>
       </c>
       <c r="R54" t="n">
-        <v>7088790</v>
+        <v>7088729</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,32 +6001,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341543</v>
+        <v>128342751</v>
       </c>
       <c r="B55" t="n">
-        <v>80171</v>
+        <v>78749</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R55" t="n">
-        <v>7088593</v>
+        <v>7088844</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342438</v>
+        <v>128342351</v>
       </c>
       <c r="B56" t="n">
-        <v>78790</v>
+        <v>92746</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574373</v>
+        <v>574372</v>
       </c>
       <c r="R56" t="n">
-        <v>7088729</v>
+        <v>7088765</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128341658</v>
+        <v>128341543</v>
       </c>
       <c r="B57" t="n">
-        <v>78699</v>
+        <v>80224</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
         <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088595</v>
+        <v>7088593</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,10 +6292,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128342751</v>
+        <v>128341658</v>
       </c>
       <c r="B58" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088844</v>
+        <v>7088595</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6389,32 +6389,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128341588</v>
+        <v>128342771</v>
       </c>
       <c r="B59" t="n">
-        <v>92650</v>
+        <v>90485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574445</v>
+        <v>574281</v>
       </c>
       <c r="R59" t="n">
-        <v>7088594</v>
+        <v>7088848</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128342667</v>
+        <v>128341588</v>
       </c>
       <c r="B60" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574390</v>
+        <v>574445</v>
       </c>
       <c r="R60" t="n">
-        <v>7088726</v>
+        <v>7088594</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6554,19 +6554,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6581,44 +6571,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342771</v>
+        <v>128342667</v>
       </c>
       <c r="B61" t="n">
-        <v>90393</v>
+        <v>92742</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6628,13 +6618,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574281</v>
+        <v>574390</v>
       </c>
       <c r="R61" t="n">
-        <v>7088848</v>
+        <v>7088726</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6661,9 +6651,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6678,12 +6678,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6693,7 +6693,7 @@
         <v>128342812</v>
       </c>
       <c r="B62" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>128341312</v>
       </c>
       <c r="B63" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>128341482</v>
       </c>
       <c r="B64" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>128342400</v>
       </c>
       <c r="B65" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>128341715</v>
       </c>
       <c r="B66" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>128342176</v>
       </c>
       <c r="B67" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128342397</v>
       </c>
       <c r="B69" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>128341878</v>
       </c>
       <c r="B70" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>128341109</v>
       </c>
       <c r="B71" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7754,32 +7754,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128341813</v>
+        <v>128342408</v>
       </c>
       <c r="B72" t="n">
-        <v>92650</v>
+        <v>79702</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7789,10 +7789,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574445</v>
+        <v>574379</v>
       </c>
       <c r="R72" t="n">
-        <v>7088668</v>
+        <v>7088725</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7851,32 +7851,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128342337</v>
+        <v>128341813</v>
       </c>
       <c r="B73" t="n">
-        <v>92644</v>
+        <v>92742</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7886,13 +7886,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574241</v>
+        <v>574445</v>
       </c>
       <c r="R73" t="n">
-        <v>7088939</v>
+        <v>7088668</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7919,19 +7919,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7946,22 +7936,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128341787</v>
+        <v>128342337</v>
       </c>
       <c r="B74" t="n">
-        <v>57673</v>
+        <v>92736</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7969,39 +7959,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574356</v>
+        <v>574241</v>
       </c>
       <c r="R74" t="n">
-        <v>7088756</v>
+        <v>7088939</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8033,7 +8018,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8043,7 +8028,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8070,10 +8055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128342408</v>
+        <v>128341787</v>
       </c>
       <c r="B75" t="n">
-        <v>79650</v>
+        <v>57685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8081,37 +8066,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574379</v>
+        <v>574356</v>
       </c>
       <c r="R75" t="n">
-        <v>7088725</v>
+        <v>7088756</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8138,9 +8128,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8155,12 +8155,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
         <v>128342186</v>
       </c>
       <c r="B76" t="n">
-        <v>92065</v>
+        <v>92157</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>128355111</v>
       </c>
       <c r="B77" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342277</v>
+        <v>128342785</v>
       </c>
       <c r="B2" t="n">
-        <v>78749</v>
+        <v>79702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574382</v>
+        <v>574275</v>
       </c>
       <c r="R2" t="n">
-        <v>7088759</v>
+        <v>7088862</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128342191</v>
+        <v>128341917</v>
       </c>
       <c r="B3" t="n">
-        <v>92736</v>
+        <v>78840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574279</v>
+        <v>574334</v>
       </c>
       <c r="R3" t="n">
-        <v>7088861</v>
+        <v>7088809</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342930</v>
+        <v>128342277</v>
       </c>
       <c r="B4" t="n">
-        <v>92758</v>
+        <v>78749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574400</v>
+        <v>574382</v>
       </c>
       <c r="R4" t="n">
-        <v>7088743</v>
+        <v>7088759</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342785</v>
+        <v>128342930</v>
       </c>
       <c r="B5" t="n">
-        <v>79702</v>
+        <v>92758</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574275</v>
+        <v>574400</v>
       </c>
       <c r="R5" t="n">
-        <v>7088862</v>
+        <v>7088743</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128341917</v>
+        <v>128342191</v>
       </c>
       <c r="B6" t="n">
-        <v>78840</v>
+        <v>92736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1084,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574334</v>
+        <v>574279</v>
       </c>
       <c r="R6" t="n">
-        <v>7088809</v>
+        <v>7088861</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,32 +1282,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128342525</v>
+        <v>128341140</v>
       </c>
       <c r="B8" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574323</v>
+        <v>574438</v>
       </c>
       <c r="R8" t="n">
-        <v>7088778</v>
+        <v>7088595</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,9 +1350,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,12 +1377,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1486,32 +1496,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341140</v>
+        <v>128342525</v>
       </c>
       <c r="B10" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,13 +1531,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574438</v>
+        <v>574323</v>
       </c>
       <c r="R10" t="n">
-        <v>7088595</v>
+        <v>7088778</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1554,19 +1564,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,12 +1581,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128341749</v>
+        <v>128342806</v>
       </c>
       <c r="B13" t="n">
-        <v>78840</v>
+        <v>80188</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574358</v>
+        <v>574452</v>
       </c>
       <c r="R13" t="n">
-        <v>7088744</v>
+        <v>7088593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128342806</v>
+        <v>128342361</v>
       </c>
       <c r="B14" t="n">
-        <v>80188</v>
+        <v>92736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574452</v>
+        <v>574230</v>
       </c>
       <c r="R14" t="n">
-        <v>7088593</v>
+        <v>7088918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342361</v>
+        <v>128341749</v>
       </c>
       <c r="B15" t="n">
-        <v>92736</v>
+        <v>78840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574230</v>
+        <v>574358</v>
       </c>
       <c r="R15" t="n">
-        <v>7088918</v>
+        <v>7088744</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,44 +2116,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128342757</v>
+        <v>128341807</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574291</v>
+        <v>574435</v>
       </c>
       <c r="R16" t="n">
-        <v>7088843</v>
+        <v>7088661</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,32 +2225,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341886</v>
+        <v>128341740</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574321</v>
+        <v>574418</v>
       </c>
       <c r="R17" t="n">
-        <v>7088769</v>
+        <v>7088654</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2293,19 +2293,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,62 +2310,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341646</v>
+        <v>128342757</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R18" t="n">
-        <v>7088594</v>
+        <v>7088843</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2408,11 +2393,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341724</v>
+        <v>128341886</v>
       </c>
       <c r="B19" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,13 +2454,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574435</v>
+        <v>574321</v>
       </c>
       <c r="R19" t="n">
-        <v>7088666</v>
+        <v>7088769</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2507,9 +2487,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2524,22 +2514,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341807</v>
+        <v>128341724</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2574,7 +2564,7 @@
         <v>574435</v>
       </c>
       <c r="R20" t="n">
-        <v>7088661</v>
+        <v>7088666</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341740</v>
+        <v>128341646</v>
       </c>
       <c r="B21" t="n">
-        <v>79702</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,34 +2634,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574418</v>
+        <v>574445</v>
       </c>
       <c r="R21" t="n">
-        <v>7088654</v>
+        <v>7088594</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2704,6 +2699,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342391</v>
+        <v>128342434</v>
       </c>
       <c r="B26" t="n">
-        <v>91613</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574371</v>
+        <v>574373</v>
       </c>
       <c r="R26" t="n">
         <v>7088729</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128341678</v>
+        <v>128342847</v>
       </c>
       <c r="B27" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574449</v>
+        <v>574354</v>
       </c>
       <c r="R27" t="n">
-        <v>7088616</v>
+        <v>7088881</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342434</v>
+        <v>128341564</v>
       </c>
       <c r="B28" t="n">
         <v>92742</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574373</v>
+        <v>574445</v>
       </c>
       <c r="R28" t="n">
-        <v>7088729</v>
+        <v>7088593</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342847</v>
+        <v>128342274</v>
       </c>
       <c r="B29" t="n">
         <v>92742</v>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574354</v>
+        <v>574276</v>
       </c>
       <c r="R29" t="n">
-        <v>7088881</v>
+        <v>7088904</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3477,9 +3477,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3494,44 +3504,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128341564</v>
+        <v>128341678</v>
       </c>
       <c r="B30" t="n">
-        <v>92742</v>
+        <v>78749</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3541,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574445</v>
+        <v>574449</v>
       </c>
       <c r="R30" t="n">
-        <v>7088593</v>
+        <v>7088616</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3603,32 +3613,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128342274</v>
+        <v>128342391</v>
       </c>
       <c r="B31" t="n">
-        <v>92742</v>
+        <v>91613</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3638,13 +3648,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574276</v>
+        <v>574371</v>
       </c>
       <c r="R31" t="n">
-        <v>7088904</v>
+        <v>7088729</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3671,19 +3681,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3698,12 +3698,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4001,32 +4001,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128342578</v>
+        <v>128341248</v>
       </c>
       <c r="B35" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,13 +4036,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574309</v>
+        <v>574418</v>
       </c>
       <c r="R35" t="n">
-        <v>7088787</v>
+        <v>7088658</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4069,9 +4069,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4086,19 +4096,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128341248</v>
+        <v>128341663</v>
       </c>
       <c r="B36" t="n">
         <v>92742</v>
@@ -4133,13 +4143,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574418</v>
+        <v>574444</v>
       </c>
       <c r="R36" t="n">
-        <v>7088658</v>
+        <v>7088610</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4166,19 +4176,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4193,19 +4193,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128341663</v>
+        <v>128342804</v>
       </c>
       <c r="B37" t="n">
         <v>92742</v>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574444</v>
+        <v>574290</v>
       </c>
       <c r="R37" t="n">
-        <v>7088610</v>
+        <v>7088881</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128342804</v>
+        <v>128342012</v>
       </c>
       <c r="B38" t="n">
         <v>92742</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574290</v>
+        <v>574415</v>
       </c>
       <c r="R38" t="n">
-        <v>7088881</v>
+        <v>7088716</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128342012</v>
+        <v>128341929</v>
       </c>
       <c r="B39" t="n">
         <v>92742</v>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574415</v>
+        <v>574406</v>
       </c>
       <c r="R39" t="n">
-        <v>7088716</v>
+        <v>7088725</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128341929</v>
+        <v>128342574</v>
       </c>
       <c r="B40" t="n">
-        <v>92742</v>
+        <v>78749</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574406</v>
+        <v>574308</v>
       </c>
       <c r="R40" t="n">
-        <v>7088725</v>
+        <v>7088789</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128342574</v>
+        <v>128342578</v>
       </c>
       <c r="B41" t="n">
-        <v>78749</v>
+        <v>79702</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4604,21 +4604,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574308</v>
+        <v>574309</v>
       </c>
       <c r="R41" t="n">
-        <v>7088789</v>
+        <v>7088787</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128342466</v>
+        <v>128341581</v>
       </c>
       <c r="B45" t="n">
-        <v>92758</v>
+        <v>78749</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574352</v>
+        <v>574445</v>
       </c>
       <c r="R45" t="n">
-        <v>7088735</v>
+        <v>7088593</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128341946</v>
+        <v>128342466</v>
       </c>
       <c r="B46" t="n">
-        <v>79702</v>
+        <v>92758</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574406</v>
+        <v>574352</v>
       </c>
       <c r="R46" t="n">
-        <v>7088724</v>
+        <v>7088735</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128341581</v>
+        <v>128341946</v>
       </c>
       <c r="B47" t="n">
-        <v>78749</v>
+        <v>79702</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,21 +5216,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574445</v>
+        <v>574406</v>
       </c>
       <c r="R47" t="n">
-        <v>7088593</v>
+        <v>7088724</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5419,32 +5419,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128342246</v>
+        <v>128342358</v>
       </c>
       <c r="B49" t="n">
-        <v>92742</v>
+        <v>90485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574397</v>
+        <v>574372</v>
       </c>
       <c r="R49" t="n">
-        <v>7088752</v>
+        <v>7088765</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5516,10 +5516,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342358</v>
+        <v>128342880</v>
       </c>
       <c r="B50" t="n">
-        <v>90485</v>
+        <v>79702</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5527,21 +5527,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574372</v>
+        <v>574359</v>
       </c>
       <c r="R50" t="n">
-        <v>7088765</v>
+        <v>7088849</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342880</v>
+        <v>128342246</v>
       </c>
       <c r="B51" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574359</v>
+        <v>574397</v>
       </c>
       <c r="R51" t="n">
-        <v>7088849</v>
+        <v>7088752</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128342561</v>
+        <v>128341658</v>
       </c>
       <c r="B53" t="n">
-        <v>79702</v>
+        <v>78749</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5818,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574312</v>
+        <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088790</v>
+        <v>7088595</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342438</v>
+        <v>128342751</v>
       </c>
       <c r="B54" t="n">
-        <v>78840</v>
+        <v>78749</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5915,21 +5915,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574373</v>
+        <v>574291</v>
       </c>
       <c r="R54" t="n">
-        <v>7088729</v>
+        <v>7088844</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342751</v>
+        <v>128342438</v>
       </c>
       <c r="B55" t="n">
-        <v>78749</v>
+        <v>78840</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574291</v>
+        <v>574373</v>
       </c>
       <c r="R55" t="n">
-        <v>7088844</v>
+        <v>7088729</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128341543</v>
+        <v>128342561</v>
       </c>
       <c r="B57" t="n">
-        <v>80224</v>
+        <v>79702</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R57" t="n">
-        <v>7088593</v>
+        <v>7088790</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,32 +6292,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341658</v>
+        <v>128341543</v>
       </c>
       <c r="B58" t="n">
-        <v>78749</v>
+        <v>80224</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6330,7 +6330,7 @@
         <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088595</v>
+        <v>7088593</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342400</v>
+        <v>128342176</v>
       </c>
       <c r="B65" t="n">
-        <v>92935</v>
+        <v>57685</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,37 +7016,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574381</v>
+        <v>574286</v>
       </c>
       <c r="R65" t="n">
-        <v>7088725</v>
+        <v>7088863</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,9 +7078,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7090,19 +7110,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128341715</v>
+        <v>128342400</v>
       </c>
       <c r="B66" t="n">
         <v>92935</v>
@@ -7137,10 +7157,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574446</v>
+        <v>574381</v>
       </c>
       <c r="R66" t="n">
-        <v>7088674</v>
+        <v>7088725</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7199,10 +7219,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128342176</v>
+        <v>128341715</v>
       </c>
       <c r="B67" t="n">
-        <v>57685</v>
+        <v>92935</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7210,42 +7230,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574286</v>
+        <v>574446</v>
       </c>
       <c r="R67" t="n">
-        <v>7088863</v>
+        <v>7088674</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7272,24 +7287,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7304,12 +7304,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7423,45 +7423,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128342397</v>
+        <v>128341109</v>
       </c>
       <c r="B69" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574294</v>
+        <v>574429</v>
       </c>
       <c r="R69" t="n">
-        <v>7088921</v>
+        <v>7088591</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,7 +7498,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7503,7 +7508,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7637,50 +7647,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128341109</v>
+        <v>128342397</v>
       </c>
       <c r="B71" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574429</v>
+        <v>574294</v>
       </c>
       <c r="R71" t="n">
-        <v>7088591</v>
+        <v>7088921</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7712,7 +7717,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7722,12 +7727,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342785</v>
+        <v>128342930</v>
       </c>
       <c r="B2" t="n">
-        <v>79702</v>
+        <v>92758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574275</v>
+        <v>574400</v>
       </c>
       <c r="R2" t="n">
-        <v>7088862</v>
+        <v>7088743</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128341917</v>
+        <v>128342191</v>
       </c>
       <c r="B3" t="n">
-        <v>78840</v>
+        <v>92736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574334</v>
+        <v>574279</v>
       </c>
       <c r="R3" t="n">
-        <v>7088809</v>
+        <v>7088861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342277</v>
+        <v>128342785</v>
       </c>
       <c r="B4" t="n">
-        <v>78749</v>
+        <v>79702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574382</v>
+        <v>574275</v>
       </c>
       <c r="R4" t="n">
-        <v>7088759</v>
+        <v>7088862</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342930</v>
+        <v>128341917</v>
       </c>
       <c r="B5" t="n">
-        <v>92758</v>
+        <v>78840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574400</v>
+        <v>574334</v>
       </c>
       <c r="R5" t="n">
-        <v>7088743</v>
+        <v>7088809</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,9 +1044,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,60 +1071,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128342191</v>
+        <v>128342842</v>
       </c>
       <c r="B6" t="n">
-        <v>92736</v>
+        <v>56876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574279</v>
+        <v>574354</v>
       </c>
       <c r="R6" t="n">
-        <v>7088861</v>
+        <v>7088880</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1141,19 +1156,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,62 +1173,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342842</v>
+        <v>128342277</v>
       </c>
       <c r="B7" t="n">
-        <v>56876</v>
+        <v>78749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574354</v>
+        <v>574382</v>
       </c>
       <c r="R7" t="n">
-        <v>7088880</v>
+        <v>7088759</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341860</v>
+        <v>128342525</v>
       </c>
       <c r="B9" t="n">
-        <v>78840</v>
+        <v>79702</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,13 +1424,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574328</v>
+        <v>574323</v>
       </c>
       <c r="R9" t="n">
-        <v>7088763</v>
+        <v>7088778</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1457,19 +1457,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1484,22 +1474,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128342525</v>
+        <v>128341860</v>
       </c>
       <c r="B10" t="n">
-        <v>79702</v>
+        <v>78840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1497,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,13 +1521,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574323</v>
+        <v>574328</v>
       </c>
       <c r="R10" t="n">
-        <v>7088778</v>
+        <v>7088763</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1564,9 +1554,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,12 +1581,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342299</v>
+        <v>128342361</v>
       </c>
       <c r="B12" t="n">
-        <v>92758</v>
+        <v>92736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574373</v>
+        <v>574230</v>
       </c>
       <c r="R12" t="n">
-        <v>7088753</v>
+        <v>7088918</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1778,9 +1778,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128342806</v>
+        <v>128341749</v>
       </c>
       <c r="B13" t="n">
-        <v>80188</v>
+        <v>78840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574452</v>
+        <v>574358</v>
       </c>
       <c r="R13" t="n">
-        <v>7088593</v>
+        <v>7088744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1887,7 +1897,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128342361</v>
+        <v>128342806</v>
       </c>
       <c r="B14" t="n">
-        <v>92736</v>
+        <v>80188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574230</v>
+        <v>574452</v>
       </c>
       <c r="R14" t="n">
-        <v>7088918</v>
+        <v>7088593</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1994,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1994,7 +2004,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128341749</v>
+        <v>128342299</v>
       </c>
       <c r="B15" t="n">
-        <v>78840</v>
+        <v>92758</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2066,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574358</v>
+        <v>574373</v>
       </c>
       <c r="R15" t="n">
-        <v>7088744</v>
+        <v>7088753</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2089,19 +2099,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:26</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,44 +2116,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341807</v>
+        <v>128342757</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574435</v>
+        <v>574291</v>
       </c>
       <c r="R16" t="n">
-        <v>7088661</v>
+        <v>7088843</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341740</v>
+        <v>128341724</v>
       </c>
       <c r="B17" t="n">
         <v>79702</v>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574418</v>
+        <v>574435</v>
       </c>
       <c r="R17" t="n">
-        <v>7088654</v>
+        <v>7088666</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,32 +2322,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128342757</v>
+        <v>128341740</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574291</v>
+        <v>574418</v>
       </c>
       <c r="R18" t="n">
-        <v>7088843</v>
+        <v>7088654</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341724</v>
+        <v>128341807</v>
       </c>
       <c r="B20" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2537,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2564,7 +2564,7 @@
         <v>574435</v>
       </c>
       <c r="R20" t="n">
-        <v>7088666</v>
+        <v>7088661</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342434</v>
+        <v>128342391</v>
       </c>
       <c r="B26" t="n">
-        <v>92742</v>
+        <v>91613</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574373</v>
+        <v>574371</v>
       </c>
       <c r="R26" t="n">
         <v>7088729</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342847</v>
+        <v>128341678</v>
       </c>
       <c r="B27" t="n">
-        <v>92742</v>
+        <v>78749</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574354</v>
+        <v>574449</v>
       </c>
       <c r="R27" t="n">
-        <v>7088881</v>
+        <v>7088616</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128341564</v>
+        <v>128342274</v>
       </c>
       <c r="B28" t="n">
         <v>92742</v>
@@ -3347,13 +3347,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574445</v>
+        <v>574276</v>
       </c>
       <c r="R28" t="n">
-        <v>7088593</v>
+        <v>7088904</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3380,9 +3380,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3397,19 +3407,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342274</v>
+        <v>128342434</v>
       </c>
       <c r="B29" t="n">
         <v>92742</v>
@@ -3444,13 +3454,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574276</v>
+        <v>574373</v>
       </c>
       <c r="R29" t="n">
-        <v>7088904</v>
+        <v>7088730</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3477,19 +3487,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3504,44 +3504,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128341678</v>
+        <v>128342847</v>
       </c>
       <c r="B30" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574449</v>
+        <v>574354</v>
       </c>
       <c r="R30" t="n">
-        <v>7088616</v>
+        <v>7088881</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3613,32 +3613,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128342391</v>
+        <v>128341564</v>
       </c>
       <c r="B31" t="n">
-        <v>91613</v>
+        <v>92742</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574371</v>
+        <v>574445</v>
       </c>
       <c r="R31" t="n">
-        <v>7088729</v>
+        <v>7088593</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4108,32 +4108,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128341663</v>
+        <v>128342574</v>
       </c>
       <c r="B36" t="n">
-        <v>92742</v>
+        <v>78749</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574444</v>
+        <v>574308</v>
       </c>
       <c r="R36" t="n">
-        <v>7088610</v>
+        <v>7088789</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4205,32 +4205,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128342804</v>
+        <v>128342578</v>
       </c>
       <c r="B37" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4240,10 +4240,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574290</v>
+        <v>574309</v>
       </c>
       <c r="R37" t="n">
-        <v>7088881</v>
+        <v>7088787</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128342012</v>
+        <v>128342804</v>
       </c>
       <c r="B38" t="n">
         <v>92742</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574415</v>
+        <v>574290</v>
       </c>
       <c r="R38" t="n">
-        <v>7088716</v>
+        <v>7088881</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128341929</v>
+        <v>128342012</v>
       </c>
       <c r="B39" t="n">
         <v>92742</v>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574406</v>
+        <v>574415</v>
       </c>
       <c r="R39" t="n">
-        <v>7088725</v>
+        <v>7088716</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128342574</v>
+        <v>128341929</v>
       </c>
       <c r="B40" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574308</v>
+        <v>574406</v>
       </c>
       <c r="R40" t="n">
-        <v>7088789</v>
+        <v>7088725</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128342578</v>
+        <v>128341663</v>
       </c>
       <c r="B41" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574309</v>
+        <v>574444</v>
       </c>
       <c r="R41" t="n">
-        <v>7088787</v>
+        <v>7088610</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4690,50 +4690,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128341748</v>
+        <v>128341959</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574361</v>
+        <v>574292</v>
       </c>
       <c r="R42" t="n">
-        <v>7088768</v>
+        <v>7088836</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,7 +4760,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4775,12 +4770,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4795,19 +4785,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341959</v>
+        <v>128342904</v>
       </c>
       <c r="B43" t="n">
         <v>92742</v>
@@ -4842,13 +4832,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574292</v>
+        <v>574370</v>
       </c>
       <c r="R43" t="n">
-        <v>7088836</v>
+        <v>7088775</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4875,19 +4865,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4902,60 +4882,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128342904</v>
+        <v>128341748</v>
       </c>
       <c r="B44" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574370</v>
+        <v>574361</v>
       </c>
       <c r="R44" t="n">
-        <v>7088775</v>
+        <v>7088768</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4982,9 +4967,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,22 +4999,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128341581</v>
+        <v>128342466</v>
       </c>
       <c r="B45" t="n">
-        <v>78749</v>
+        <v>92758</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574445</v>
+        <v>574352</v>
       </c>
       <c r="R45" t="n">
-        <v>7088593</v>
+        <v>7088735</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128342466</v>
+        <v>128341581</v>
       </c>
       <c r="B46" t="n">
-        <v>92758</v>
+        <v>78749</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574352</v>
+        <v>574445</v>
       </c>
       <c r="R46" t="n">
-        <v>7088735</v>
+        <v>7088593</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128341946</v>
+        <v>128342664</v>
       </c>
       <c r="B47" t="n">
-        <v>79702</v>
+        <v>57685</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,37 +5216,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574406</v>
+        <v>574390</v>
       </c>
       <c r="R47" t="n">
-        <v>7088724</v>
+        <v>7088731</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5273,9 +5278,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5290,22 +5310,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128342664</v>
+        <v>128341946</v>
       </c>
       <c r="B48" t="n">
-        <v>57685</v>
+        <v>79702</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5313,42 +5333,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574390</v>
+        <v>574406</v>
       </c>
       <c r="R48" t="n">
-        <v>7088731</v>
+        <v>7088724</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5375,24 +5390,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5407,22 +5407,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128342358</v>
+        <v>128342880</v>
       </c>
       <c r="B49" t="n">
-        <v>90485</v>
+        <v>79702</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5430,21 +5430,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574372</v>
+        <v>574359</v>
       </c>
       <c r="R49" t="n">
-        <v>7088765</v>
+        <v>7088849</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5516,32 +5516,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342880</v>
+        <v>128342898</v>
       </c>
       <c r="B50" t="n">
-        <v>79702</v>
+        <v>91417</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574359</v>
+        <v>574369</v>
       </c>
       <c r="R50" t="n">
-        <v>7088849</v>
+        <v>7088771</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342246</v>
+        <v>128342358</v>
       </c>
       <c r="B51" t="n">
-        <v>92742</v>
+        <v>90485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574397</v>
+        <v>574372</v>
       </c>
       <c r="R51" t="n">
-        <v>7088752</v>
+        <v>7088765</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128342898</v>
+        <v>128342246</v>
       </c>
       <c r="B52" t="n">
-        <v>91417</v>
+        <v>92742</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574369</v>
+        <v>574397</v>
       </c>
       <c r="R52" t="n">
-        <v>7088771</v>
+        <v>7088752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341658</v>
+        <v>128342561</v>
       </c>
       <c r="B53" t="n">
-        <v>78749</v>
+        <v>79702</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5818,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R53" t="n">
-        <v>7088595</v>
+        <v>7088790</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342751</v>
+        <v>128341543</v>
       </c>
       <c r="B54" t="n">
-        <v>78749</v>
+        <v>80224</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088844</v>
+        <v>7088593</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6039,7 +6039,7 @@
         <v>574373</v>
       </c>
       <c r="R55" t="n">
-        <v>7088729</v>
+        <v>7088730</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342351</v>
+        <v>128341658</v>
       </c>
       <c r="B56" t="n">
-        <v>92746</v>
+        <v>78749</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574372</v>
+        <v>574445</v>
       </c>
       <c r="R56" t="n">
-        <v>7088765</v>
+        <v>7088595</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342561</v>
+        <v>128342751</v>
       </c>
       <c r="B57" t="n">
-        <v>79702</v>
+        <v>78749</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6206,21 +6206,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574312</v>
+        <v>574291</v>
       </c>
       <c r="R57" t="n">
-        <v>7088790</v>
+        <v>7088844</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,32 +6292,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341543</v>
+        <v>128342351</v>
       </c>
       <c r="B58" t="n">
-        <v>80224</v>
+        <v>92746</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>4365</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574445</v>
+        <v>574372</v>
       </c>
       <c r="R58" t="n">
-        <v>7088593</v>
+        <v>7088765</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6486,7 +6486,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128341588</v>
+        <v>128342667</v>
       </c>
       <c r="B60" t="n">
         <v>92742</v>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574445</v>
+        <v>574390</v>
       </c>
       <c r="R60" t="n">
-        <v>7088594</v>
+        <v>7088726</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6554,9 +6554,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6571,19 +6581,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342667</v>
+        <v>128341588</v>
       </c>
       <c r="B61" t="n">
         <v>92742</v>
@@ -6618,13 +6628,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574390</v>
+        <v>574445</v>
       </c>
       <c r="R61" t="n">
-        <v>7088726</v>
+        <v>7088594</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6651,19 +6661,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6678,12 +6678,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7540,32 +7540,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128341878</v>
+        <v>128342397</v>
       </c>
       <c r="B70" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574329</v>
+        <v>574294</v>
       </c>
       <c r="R70" t="n">
-        <v>7088770</v>
+        <v>7088921</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7635,44 +7635,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128342397</v>
+        <v>128341878</v>
       </c>
       <c r="B71" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574294</v>
+        <v>574329</v>
       </c>
       <c r="R71" t="n">
-        <v>7088921</v>
+        <v>7088770</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7742,12 +7742,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342930</v>
+        <v>128342277</v>
       </c>
       <c r="B2" t="n">
-        <v>92758</v>
+        <v>78749</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574400</v>
+        <v>574382</v>
       </c>
       <c r="R2" t="n">
-        <v>7088743</v>
+        <v>7088759</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128342191</v>
+        <v>128342930</v>
       </c>
       <c r="B3" t="n">
-        <v>92736</v>
+        <v>92758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574279</v>
+        <v>574400</v>
       </c>
       <c r="R3" t="n">
-        <v>7088861</v>
+        <v>7088743</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,19 +840,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342785</v>
+        <v>128342191</v>
       </c>
       <c r="B4" t="n">
-        <v>79702</v>
+        <v>92736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574275</v>
+        <v>574279</v>
       </c>
       <c r="R4" t="n">
-        <v>7088862</v>
+        <v>7088861</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,9 +937,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128341917</v>
+        <v>128342785</v>
       </c>
       <c r="B5" t="n">
-        <v>78840</v>
+        <v>79702</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574334</v>
+        <v>574275</v>
       </c>
       <c r="R5" t="n">
-        <v>7088809</v>
+        <v>7088862</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,19 +1044,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1061,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128342842</v>
+        <v>128341917</v>
       </c>
       <c r="B6" t="n">
-        <v>56876</v>
+        <v>78840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574354</v>
+        <v>574334</v>
       </c>
       <c r="R6" t="n">
-        <v>7088880</v>
+        <v>7088809</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,9 +1141,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,57 +1168,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342277</v>
+        <v>128342842</v>
       </c>
       <c r="B7" t="n">
-        <v>78749</v>
+        <v>56876</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574382</v>
+        <v>574354</v>
       </c>
       <c r="R7" t="n">
-        <v>7088759</v>
+        <v>7088880</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -2924,32 +2924,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342754</v>
+        <v>128342655</v>
       </c>
       <c r="B24" t="n">
-        <v>79702</v>
+        <v>90253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574291</v>
+        <v>574282</v>
       </c>
       <c r="R24" t="n">
-        <v>7088845</v>
+        <v>7088807</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342655</v>
+        <v>128342754</v>
       </c>
       <c r="B25" t="n">
-        <v>90253</v>
+        <v>79702</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574282</v>
+        <v>574291</v>
       </c>
       <c r="R25" t="n">
-        <v>7088807</v>
+        <v>7088845</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128341248</v>
+        <v>128342804</v>
       </c>
       <c r="B35" t="n">
         <v>92742</v>
@@ -4036,13 +4036,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574418</v>
+        <v>574290</v>
       </c>
       <c r="R35" t="n">
-        <v>7088658</v>
+        <v>7088881</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4069,19 +4069,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4096,44 +4086,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128342574</v>
+        <v>128342012</v>
       </c>
       <c r="B36" t="n">
-        <v>78749</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4143,10 +4133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574308</v>
+        <v>574415</v>
       </c>
       <c r="R36" t="n">
-        <v>7088789</v>
+        <v>7088716</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4205,32 +4195,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128342578</v>
+        <v>128341929</v>
       </c>
       <c r="B37" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4240,10 +4230,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574309</v>
+        <v>574406</v>
       </c>
       <c r="R37" t="n">
-        <v>7088787</v>
+        <v>7088725</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4302,7 +4292,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128342804</v>
+        <v>128341248</v>
       </c>
       <c r="B38" t="n">
         <v>92742</v>
@@ -4337,13 +4327,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574290</v>
+        <v>574418</v>
       </c>
       <c r="R38" t="n">
-        <v>7088881</v>
+        <v>7088658</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4370,9 +4360,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4387,44 +4387,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128342012</v>
+        <v>128342574</v>
       </c>
       <c r="B39" t="n">
-        <v>92742</v>
+        <v>78749</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574415</v>
+        <v>574308</v>
       </c>
       <c r="R39" t="n">
-        <v>7088716</v>
+        <v>7088789</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128341929</v>
+        <v>128342578</v>
       </c>
       <c r="B40" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574406</v>
+        <v>574309</v>
       </c>
       <c r="R40" t="n">
-        <v>7088725</v>
+        <v>7088787</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4690,45 +4690,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128341959</v>
+        <v>128341748</v>
       </c>
       <c r="B42" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574292</v>
+        <v>574361</v>
       </c>
       <c r="R42" t="n">
-        <v>7088836</v>
+        <v>7088768</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4760,7 +4765,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4770,7 +4775,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4785,19 +4795,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128342904</v>
+        <v>128341959</v>
       </c>
       <c r="B43" t="n">
         <v>92742</v>
@@ -4832,13 +4842,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574370</v>
+        <v>574292</v>
       </c>
       <c r="R43" t="n">
-        <v>7088775</v>
+        <v>7088836</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4865,9 +4875,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4882,65 +4902,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128341748</v>
+        <v>128342904</v>
       </c>
       <c r="B44" t="n">
-        <v>57685</v>
+        <v>92742</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574361</v>
+        <v>574370</v>
       </c>
       <c r="R44" t="n">
-        <v>7088768</v>
+        <v>7088775</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4967,24 +4982,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,12 +4999,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -7851,48 +7851,53 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128341813</v>
+        <v>128341787</v>
       </c>
       <c r="B73" t="n">
-        <v>92742</v>
+        <v>57685</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574445</v>
+        <v>574356</v>
       </c>
       <c r="R73" t="n">
-        <v>7088668</v>
+        <v>7088756</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7919,9 +7924,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7936,44 +7951,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128342337</v>
+        <v>128341813</v>
       </c>
       <c r="B74" t="n">
-        <v>92736</v>
+        <v>92742</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7983,13 +7998,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574241</v>
+        <v>574445</v>
       </c>
       <c r="R74" t="n">
-        <v>7088939</v>
+        <v>7088668</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8016,19 +8031,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8043,22 +8048,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128341787</v>
+        <v>128342337</v>
       </c>
       <c r="B75" t="n">
-        <v>57685</v>
+        <v>92736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8066,39 +8071,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574356</v>
+        <v>574241</v>
       </c>
       <c r="R75" t="n">
-        <v>7088756</v>
+        <v>7088939</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128342277</v>
       </c>
       <c r="B2" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128342930</v>
+        <v>128342842</v>
       </c>
       <c r="B3" t="n">
-        <v>92758</v>
+        <v>56880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574400</v>
+        <v>574354</v>
       </c>
       <c r="R3" t="n">
-        <v>7088743</v>
+        <v>7088880</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +877,7 @@
         <v>128342191</v>
       </c>
       <c r="B4" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +984,7 @@
         <v>128342785</v>
       </c>
       <c r="B5" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1081,7 @@
         <v>128341917</v>
       </c>
       <c r="B6" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,50 +1185,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342842</v>
+        <v>128342930</v>
       </c>
       <c r="B7" t="n">
-        <v>56876</v>
+        <v>92770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574354</v>
+        <v>574400</v>
       </c>
       <c r="R7" t="n">
-        <v>7088880</v>
+        <v>7088743</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,45 +1282,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341140</v>
+        <v>128341697</v>
       </c>
       <c r="B8" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574438</v>
+        <v>574383</v>
       </c>
       <c r="R8" t="n">
-        <v>7088595</v>
+        <v>7088749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1362,7 +1367,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,32 +1399,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128342525</v>
+        <v>128341140</v>
       </c>
       <c r="B9" t="n">
-        <v>79702</v>
+        <v>92754</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574323</v>
+        <v>574438</v>
       </c>
       <c r="R9" t="n">
-        <v>7088778</v>
+        <v>7088595</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1457,9 +1467,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341860</v>
+        <v>128342525</v>
       </c>
       <c r="B10" t="n">
-        <v>78840</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,13 +1541,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574328</v>
+        <v>574323</v>
       </c>
       <c r="R10" t="n">
-        <v>7088763</v>
+        <v>7088778</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1554,19 +1574,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,22 +1591,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341697</v>
+        <v>128341860</v>
       </c>
       <c r="B11" t="n">
-        <v>57685</v>
+        <v>78844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,39 +1614,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574383</v>
+        <v>574328</v>
       </c>
       <c r="R11" t="n">
-        <v>7088749</v>
+        <v>7088763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,12 +1698,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
         <v>128342361</v>
       </c>
       <c r="B12" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>128341749</v>
       </c>
       <c r="B13" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>128342806</v>
       </c>
       <c r="B14" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         <v>128342299</v>
       </c>
       <c r="B15" t="n">
-        <v>92758</v>
+        <v>92770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,45 +2128,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128342757</v>
+        <v>128341646</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R16" t="n">
-        <v>7088843</v>
+        <v>7088594</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2199,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,32 +2235,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341724</v>
+        <v>128342757</v>
       </c>
       <c r="B17" t="n">
-        <v>79702</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574435</v>
+        <v>574291</v>
       </c>
       <c r="R17" t="n">
-        <v>7088666</v>
+        <v>7088843</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,32 +2332,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341740</v>
+        <v>128341886</v>
       </c>
       <c r="B18" t="n">
-        <v>79702</v>
+        <v>92754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574418</v>
+        <v>574321</v>
       </c>
       <c r="R18" t="n">
-        <v>7088654</v>
+        <v>7088769</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2390,9 +2400,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2407,44 +2427,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341886</v>
+        <v>128341724</v>
       </c>
       <c r="B19" t="n">
-        <v>92742</v>
+        <v>79706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,13 +2474,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574321</v>
+        <v>574435</v>
       </c>
       <c r="R19" t="n">
-        <v>7088769</v>
+        <v>7088666</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2487,19 +2507,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,12 +2524,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2529,7 +2539,7 @@
         <v>128341807</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2623,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341646</v>
+        <v>128341740</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>79706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,39 +2644,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574445</v>
+        <v>574418</v>
       </c>
       <c r="R21" t="n">
-        <v>7088594</v>
+        <v>7088654</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2699,11 +2704,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,7 +2733,7 @@
         <v>128342521</v>
       </c>
       <c r="B22" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128342284</v>
       </c>
       <c r="B23" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,32 +2924,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342655</v>
+        <v>128342754</v>
       </c>
       <c r="B24" t="n">
-        <v>90253</v>
+        <v>79706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574282</v>
+        <v>574291</v>
       </c>
       <c r="R24" t="n">
-        <v>7088807</v>
+        <v>7088845</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342754</v>
+        <v>128342655</v>
       </c>
       <c r="B25" t="n">
-        <v>79702</v>
+        <v>90265</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574291</v>
+        <v>574282</v>
       </c>
       <c r="R25" t="n">
-        <v>7088845</v>
+        <v>7088807</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342391</v>
+        <v>128342434</v>
       </c>
       <c r="B26" t="n">
-        <v>91613</v>
+        <v>92754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574371</v>
+        <v>574373</v>
       </c>
       <c r="R26" t="n">
         <v>7088729</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128341678</v>
+        <v>128342847</v>
       </c>
       <c r="B27" t="n">
-        <v>78749</v>
+        <v>92754</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574449</v>
+        <v>574354</v>
       </c>
       <c r="R27" t="n">
-        <v>7088616</v>
+        <v>7088881</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342274</v>
+        <v>128341564</v>
       </c>
       <c r="B28" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,13 +3347,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574276</v>
+        <v>574445</v>
       </c>
       <c r="R28" t="n">
-        <v>7088904</v>
+        <v>7088593</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3380,19 +3380,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3407,22 +3397,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342434</v>
+        <v>128342274</v>
       </c>
       <c r="B29" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574373</v>
+        <v>574276</v>
       </c>
       <c r="R29" t="n">
-        <v>7088730</v>
+        <v>7088904</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3487,9 +3477,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3504,44 +3504,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128342847</v>
+        <v>128341678</v>
       </c>
       <c r="B30" t="n">
-        <v>92742</v>
+        <v>78753</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574354</v>
+        <v>574449</v>
       </c>
       <c r="R30" t="n">
-        <v>7088881</v>
+        <v>7088616</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3613,32 +3613,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128341564</v>
+        <v>128342391</v>
       </c>
       <c r="B31" t="n">
-        <v>92742</v>
+        <v>91625</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574445</v>
+        <v>574371</v>
       </c>
       <c r="R31" t="n">
-        <v>7088593</v>
+        <v>7088729</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3710,32 +3710,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128341686</v>
+        <v>128342815</v>
       </c>
       <c r="B32" t="n">
-        <v>90485</v>
+        <v>92754</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R32" t="n">
-        <v>7088630</v>
+        <v>7088883</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128342782</v>
+        <v>128341686</v>
       </c>
       <c r="B33" t="n">
-        <v>92758</v>
+        <v>90497</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,21 +3818,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574280</v>
+        <v>574445</v>
       </c>
       <c r="R33" t="n">
-        <v>7088852</v>
+        <v>7088630</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3904,32 +3904,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128342815</v>
+        <v>128342782</v>
       </c>
       <c r="B34" t="n">
-        <v>92742</v>
+        <v>92770</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574292</v>
+        <v>574280</v>
       </c>
       <c r="R34" t="n">
-        <v>7088883</v>
+        <v>7088852</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4001,32 +4001,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128342804</v>
+        <v>128342578</v>
       </c>
       <c r="B35" t="n">
-        <v>92742</v>
+        <v>79706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574290</v>
+        <v>574309</v>
       </c>
       <c r="R35" t="n">
-        <v>7088881</v>
+        <v>7088787</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128342012</v>
+        <v>128341248</v>
       </c>
       <c r="B36" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574415</v>
+        <v>574418</v>
       </c>
       <c r="R36" t="n">
-        <v>7088716</v>
+        <v>7088658</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4166,9 +4166,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,22 +4193,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128341929</v>
+        <v>128341663</v>
       </c>
       <c r="B37" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4230,10 +4240,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574406</v>
+        <v>574444</v>
       </c>
       <c r="R37" t="n">
-        <v>7088725</v>
+        <v>7088610</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4292,10 +4302,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128341248</v>
+        <v>128342804</v>
       </c>
       <c r="B38" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4327,13 +4337,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574418</v>
+        <v>574290</v>
       </c>
       <c r="R38" t="n">
-        <v>7088658</v>
+        <v>7088881</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4360,19 +4370,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4387,44 +4387,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128342574</v>
+        <v>128342012</v>
       </c>
       <c r="B39" t="n">
-        <v>78749</v>
+        <v>92754</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574308</v>
+        <v>574415</v>
       </c>
       <c r="R39" t="n">
-        <v>7088789</v>
+        <v>7088716</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128342578</v>
+        <v>128341929</v>
       </c>
       <c r="B40" t="n">
-        <v>79702</v>
+        <v>92754</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574309</v>
+        <v>574406</v>
       </c>
       <c r="R40" t="n">
-        <v>7088787</v>
+        <v>7088725</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128341663</v>
+        <v>128342574</v>
       </c>
       <c r="B41" t="n">
-        <v>92742</v>
+        <v>78753</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574444</v>
+        <v>574308</v>
       </c>
       <c r="R41" t="n">
-        <v>7088610</v>
+        <v>7088789</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4693,7 +4693,7 @@
         <v>128341748</v>
       </c>
       <c r="B42" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>128341959</v>
       </c>
       <c r="B43" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>128342904</v>
       </c>
       <c r="B44" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128342466</v>
+        <v>128342664</v>
       </c>
       <c r="B45" t="n">
-        <v>92758</v>
+        <v>57689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,37 +5022,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574352</v>
+        <v>574390</v>
       </c>
       <c r="R45" t="n">
-        <v>7088735</v>
+        <v>7088731</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5079,9 +5084,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5096,22 +5116,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128341581</v>
+        <v>128341946</v>
       </c>
       <c r="B46" t="n">
-        <v>78749</v>
+        <v>79706</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5139,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5163,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574445</v>
+        <v>574406</v>
       </c>
       <c r="R46" t="n">
-        <v>7088593</v>
+        <v>7088724</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5205,10 +5225,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128342664</v>
+        <v>128341581</v>
       </c>
       <c r="B47" t="n">
-        <v>57685</v>
+        <v>78753</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,42 +5236,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574390</v>
+        <v>574445</v>
       </c>
       <c r="R47" t="n">
-        <v>7088731</v>
+        <v>7088593</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5278,24 +5293,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5310,22 +5310,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128341946</v>
+        <v>128342466</v>
       </c>
       <c r="B48" t="n">
-        <v>79702</v>
+        <v>92770</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5333,21 +5333,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574406</v>
+        <v>574352</v>
       </c>
       <c r="R48" t="n">
-        <v>7088724</v>
+        <v>7088735</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5422,7 +5422,7 @@
         <v>128342880</v>
       </c>
       <c r="B49" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,32 +5516,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342898</v>
+        <v>128342358</v>
       </c>
       <c r="B50" t="n">
-        <v>91417</v>
+        <v>90497</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574369</v>
+        <v>574372</v>
       </c>
       <c r="R50" t="n">
-        <v>7088771</v>
+        <v>7088765</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342358</v>
+        <v>128342246</v>
       </c>
       <c r="B51" t="n">
-        <v>90485</v>
+        <v>92754</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574372</v>
+        <v>574397</v>
       </c>
       <c r="R51" t="n">
-        <v>7088765</v>
+        <v>7088752</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128342246</v>
+        <v>128342898</v>
       </c>
       <c r="B52" t="n">
-        <v>92742</v>
+        <v>91429</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574397</v>
+        <v>574369</v>
       </c>
       <c r="R52" t="n">
-        <v>7088752</v>
+        <v>7088771</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5810,7 +5810,7 @@
         <v>128342561</v>
       </c>
       <c r="B53" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341543</v>
+        <v>128342438</v>
       </c>
       <c r="B54" t="n">
-        <v>80224</v>
+        <v>78844</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574445</v>
+        <v>574373</v>
       </c>
       <c r="R54" t="n">
-        <v>7088593</v>
+        <v>7088729</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342438</v>
+        <v>128341658</v>
       </c>
       <c r="B55" t="n">
-        <v>78840</v>
+        <v>78753</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574373</v>
+        <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088730</v>
+        <v>7088595</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128341658</v>
+        <v>128342751</v>
       </c>
       <c r="B56" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R56" t="n">
-        <v>7088595</v>
+        <v>7088844</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342751</v>
+        <v>128342351</v>
       </c>
       <c r="B57" t="n">
-        <v>78749</v>
+        <v>92758</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574291</v>
+        <v>574372</v>
       </c>
       <c r="R57" t="n">
-        <v>7088844</v>
+        <v>7088765</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,32 +6292,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128342351</v>
+        <v>128341543</v>
       </c>
       <c r="B58" t="n">
-        <v>92746</v>
+        <v>80228</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4365</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574372</v>
+        <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088765</v>
+        <v>7088593</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6389,32 +6389,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128342771</v>
+        <v>128341588</v>
       </c>
       <c r="B59" t="n">
-        <v>90485</v>
+        <v>92754</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574281</v>
+        <v>574445</v>
       </c>
       <c r="R59" t="n">
-        <v>7088848</v>
+        <v>7088594</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6489,7 +6489,7 @@
         <v>128342667</v>
       </c>
       <c r="B60" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6593,10 +6593,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128341588</v>
+        <v>128342812</v>
       </c>
       <c r="B61" t="n">
-        <v>92742</v>
+        <v>80221</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6604,21 +6604,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R61" t="n">
-        <v>7088594</v>
+        <v>7088883</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6690,32 +6690,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128342812</v>
+        <v>128342771</v>
       </c>
       <c r="B62" t="n">
-        <v>80217</v>
+        <v>90497</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574292</v>
+        <v>574281</v>
       </c>
       <c r="R62" t="n">
-        <v>7088883</v>
+        <v>7088848</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6787,10 +6787,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128341312</v>
+        <v>128341482</v>
       </c>
       <c r="B63" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6816,16 +6816,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574418</v>
+        <v>574408</v>
       </c>
       <c r="R63" t="n">
-        <v>7088693</v>
+        <v>7088736</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6857,7 +6860,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6867,7 +6870,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6876,6 +6879,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6894,10 +6898,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128341482</v>
+        <v>128341312</v>
       </c>
       <c r="B64" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,19 +6927,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574408</v>
+        <v>574418</v>
       </c>
       <c r="R64" t="n">
-        <v>7088736</v>
+        <v>7088693</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6967,7 +6968,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -6977,7 +6978,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6986,7 +6987,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>128342176</v>
       </c>
       <c r="B65" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>128342400</v>
       </c>
       <c r="B66" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>128341715</v>
       </c>
       <c r="B67" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128341109</v>
       </c>
       <c r="B69" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>128342397</v>
       </c>
       <c r="B70" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>128341878</v>
       </c>
       <c r="B71" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7754,10 +7754,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128342408</v>
+        <v>128341787</v>
       </c>
       <c r="B72" t="n">
-        <v>79702</v>
+        <v>57689</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7765,37 +7765,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574379</v>
+        <v>574356</v>
       </c>
       <c r="R72" t="n">
-        <v>7088725</v>
+        <v>7088756</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7822,9 +7827,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7839,65 +7854,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128341787</v>
+        <v>128341813</v>
       </c>
       <c r="B73" t="n">
-        <v>57685</v>
+        <v>92754</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574356</v>
+        <v>574445</v>
       </c>
       <c r="R73" t="n">
-        <v>7088756</v>
+        <v>7088668</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7924,19 +7934,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7951,44 +7951,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128341813</v>
+        <v>128342337</v>
       </c>
       <c r="B74" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7998,13 +7998,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574445</v>
+        <v>574241</v>
       </c>
       <c r="R74" t="n">
-        <v>7088668</v>
+        <v>7088939</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8031,9 +8031,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8048,22 +8058,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128342337</v>
+        <v>128342408</v>
       </c>
       <c r="B75" t="n">
-        <v>92736</v>
+        <v>79706</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8071,21 +8081,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8095,13 +8105,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574241</v>
+        <v>574379</v>
       </c>
       <c r="R75" t="n">
-        <v>7088939</v>
+        <v>7088725</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8128,19 +8138,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8155,12 +8155,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
         <v>128342186</v>
       </c>
       <c r="B76" t="n">
-        <v>92157</v>
+        <v>92169</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>128355111</v>
       </c>
       <c r="B77" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342361</v>
+        <v>128341749</v>
       </c>
       <c r="B12" t="n">
-        <v>92748</v>
+        <v>78844</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574230</v>
+        <v>574358</v>
       </c>
       <c r="R12" t="n">
-        <v>7088918</v>
+        <v>7088744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128341749</v>
+        <v>128342806</v>
       </c>
       <c r="B13" t="n">
-        <v>78844</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574358</v>
+        <v>574452</v>
       </c>
       <c r="R13" t="n">
-        <v>7088744</v>
+        <v>7088593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128342806</v>
+        <v>128342299</v>
       </c>
       <c r="B14" t="n">
-        <v>80192</v>
+        <v>92770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574452</v>
+        <v>574373</v>
       </c>
       <c r="R14" t="n">
-        <v>7088593</v>
+        <v>7088753</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,19 +1992,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342299</v>
+        <v>128342361</v>
       </c>
       <c r="B15" t="n">
-        <v>92770</v>
+        <v>92748</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574373</v>
+        <v>574230</v>
       </c>
       <c r="R15" t="n">
-        <v>7088753</v>
+        <v>7088918</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2099,9 +2089,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,12 +2116,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -4001,10 +4001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128342578</v>
+        <v>128342574</v>
       </c>
       <c r="B35" t="n">
-        <v>79706</v>
+        <v>78753</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,21 +4012,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574309</v>
+        <v>574308</v>
       </c>
       <c r="R35" t="n">
-        <v>7088787</v>
+        <v>7088789</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4593,10 +4593,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128342574</v>
+        <v>128342578</v>
       </c>
       <c r="B41" t="n">
-        <v>78753</v>
+        <v>79706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4604,21 +4604,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574308</v>
+        <v>574309</v>
       </c>
       <c r="R41" t="n">
-        <v>7088789</v>
+        <v>7088787</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128342664</v>
+        <v>128341946</v>
       </c>
       <c r="B45" t="n">
-        <v>57689</v>
+        <v>79706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,42 +5022,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574390</v>
+        <v>574406</v>
       </c>
       <c r="R45" t="n">
-        <v>7088731</v>
+        <v>7088724</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5084,24 +5079,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5116,22 +5096,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128341946</v>
+        <v>128341581</v>
       </c>
       <c r="B46" t="n">
-        <v>79706</v>
+        <v>78753</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5139,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5163,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574406</v>
+        <v>574445</v>
       </c>
       <c r="R46" t="n">
-        <v>7088724</v>
+        <v>7088593</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5225,10 +5205,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128341581</v>
+        <v>128342466</v>
       </c>
       <c r="B47" t="n">
-        <v>78753</v>
+        <v>92770</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5236,21 +5216,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5260,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574445</v>
+        <v>574352</v>
       </c>
       <c r="R47" t="n">
-        <v>7088593</v>
+        <v>7088735</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5322,10 +5302,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128342466</v>
+        <v>128342664</v>
       </c>
       <c r="B48" t="n">
-        <v>92770</v>
+        <v>57689</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5333,37 +5313,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574352</v>
+        <v>574390</v>
       </c>
       <c r="R48" t="n">
-        <v>7088735</v>
+        <v>7088731</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5390,9 +5375,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5407,12 +5407,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128342561</v>
+        <v>128342351</v>
       </c>
       <c r="B53" t="n">
-        <v>79706</v>
+        <v>92758</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574312</v>
+        <v>574372</v>
       </c>
       <c r="R53" t="n">
-        <v>7088790</v>
+        <v>7088765</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342438</v>
+        <v>128341543</v>
       </c>
       <c r="B54" t="n">
-        <v>78844</v>
+        <v>80228</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574373</v>
+        <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088729</v>
+        <v>7088593</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341658</v>
+        <v>128342561</v>
       </c>
       <c r="B55" t="n">
-        <v>78753</v>
+        <v>79706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R55" t="n">
-        <v>7088595</v>
+        <v>7088790</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342751</v>
+        <v>128342438</v>
       </c>
       <c r="B56" t="n">
-        <v>78753</v>
+        <v>78844</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6109,21 +6109,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574291</v>
+        <v>574373</v>
       </c>
       <c r="R56" t="n">
-        <v>7088844</v>
+        <v>7088729</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342351</v>
+        <v>128341658</v>
       </c>
       <c r="B57" t="n">
-        <v>92758</v>
+        <v>78753</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574372</v>
+        <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088765</v>
+        <v>7088595</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,32 +6292,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341543</v>
+        <v>128342751</v>
       </c>
       <c r="B58" t="n">
-        <v>80228</v>
+        <v>78753</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R58" t="n">
-        <v>7088593</v>
+        <v>7088844</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6787,7 +6787,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128341482</v>
+        <v>128341312</v>
       </c>
       <c r="B63" t="n">
         <v>92754</v>
@@ -6816,19 +6816,16 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>574408</v>
+        <v>574418</v>
       </c>
       <c r="R63" t="n">
-        <v>7088736</v>
+        <v>7088693</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6860,7 +6857,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6870,7 +6867,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6879,7 +6876,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6898,7 +6894,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128341312</v>
+        <v>128341482</v>
       </c>
       <c r="B64" t="n">
         <v>92754</v>
@@ -6927,16 +6923,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>574418</v>
+        <v>574408</v>
       </c>
       <c r="R64" t="n">
-        <v>7088693</v>
+        <v>7088736</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6968,7 +6967,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -6978,7 +6977,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6987,6 +6986,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7423,50 +7423,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341109</v>
+        <v>128342397</v>
       </c>
       <c r="B69" t="n">
-        <v>57689</v>
+        <v>92754</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574429</v>
+        <v>574294</v>
       </c>
       <c r="R69" t="n">
-        <v>7088591</v>
+        <v>7088921</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7498,7 +7493,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7508,12 +7503,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7540,32 +7530,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128342397</v>
+        <v>128341878</v>
       </c>
       <c r="B70" t="n">
-        <v>92754</v>
+        <v>79706</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7575,10 +7565,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574294</v>
+        <v>574329</v>
       </c>
       <c r="R70" t="n">
-        <v>7088921</v>
+        <v>7088770</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7610,7 +7600,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7620,7 +7610,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7635,22 +7625,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128341878</v>
+        <v>128341109</v>
       </c>
       <c r="B71" t="n">
-        <v>79706</v>
+        <v>57689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7658,34 +7648,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574329</v>
+        <v>574429</v>
       </c>
       <c r="R71" t="n">
-        <v>7088770</v>
+        <v>7088591</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,7 +7712,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7727,7 +7722,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7742,12 +7742,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128342277</v>
       </c>
       <c r="B2" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128342842</v>
+        <v>128342930</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>92772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574354</v>
+        <v>574400</v>
       </c>
       <c r="R3" t="n">
-        <v>7088880</v>
+        <v>7088743</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -877,7 +872,7 @@
         <v>128342191</v>
       </c>
       <c r="B4" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
         <v>128342785</v>
       </c>
       <c r="B5" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1076,7 @@
         <v>128341917</v>
       </c>
       <c r="B6" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,45 +1180,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342930</v>
+        <v>128342842</v>
       </c>
       <c r="B7" t="n">
-        <v>92770</v>
+        <v>56880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574400</v>
+        <v>574354</v>
       </c>
       <c r="R7" t="n">
-        <v>7088743</v>
+        <v>7088880</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,50 +1282,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341697</v>
+        <v>128341140</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574383</v>
+        <v>574438</v>
       </c>
       <c r="R8" t="n">
-        <v>7088749</v>
+        <v>7088595</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1352,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1367,12 +1362,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,32 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341140</v>
+        <v>128342525</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>79708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,13 +1424,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574438</v>
+        <v>574323</v>
       </c>
       <c r="R9" t="n">
-        <v>7088595</v>
+        <v>7088778</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1467,19 +1457,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1474,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128342525</v>
+        <v>128341860</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1497,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1521,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574323</v>
+        <v>574328</v>
       </c>
       <c r="R10" t="n">
-        <v>7088778</v>
+        <v>7088763</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,9 +1554,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341860</v>
+        <v>128341697</v>
       </c>
       <c r="B11" t="n">
-        <v>78844</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,34 +1604,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574328</v>
+        <v>574383</v>
       </c>
       <c r="R11" t="n">
-        <v>7088763</v>
+        <v>7088749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128341749</v>
+        <v>128342299</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>92772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574358</v>
+        <v>574373</v>
       </c>
       <c r="R12" t="n">
-        <v>7088744</v>
+        <v>7088753</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1778,19 +1778,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:26</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128342806</v>
+        <v>128342361</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>92750</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1818,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574452</v>
+        <v>574230</v>
       </c>
       <c r="R13" t="n">
-        <v>7088593</v>
+        <v>7088918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1877,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1897,7 +1887,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,22 +1902,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128342299</v>
+        <v>128341749</v>
       </c>
       <c r="B14" t="n">
-        <v>92770</v>
+        <v>78846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1949,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574373</v>
+        <v>574358</v>
       </c>
       <c r="R14" t="n">
-        <v>7088753</v>
+        <v>7088744</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,9 +1982,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342361</v>
+        <v>128342806</v>
       </c>
       <c r="B15" t="n">
-        <v>92748</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574230</v>
+        <v>574452</v>
       </c>
       <c r="R15" t="n">
-        <v>7088918</v>
+        <v>7088593</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,65 +2116,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341646</v>
+        <v>128341886</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574445</v>
+        <v>574321</v>
       </c>
       <c r="R16" t="n">
-        <v>7088594</v>
+        <v>7088769</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2201,14 +2196,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,12 +2223,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2238,7 +2238,7 @@
         <v>128342757</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2332,32 +2332,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341886</v>
+        <v>128341807</v>
       </c>
       <c r="B18" t="n">
-        <v>92754</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,13 +2367,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574321</v>
+        <v>574435</v>
       </c>
       <c r="R18" t="n">
-        <v>7088769</v>
+        <v>7088661</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2400,19 +2400,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2427,12 +2417,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2442,7 +2432,7 @@
         <v>128341724</v>
       </c>
       <c r="B19" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341807</v>
+        <v>128341740</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,21 +2537,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574435</v>
+        <v>574418</v>
       </c>
       <c r="R20" t="n">
-        <v>7088661</v>
+        <v>7088654</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2633,10 +2623,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341740</v>
+        <v>128341646</v>
       </c>
       <c r="B21" t="n">
-        <v>79706</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,34 +2634,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574418</v>
+        <v>574445</v>
       </c>
       <c r="R21" t="n">
-        <v>7088654</v>
+        <v>7088594</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2704,6 +2699,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2733,7 +2733,7 @@
         <v>128342521</v>
       </c>
       <c r="B22" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128342284</v>
       </c>
       <c r="B23" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,32 +2924,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342754</v>
+        <v>128342655</v>
       </c>
       <c r="B24" t="n">
-        <v>79706</v>
+        <v>90267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574291</v>
+        <v>574282</v>
       </c>
       <c r="R24" t="n">
-        <v>7088845</v>
+        <v>7088807</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342655</v>
+        <v>128342754</v>
       </c>
       <c r="B25" t="n">
-        <v>90265</v>
+        <v>79708</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574282</v>
+        <v>574291</v>
       </c>
       <c r="R25" t="n">
-        <v>7088807</v>
+        <v>7088845</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342434</v>
+        <v>128341678</v>
       </c>
       <c r="B26" t="n">
-        <v>92754</v>
+        <v>78755</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574373</v>
+        <v>574449</v>
       </c>
       <c r="R26" t="n">
-        <v>7088729</v>
+        <v>7088616</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342847</v>
+        <v>128342391</v>
       </c>
       <c r="B27" t="n">
-        <v>92754</v>
+        <v>91627</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574354</v>
+        <v>574371</v>
       </c>
       <c r="R27" t="n">
-        <v>7088881</v>
+        <v>7088729</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128341564</v>
+        <v>128342274</v>
       </c>
       <c r="B28" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,13 +3347,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574445</v>
+        <v>574276</v>
       </c>
       <c r="R28" t="n">
-        <v>7088593</v>
+        <v>7088904</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3380,9 +3380,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3397,22 +3407,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342274</v>
+        <v>128342434</v>
       </c>
       <c r="B29" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3444,13 +3454,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574276</v>
+        <v>574373</v>
       </c>
       <c r="R29" t="n">
-        <v>7088904</v>
+        <v>7088729</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3477,19 +3487,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3504,44 +3504,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128341678</v>
+        <v>128342847</v>
       </c>
       <c r="B30" t="n">
-        <v>78753</v>
+        <v>92756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574449</v>
+        <v>574354</v>
       </c>
       <c r="R30" t="n">
-        <v>7088616</v>
+        <v>7088881</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3613,32 +3613,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128342391</v>
+        <v>128341564</v>
       </c>
       <c r="B31" t="n">
-        <v>91625</v>
+        <v>92756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574371</v>
+        <v>574445</v>
       </c>
       <c r="R31" t="n">
-        <v>7088729</v>
+        <v>7088593</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3710,32 +3710,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128342815</v>
+        <v>128341686</v>
       </c>
       <c r="B32" t="n">
-        <v>92754</v>
+        <v>90499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574292</v>
+        <v>574445</v>
       </c>
       <c r="R32" t="n">
-        <v>7088883</v>
+        <v>7088630</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128341686</v>
+        <v>128342782</v>
       </c>
       <c r="B33" t="n">
-        <v>90497</v>
+        <v>92772</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,21 +3818,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574445</v>
+        <v>574280</v>
       </c>
       <c r="R33" t="n">
-        <v>7088630</v>
+        <v>7088852</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3904,32 +3904,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128342782</v>
+        <v>128342815</v>
       </c>
       <c r="B34" t="n">
-        <v>92770</v>
+        <v>92756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574280</v>
+        <v>574292</v>
       </c>
       <c r="R34" t="n">
-        <v>7088852</v>
+        <v>7088883</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4004,7 +4004,7 @@
         <v>128342574</v>
       </c>
       <c r="B35" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4098,10 +4098,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128341248</v>
+        <v>128342804</v>
       </c>
       <c r="B36" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574418</v>
+        <v>574290</v>
       </c>
       <c r="R36" t="n">
-        <v>7088658</v>
+        <v>7088881</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4166,19 +4166,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4193,12 +4183,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4208,7 +4198,7 @@
         <v>128341663</v>
       </c>
       <c r="B37" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4302,10 +4292,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128342804</v>
+        <v>128342012</v>
       </c>
       <c r="B38" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4337,10 +4327,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574290</v>
+        <v>574415</v>
       </c>
       <c r="R38" t="n">
-        <v>7088881</v>
+        <v>7088716</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4399,10 +4389,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128342012</v>
+        <v>128341929</v>
       </c>
       <c r="B39" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4434,10 +4424,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574415</v>
+        <v>574406</v>
       </c>
       <c r="R39" t="n">
-        <v>7088716</v>
+        <v>7088725</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4486,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128341929</v>
+        <v>128342578</v>
       </c>
       <c r="B40" t="n">
-        <v>92754</v>
+        <v>79708</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4521,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574406</v>
+        <v>574309</v>
       </c>
       <c r="R40" t="n">
-        <v>7088725</v>
+        <v>7088787</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,32 +4583,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128342578</v>
+        <v>128341248</v>
       </c>
       <c r="B41" t="n">
-        <v>79706</v>
+        <v>92756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,13 +4618,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574309</v>
+        <v>574418</v>
       </c>
       <c r="R41" t="n">
-        <v>7088787</v>
+        <v>7088658</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4661,9 +4651,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4678,12 +4678,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4807,10 +4807,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341959</v>
+        <v>128342904</v>
       </c>
       <c r="B43" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4842,13 +4842,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574292</v>
+        <v>574370</v>
       </c>
       <c r="R43" t="n">
-        <v>7088836</v>
+        <v>7088775</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4875,19 +4875,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4902,22 +4892,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128342904</v>
+        <v>128341959</v>
       </c>
       <c r="B44" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4949,13 +4939,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574370</v>
+        <v>574292</v>
       </c>
       <c r="R44" t="n">
-        <v>7088775</v>
+        <v>7088836</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4982,9 +4972,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,22 +4999,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128341946</v>
+        <v>128341581</v>
       </c>
       <c r="B45" t="n">
-        <v>79706</v>
+        <v>78755</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574406</v>
+        <v>574445</v>
       </c>
       <c r="R45" t="n">
-        <v>7088724</v>
+        <v>7088593</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128341581</v>
+        <v>128342466</v>
       </c>
       <c r="B46" t="n">
-        <v>78753</v>
+        <v>92772</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574445</v>
+        <v>574352</v>
       </c>
       <c r="R46" t="n">
-        <v>7088593</v>
+        <v>7088735</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128342466</v>
+        <v>128341946</v>
       </c>
       <c r="B47" t="n">
-        <v>92770</v>
+        <v>79708</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,21 +5216,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574352</v>
+        <v>574406</v>
       </c>
       <c r="R47" t="n">
-        <v>7088735</v>
+        <v>7088724</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5419,32 +5419,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128342880</v>
+        <v>128342246</v>
       </c>
       <c r="B49" t="n">
-        <v>79706</v>
+        <v>92756</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574359</v>
+        <v>574397</v>
       </c>
       <c r="R49" t="n">
-        <v>7088849</v>
+        <v>7088752</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5516,10 +5516,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342358</v>
+        <v>128342880</v>
       </c>
       <c r="B50" t="n">
-        <v>90497</v>
+        <v>79708</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5527,21 +5527,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574372</v>
+        <v>574359</v>
       </c>
       <c r="R50" t="n">
-        <v>7088765</v>
+        <v>7088849</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342246</v>
+        <v>128342898</v>
       </c>
       <c r="B51" t="n">
-        <v>92754</v>
+        <v>91431</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5624,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574397</v>
+        <v>574369</v>
       </c>
       <c r="R51" t="n">
-        <v>7088752</v>
+        <v>7088771</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5710,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128342898</v>
+        <v>128342358</v>
       </c>
       <c r="B52" t="n">
-        <v>91429</v>
+        <v>90499</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574369</v>
+        <v>574372</v>
       </c>
       <c r="R52" t="n">
-        <v>7088771</v>
+        <v>7088765</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5810,7 +5810,7 @@
         <v>128342351</v>
       </c>
       <c r="B53" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341543</v>
+        <v>128341658</v>
       </c>
       <c r="B54" t="n">
-        <v>80228</v>
+        <v>78755</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
         <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088593</v>
+        <v>7088595</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342561</v>
+        <v>128342751</v>
       </c>
       <c r="B55" t="n">
-        <v>79706</v>
+        <v>78755</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6012,21 +6012,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574312</v>
+        <v>574291</v>
       </c>
       <c r="R55" t="n">
-        <v>7088790</v>
+        <v>7088844</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342438</v>
+        <v>128342561</v>
       </c>
       <c r="B56" t="n">
-        <v>78844</v>
+        <v>79708</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6109,21 +6109,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574373</v>
+        <v>574312</v>
       </c>
       <c r="R56" t="n">
-        <v>7088729</v>
+        <v>7088790</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128341658</v>
+        <v>128341543</v>
       </c>
       <c r="B57" t="n">
-        <v>78753</v>
+        <v>80230</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6233,7 +6233,7 @@
         <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088595</v>
+        <v>7088593</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,10 +6292,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128342751</v>
+        <v>128342438</v>
       </c>
       <c r="B58" t="n">
-        <v>78753</v>
+        <v>78846</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6303,21 +6303,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574291</v>
+        <v>574373</v>
       </c>
       <c r="R58" t="n">
-        <v>7088844</v>
+        <v>7088729</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6389,10 +6389,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128341588</v>
+        <v>128342812</v>
       </c>
       <c r="B59" t="n">
-        <v>92754</v>
+        <v>80223</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6400,21 +6400,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R59" t="n">
-        <v>7088594</v>
+        <v>7088883</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6486,32 +6486,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128342667</v>
+        <v>128342771</v>
       </c>
       <c r="B60" t="n">
-        <v>92754</v>
+        <v>90499</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574390</v>
+        <v>574281</v>
       </c>
       <c r="R60" t="n">
-        <v>7088726</v>
+        <v>7088848</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6554,19 +6554,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6581,22 +6571,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342812</v>
+        <v>128342667</v>
       </c>
       <c r="B61" t="n">
-        <v>80221</v>
+        <v>92756</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6604,21 +6594,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6628,13 +6618,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574292</v>
+        <v>574390</v>
       </c>
       <c r="R61" t="n">
-        <v>7088883</v>
+        <v>7088726</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6661,9 +6651,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6678,44 +6678,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128342771</v>
+        <v>128341588</v>
       </c>
       <c r="B62" t="n">
-        <v>90497</v>
+        <v>92756</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574281</v>
+        <v>574445</v>
       </c>
       <c r="R62" t="n">
-        <v>7088848</v>
+        <v>7088594</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6790,7 +6790,7 @@
         <v>128341312</v>
       </c>
       <c r="B63" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>128341482</v>
       </c>
       <c r="B64" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>128342400</v>
       </c>
       <c r="B66" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>128341715</v>
       </c>
       <c r="B67" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128342397</v>
       </c>
       <c r="B69" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>128341878</v>
       </c>
       <c r="B70" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7754,53 +7754,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128341787</v>
+        <v>128341813</v>
       </c>
       <c r="B72" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574356</v>
+        <v>574445</v>
       </c>
       <c r="R72" t="n">
-        <v>7088756</v>
+        <v>7088668</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7827,19 +7822,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>17:28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7854,44 +7839,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128341813</v>
+        <v>128342337</v>
       </c>
       <c r="B73" t="n">
-        <v>92754</v>
+        <v>92750</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7901,13 +7886,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574445</v>
+        <v>574241</v>
       </c>
       <c r="R73" t="n">
-        <v>7088668</v>
+        <v>7088939</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7934,9 +7919,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7951,22 +7946,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128342337</v>
+        <v>128342408</v>
       </c>
       <c r="B74" t="n">
-        <v>92748</v>
+        <v>79708</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7974,21 +7969,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7998,13 +7993,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574241</v>
+        <v>574379</v>
       </c>
       <c r="R74" t="n">
-        <v>7088939</v>
+        <v>7088725</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8031,19 +8026,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8058,22 +8043,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128342408</v>
+        <v>128341787</v>
       </c>
       <c r="B75" t="n">
-        <v>79706</v>
+        <v>57689</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8081,37 +8066,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>574379</v>
+        <v>574356</v>
       </c>
       <c r="R75" t="n">
-        <v>7088725</v>
+        <v>7088756</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8138,9 +8128,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8155,12 +8155,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8170,7 +8170,7 @@
         <v>128342186</v>
       </c>
       <c r="B76" t="n">
-        <v>92169</v>
+        <v>92171</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342277</v>
+        <v>128342191</v>
       </c>
       <c r="B2" t="n">
-        <v>78755</v>
+        <v>92750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574382</v>
+        <v>574279</v>
       </c>
       <c r="R2" t="n">
-        <v>7088759</v>
+        <v>7088861</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +743,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128342930</v>
+        <v>128342785</v>
       </c>
       <c r="B3" t="n">
-        <v>92772</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574400</v>
+        <v>574275</v>
       </c>
       <c r="R3" t="n">
-        <v>7088743</v>
+        <v>7088862</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342191</v>
+        <v>128341917</v>
       </c>
       <c r="B4" t="n">
-        <v>92750</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574279</v>
+        <v>574334</v>
       </c>
       <c r="R4" t="n">
-        <v>7088861</v>
+        <v>7088809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -949,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,45 +986,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342785</v>
+        <v>128342842</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>56880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574275</v>
+        <v>574354</v>
       </c>
       <c r="R5" t="n">
-        <v>7088862</v>
+        <v>7088880</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128341917</v>
+        <v>128342277</v>
       </c>
       <c r="B6" t="n">
-        <v>78846</v>
+        <v>78755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574334</v>
+        <v>574382</v>
       </c>
       <c r="R6" t="n">
-        <v>7088809</v>
+        <v>7088759</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1141,19 +1156,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,62 +1173,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342842</v>
+        <v>128342930</v>
       </c>
       <c r="B7" t="n">
-        <v>56880</v>
+        <v>92772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574354</v>
+        <v>574400</v>
       </c>
       <c r="R7" t="n">
-        <v>7088880</v>
+        <v>7088743</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,45 +1282,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341140</v>
+        <v>128341697</v>
       </c>
       <c r="B8" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574438</v>
+        <v>574383</v>
       </c>
       <c r="R8" t="n">
-        <v>7088595</v>
+        <v>7088749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1357,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1362,7 +1367,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,32 +1399,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128342525</v>
+        <v>128341140</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>92756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,13 +1434,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574323</v>
+        <v>574438</v>
       </c>
       <c r="R9" t="n">
-        <v>7088778</v>
+        <v>7088595</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1457,9 +1467,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341860</v>
+        <v>128342525</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1521,13 +1541,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574328</v>
+        <v>574323</v>
       </c>
       <c r="R10" t="n">
-        <v>7088763</v>
+        <v>7088778</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1554,19 +1574,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,22 +1591,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341697</v>
+        <v>128341860</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,39 +1614,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574383</v>
+        <v>574328</v>
       </c>
       <c r="R11" t="n">
-        <v>7088749</v>
+        <v>7088763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1668,7 +1673,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1678,12 +1683,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342299</v>
+        <v>128342361</v>
       </c>
       <c r="B12" t="n">
-        <v>92772</v>
+        <v>92750</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574373</v>
+        <v>574230</v>
       </c>
       <c r="R12" t="n">
-        <v>7088753</v>
+        <v>7088918</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1778,9 +1778,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1795,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128342361</v>
+        <v>128341749</v>
       </c>
       <c r="B13" t="n">
-        <v>92750</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1818,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574230</v>
+        <v>574358</v>
       </c>
       <c r="R13" t="n">
-        <v>7088918</v>
+        <v>7088744</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1887,7 +1897,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128341749</v>
+        <v>128342806</v>
       </c>
       <c r="B14" t="n">
-        <v>78846</v>
+        <v>80194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574358</v>
+        <v>574452</v>
       </c>
       <c r="R14" t="n">
-        <v>7088744</v>
+        <v>7088593</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1994,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1994,7 +2004,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342806</v>
+        <v>128342299</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>92772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2066,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574452</v>
+        <v>574373</v>
       </c>
       <c r="R15" t="n">
-        <v>7088593</v>
+        <v>7088753</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2089,19 +2099,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,44 +2116,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341886</v>
+        <v>128341724</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,13 +2163,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574321</v>
+        <v>574435</v>
       </c>
       <c r="R16" t="n">
-        <v>7088769</v>
+        <v>7088666</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2196,19 +2196,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,44 +2213,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128342757</v>
+        <v>128341807</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574291</v>
+        <v>574435</v>
       </c>
       <c r="R17" t="n">
-        <v>7088843</v>
+        <v>7088661</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2332,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341807</v>
+        <v>128341740</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574435</v>
+        <v>574418</v>
       </c>
       <c r="R18" t="n">
-        <v>7088661</v>
+        <v>7088654</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341724</v>
+        <v>128342757</v>
       </c>
       <c r="B19" t="n">
-        <v>79708</v>
+        <v>92756</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574435</v>
+        <v>574291</v>
       </c>
       <c r="R19" t="n">
-        <v>7088666</v>
+        <v>7088843</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2526,32 +2516,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341740</v>
+        <v>128341886</v>
       </c>
       <c r="B20" t="n">
-        <v>79708</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,13 +2551,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574418</v>
+        <v>574321</v>
       </c>
       <c r="R20" t="n">
-        <v>7088654</v>
+        <v>7088769</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2594,9 +2584,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,12 +2611,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342274</v>
+        <v>128342434</v>
       </c>
       <c r="B28" t="n">
         <v>92756</v>
@@ -3347,13 +3347,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574276</v>
+        <v>574373</v>
       </c>
       <c r="R28" t="n">
-        <v>7088904</v>
+        <v>7088729</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3380,19 +3380,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3407,19 +3397,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342434</v>
+        <v>128342847</v>
       </c>
       <c r="B29" t="n">
         <v>92756</v>
@@ -3454,10 +3444,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574373</v>
+        <v>574354</v>
       </c>
       <c r="R29" t="n">
-        <v>7088729</v>
+        <v>7088881</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3516,7 +3506,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128342847</v>
+        <v>128341564</v>
       </c>
       <c r="B30" t="n">
         <v>92756</v>
@@ -3551,10 +3541,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574354</v>
+        <v>574445</v>
       </c>
       <c r="R30" t="n">
-        <v>7088881</v>
+        <v>7088593</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3613,7 +3603,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128341564</v>
+        <v>128342274</v>
       </c>
       <c r="B31" t="n">
         <v>92756</v>
@@ -3648,13 +3638,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574445</v>
+        <v>574276</v>
       </c>
       <c r="R31" t="n">
-        <v>7088593</v>
+        <v>7088904</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3681,9 +3671,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3698,12 +3698,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128342804</v>
+        <v>128341248</v>
       </c>
       <c r="B36" t="n">
         <v>92756</v>
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574290</v>
+        <v>574418</v>
       </c>
       <c r="R36" t="n">
-        <v>7088881</v>
+        <v>7088658</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4166,9 +4166,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4183,12 +4193,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4292,7 +4302,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128342012</v>
+        <v>128342804</v>
       </c>
       <c r="B38" t="n">
         <v>92756</v>
@@ -4327,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574415</v>
+        <v>574290</v>
       </c>
       <c r="R38" t="n">
-        <v>7088716</v>
+        <v>7088881</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4389,7 +4399,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128341929</v>
+        <v>128342012</v>
       </c>
       <c r="B39" t="n">
         <v>92756</v>
@@ -4424,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574406</v>
+        <v>574415</v>
       </c>
       <c r="R39" t="n">
-        <v>7088725</v>
+        <v>7088716</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4486,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128342578</v>
+        <v>128341929</v>
       </c>
       <c r="B40" t="n">
-        <v>79708</v>
+        <v>92756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4521,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574309</v>
+        <v>574406</v>
       </c>
       <c r="R40" t="n">
-        <v>7088787</v>
+        <v>7088725</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4583,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128341248</v>
+        <v>128342578</v>
       </c>
       <c r="B41" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4618,13 +4628,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574418</v>
+        <v>574309</v>
       </c>
       <c r="R41" t="n">
-        <v>7088658</v>
+        <v>7088787</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4651,19 +4661,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4678,62 +4678,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128341748</v>
+        <v>128341959</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574361</v>
+        <v>574292</v>
       </c>
       <c r="R42" t="n">
-        <v>7088768</v>
+        <v>7088836</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4765,7 +4760,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4775,12 +4770,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4795,12 +4785,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4904,45 +4894,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128341959</v>
+        <v>128341748</v>
       </c>
       <c r="B44" t="n">
-        <v>92756</v>
+        <v>57689</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574292</v>
+        <v>574361</v>
       </c>
       <c r="R44" t="n">
-        <v>7088836</v>
+        <v>7088768</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4974,7 +4969,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -4984,7 +4979,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,12 +4999,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128342246</v>
+        <v>128342898</v>
       </c>
       <c r="B49" t="n">
-        <v>92756</v>
+        <v>91431</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5430,21 +5430,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574397</v>
+        <v>574369</v>
       </c>
       <c r="R49" t="n">
-        <v>7088752</v>
+        <v>7088771</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5516,10 +5516,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342880</v>
+        <v>128342358</v>
       </c>
       <c r="B50" t="n">
-        <v>79708</v>
+        <v>90499</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5527,21 +5527,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574359</v>
+        <v>574372</v>
       </c>
       <c r="R50" t="n">
-        <v>7088849</v>
+        <v>7088765</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342898</v>
+        <v>128342246</v>
       </c>
       <c r="B51" t="n">
-        <v>91431</v>
+        <v>92756</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5624,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574369</v>
+        <v>574397</v>
       </c>
       <c r="R51" t="n">
-        <v>7088771</v>
+        <v>7088752</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128342358</v>
+        <v>128342880</v>
       </c>
       <c r="B52" t="n">
-        <v>90499</v>
+        <v>79708</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574372</v>
+        <v>574359</v>
       </c>
       <c r="R52" t="n">
-        <v>7088765</v>
+        <v>7088849</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128342351</v>
+        <v>128341658</v>
       </c>
       <c r="B53" t="n">
-        <v>92760</v>
+        <v>78755</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574372</v>
+        <v>574445</v>
       </c>
       <c r="R53" t="n">
-        <v>7088765</v>
+        <v>7088595</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128341658</v>
+        <v>128342751</v>
       </c>
       <c r="B54" t="n">
         <v>78755</v>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R54" t="n">
-        <v>7088595</v>
+        <v>7088844</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,32 +6001,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342751</v>
+        <v>128342351</v>
       </c>
       <c r="B55" t="n">
-        <v>78755</v>
+        <v>92760</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574291</v>
+        <v>574372</v>
       </c>
       <c r="R55" t="n">
-        <v>7088844</v>
+        <v>7088765</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342561</v>
+        <v>128341543</v>
       </c>
       <c r="B56" t="n">
-        <v>79708</v>
+        <v>80230</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574312</v>
+        <v>574445</v>
       </c>
       <c r="R56" t="n">
-        <v>7088790</v>
+        <v>7088593</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,32 +6195,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128341543</v>
+        <v>128342561</v>
       </c>
       <c r="B57" t="n">
-        <v>80230</v>
+        <v>79708</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R57" t="n">
-        <v>7088593</v>
+        <v>7088790</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6389,32 +6389,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128342812</v>
+        <v>128342771</v>
       </c>
       <c r="B59" t="n">
-        <v>80223</v>
+        <v>90499</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574292</v>
+        <v>574281</v>
       </c>
       <c r="R59" t="n">
-        <v>7088883</v>
+        <v>7088848</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6486,32 +6486,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128342771</v>
+        <v>128341588</v>
       </c>
       <c r="B60" t="n">
-        <v>90499</v>
+        <v>92756</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574281</v>
+        <v>574445</v>
       </c>
       <c r="R60" t="n">
-        <v>7088848</v>
+        <v>7088594</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6690,10 +6690,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128341588</v>
+        <v>128342812</v>
       </c>
       <c r="B62" t="n">
-        <v>92756</v>
+        <v>80223</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6701,21 +6701,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R62" t="n">
-        <v>7088594</v>
+        <v>7088883</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342176</v>
+        <v>128342400</v>
       </c>
       <c r="B65" t="n">
-        <v>57689</v>
+        <v>92949</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,42 +7016,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574286</v>
+        <v>574381</v>
       </c>
       <c r="R65" t="n">
-        <v>7088863</v>
+        <v>7088725</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7078,24 +7073,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7110,19 +7090,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128342400</v>
+        <v>128341715</v>
       </c>
       <c r="B66" t="n">
         <v>92949</v>
@@ -7157,10 +7137,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574381</v>
+        <v>574446</v>
       </c>
       <c r="R66" t="n">
-        <v>7088725</v>
+        <v>7088674</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7219,10 +7199,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128341715</v>
+        <v>128342176</v>
       </c>
       <c r="B67" t="n">
-        <v>92949</v>
+        <v>57689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7230,37 +7210,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574446</v>
+        <v>574286</v>
       </c>
       <c r="R67" t="n">
-        <v>7088674</v>
+        <v>7088863</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7287,9 +7272,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7304,12 +7304,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7423,32 +7423,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128342397</v>
+        <v>128341878</v>
       </c>
       <c r="B69" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574294</v>
+        <v>574329</v>
       </c>
       <c r="R69" t="n">
-        <v>7088921</v>
+        <v>7088770</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7518,22 +7518,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128341878</v>
+        <v>128341109</v>
       </c>
       <c r="B70" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7541,34 +7541,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574329</v>
+        <v>574429</v>
       </c>
       <c r="R70" t="n">
-        <v>7088770</v>
+        <v>7088591</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7600,7 +7605,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7610,7 +7615,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7625,62 +7635,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128341109</v>
+        <v>128342397</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>92756</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574429</v>
+        <v>574294</v>
       </c>
       <c r="R71" t="n">
-        <v>7088591</v>
+        <v>7088921</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7712,7 +7717,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7722,12 +7727,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128341678</v>
+        <v>128342391</v>
       </c>
       <c r="B26" t="n">
-        <v>78755</v>
+        <v>91627</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574449</v>
+        <v>574371</v>
       </c>
       <c r="R26" t="n">
-        <v>7088616</v>
+        <v>7088729</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342391</v>
+        <v>128342434</v>
       </c>
       <c r="B27" t="n">
-        <v>91627</v>
+        <v>92756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574371</v>
+        <v>574373</v>
       </c>
       <c r="R27" t="n">
         <v>7088729</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342434</v>
+        <v>128342847</v>
       </c>
       <c r="B28" t="n">
         <v>92756</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574373</v>
+        <v>574354</v>
       </c>
       <c r="R28" t="n">
-        <v>7088729</v>
+        <v>7088881</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342847</v>
+        <v>128341564</v>
       </c>
       <c r="B29" t="n">
         <v>92756</v>
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574354</v>
+        <v>574445</v>
       </c>
       <c r="R29" t="n">
-        <v>7088881</v>
+        <v>7088593</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128341564</v>
+        <v>128342274</v>
       </c>
       <c r="B30" t="n">
         <v>92756</v>
@@ -3541,13 +3541,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574445</v>
+        <v>574276</v>
       </c>
       <c r="R30" t="n">
-        <v>7088593</v>
+        <v>7088904</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3574,9 +3574,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3591,44 +3601,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128342274</v>
+        <v>128341678</v>
       </c>
       <c r="B31" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3638,13 +3648,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574276</v>
+        <v>574449</v>
       </c>
       <c r="R31" t="n">
-        <v>7088904</v>
+        <v>7088616</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3671,19 +3681,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3698,44 +3698,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128341686</v>
+        <v>128342815</v>
       </c>
       <c r="B32" t="n">
-        <v>90499</v>
+        <v>92756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574445</v>
+        <v>574292</v>
       </c>
       <c r="R32" t="n">
-        <v>7088630</v>
+        <v>7088883</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128342782</v>
+        <v>128341686</v>
       </c>
       <c r="B33" t="n">
-        <v>92772</v>
+        <v>90499</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,21 +3818,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574280</v>
+        <v>574445</v>
       </c>
       <c r="R33" t="n">
-        <v>7088852</v>
+        <v>7088630</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3904,32 +3904,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128342815</v>
+        <v>128342782</v>
       </c>
       <c r="B34" t="n">
-        <v>92756</v>
+        <v>92772</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574292</v>
+        <v>574280</v>
       </c>
       <c r="R34" t="n">
-        <v>7088883</v>
+        <v>7088852</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4001,10 +4001,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128342574</v>
+        <v>128342578</v>
       </c>
       <c r="B35" t="n">
-        <v>78755</v>
+        <v>79708</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,21 +4012,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574308</v>
+        <v>574309</v>
       </c>
       <c r="R35" t="n">
-        <v>7088789</v>
+        <v>7088787</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4098,32 +4098,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128341248</v>
+        <v>128342574</v>
       </c>
       <c r="B36" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574418</v>
+        <v>574308</v>
       </c>
       <c r="R36" t="n">
-        <v>7088658</v>
+        <v>7088789</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4166,19 +4166,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4193,19 +4183,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128341663</v>
+        <v>128341248</v>
       </c>
       <c r="B37" t="n">
         <v>92756</v>
@@ -4240,13 +4230,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574444</v>
+        <v>574418</v>
       </c>
       <c r="R37" t="n">
-        <v>7088610</v>
+        <v>7088658</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4273,9 +4263,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4290,19 +4290,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128342804</v>
+        <v>128341663</v>
       </c>
       <c r="B38" t="n">
         <v>92756</v>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574290</v>
+        <v>574444</v>
       </c>
       <c r="R38" t="n">
-        <v>7088881</v>
+        <v>7088610</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128342012</v>
+        <v>128342804</v>
       </c>
       <c r="B39" t="n">
         <v>92756</v>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574415</v>
+        <v>574290</v>
       </c>
       <c r="R39" t="n">
-        <v>7088716</v>
+        <v>7088881</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128341929</v>
+        <v>128342012</v>
       </c>
       <c r="B40" t="n">
         <v>92756</v>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574406</v>
+        <v>574415</v>
       </c>
       <c r="R40" t="n">
-        <v>7088725</v>
+        <v>7088716</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128342578</v>
+        <v>128341929</v>
       </c>
       <c r="B41" t="n">
-        <v>79708</v>
+        <v>92756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574309</v>
+        <v>574406</v>
       </c>
       <c r="R41" t="n">
-        <v>7088787</v>
+        <v>7088725</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5613,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342246</v>
+        <v>128342880</v>
       </c>
       <c r="B51" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574397</v>
+        <v>574359</v>
       </c>
       <c r="R51" t="n">
-        <v>7088752</v>
+        <v>7088849</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5710,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128342880</v>
+        <v>128342246</v>
       </c>
       <c r="B52" t="n">
-        <v>79708</v>
+        <v>92756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574359</v>
+        <v>574397</v>
       </c>
       <c r="R52" t="n">
-        <v>7088849</v>
+        <v>7088752</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6001,32 +6001,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342351</v>
+        <v>128341543</v>
       </c>
       <c r="B55" t="n">
-        <v>92760</v>
+        <v>80230</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4365</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574372</v>
+        <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088765</v>
+        <v>7088593</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128341543</v>
+        <v>128342561</v>
       </c>
       <c r="B56" t="n">
-        <v>80230</v>
+        <v>79708</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R56" t="n">
-        <v>7088593</v>
+        <v>7088790</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342561</v>
+        <v>128342438</v>
       </c>
       <c r="B57" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6206,21 +6206,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574312</v>
+        <v>574373</v>
       </c>
       <c r="R57" t="n">
-        <v>7088790</v>
+        <v>7088729</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,32 +6292,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128342438</v>
+        <v>128342351</v>
       </c>
       <c r="B58" t="n">
-        <v>78846</v>
+        <v>92760</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574373</v>
+        <v>574372</v>
       </c>
       <c r="R58" t="n">
-        <v>7088729</v>
+        <v>7088765</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6389,32 +6389,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128342771</v>
+        <v>128341588</v>
       </c>
       <c r="B59" t="n">
-        <v>90499</v>
+        <v>92756</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574281</v>
+        <v>574445</v>
       </c>
       <c r="R59" t="n">
-        <v>7088848</v>
+        <v>7088594</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6486,7 +6486,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128341588</v>
+        <v>128342667</v>
       </c>
       <c r="B60" t="n">
         <v>92756</v>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574445</v>
+        <v>574390</v>
       </c>
       <c r="R60" t="n">
-        <v>7088594</v>
+        <v>7088726</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6554,9 +6554,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6571,22 +6581,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342667</v>
+        <v>128342812</v>
       </c>
       <c r="B61" t="n">
-        <v>92756</v>
+        <v>80223</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6594,21 +6604,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,13 +6628,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574390</v>
+        <v>574292</v>
       </c>
       <c r="R61" t="n">
-        <v>7088726</v>
+        <v>7088883</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6651,19 +6661,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6678,44 +6678,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128342812</v>
+        <v>128342771</v>
       </c>
       <c r="B62" t="n">
-        <v>80223</v>
+        <v>90499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574292</v>
+        <v>574281</v>
       </c>
       <c r="R62" t="n">
-        <v>7088883</v>
+        <v>7088848</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342400</v>
+        <v>128342176</v>
       </c>
       <c r="B65" t="n">
-        <v>92949</v>
+        <v>57689</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,37 +7016,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574381</v>
+        <v>574286</v>
       </c>
       <c r="R65" t="n">
-        <v>7088725</v>
+        <v>7088863</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,9 +7078,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7090,19 +7110,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128341715</v>
+        <v>128342400</v>
       </c>
       <c r="B66" t="n">
         <v>92949</v>
@@ -7137,10 +7157,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574446</v>
+        <v>574381</v>
       </c>
       <c r="R66" t="n">
-        <v>7088674</v>
+        <v>7088725</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7199,10 +7219,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128342176</v>
+        <v>128341715</v>
       </c>
       <c r="B67" t="n">
-        <v>57689</v>
+        <v>92949</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7210,42 +7230,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574286</v>
+        <v>574446</v>
       </c>
       <c r="R67" t="n">
-        <v>7088863</v>
+        <v>7088674</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7272,24 +7287,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7304,12 +7304,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7423,32 +7423,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128341878</v>
+        <v>128342397</v>
       </c>
       <c r="B69" t="n">
-        <v>79708</v>
+        <v>92756</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574329</v>
+        <v>574294</v>
       </c>
       <c r="R69" t="n">
-        <v>7088770</v>
+        <v>7088921</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7518,12 +7518,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7647,32 +7647,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128342397</v>
+        <v>128341878</v>
       </c>
       <c r="B71" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574294</v>
+        <v>574329</v>
       </c>
       <c r="R71" t="n">
-        <v>7088921</v>
+        <v>7088770</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7742,12 +7742,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342191</v>
+        <v>128342277</v>
       </c>
       <c r="B2" t="n">
-        <v>92750</v>
+        <v>78755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574279</v>
+        <v>574382</v>
       </c>
       <c r="R2" t="n">
-        <v>7088861</v>
+        <v>7088759</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,19 +743,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128342785</v>
+        <v>128341917</v>
       </c>
       <c r="B3" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574275</v>
+        <v>574334</v>
       </c>
       <c r="R3" t="n">
-        <v>7088862</v>
+        <v>7088809</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +840,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128341917</v>
+        <v>128342930</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>92773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574334</v>
+        <v>574400</v>
       </c>
       <c r="R4" t="n">
-        <v>7088809</v>
+        <v>7088743</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +947,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,65 +964,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342842</v>
+        <v>128342191</v>
       </c>
       <c r="B5" t="n">
-        <v>56880</v>
+        <v>92751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574354</v>
+        <v>574279</v>
       </c>
       <c r="R5" t="n">
-        <v>7088880</v>
+        <v>7088861</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1059,9 +1044,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128342277</v>
+        <v>128342785</v>
       </c>
       <c r="B6" t="n">
-        <v>78755</v>
+        <v>79708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574382</v>
+        <v>574275</v>
       </c>
       <c r="R6" t="n">
-        <v>7088759</v>
+        <v>7088862</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,45 +1180,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342930</v>
+        <v>128342842</v>
       </c>
       <c r="B7" t="n">
-        <v>92772</v>
+        <v>56880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574400</v>
+        <v>574354</v>
       </c>
       <c r="R7" t="n">
-        <v>7088743</v>
+        <v>7088880</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341697</v>
+        <v>128342525</v>
       </c>
       <c r="B8" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,42 +1293,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574383</v>
+        <v>574323</v>
       </c>
       <c r="R8" t="n">
-        <v>7088749</v>
+        <v>7088778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1355,24 +1350,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,12 +1367,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1402,7 +1382,7 @@
         <v>128341140</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,10 +1486,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128342525</v>
+        <v>128341860</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1517,21 +1497,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1521,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574323</v>
+        <v>574328</v>
       </c>
       <c r="R10" t="n">
-        <v>7088778</v>
+        <v>7088763</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,9 +1554,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,22 +1581,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341860</v>
+        <v>128341697</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,34 +1604,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574328</v>
+        <v>574383</v>
       </c>
       <c r="R11" t="n">
-        <v>7088763</v>
+        <v>7088749</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1668,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1683,7 +1678,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342361</v>
+        <v>128341749</v>
       </c>
       <c r="B12" t="n">
-        <v>92750</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574230</v>
+        <v>574358</v>
       </c>
       <c r="R12" t="n">
-        <v>7088918</v>
+        <v>7088744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128341749</v>
+        <v>128342806</v>
       </c>
       <c r="B13" t="n">
-        <v>78846</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574358</v>
+        <v>574452</v>
       </c>
       <c r="R13" t="n">
-        <v>7088744</v>
+        <v>7088593</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128342806</v>
+        <v>128342361</v>
       </c>
       <c r="B14" t="n">
-        <v>80194</v>
+        <v>92751</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574452</v>
+        <v>574230</v>
       </c>
       <c r="R14" t="n">
-        <v>7088593</v>
+        <v>7088918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,12 +2019,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2034,7 +2034,7 @@
         <v>128342299</v>
       </c>
       <c r="B15" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2128,32 +2128,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341724</v>
+        <v>128342757</v>
       </c>
       <c r="B16" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574435</v>
+        <v>574291</v>
       </c>
       <c r="R16" t="n">
-        <v>7088666</v>
+        <v>7088843</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,32 +2225,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341807</v>
+        <v>128341886</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574435</v>
+        <v>574321</v>
       </c>
       <c r="R17" t="n">
-        <v>7088661</v>
+        <v>7088769</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2293,9 +2293,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341740</v>
+        <v>128341807</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574418</v>
+        <v>574435</v>
       </c>
       <c r="R18" t="n">
-        <v>7088654</v>
+        <v>7088661</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2419,32 +2429,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128342757</v>
+        <v>128341724</v>
       </c>
       <c r="B19" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574291</v>
+        <v>574435</v>
       </c>
       <c r="R19" t="n">
-        <v>7088843</v>
+        <v>7088666</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2516,32 +2526,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341886</v>
+        <v>128341740</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,13 +2561,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574321</v>
+        <v>574418</v>
       </c>
       <c r="R20" t="n">
-        <v>7088769</v>
+        <v>7088654</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2584,19 +2594,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,12 +2611,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342391</v>
+        <v>128342434</v>
       </c>
       <c r="B26" t="n">
-        <v>91627</v>
+        <v>92757</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574371</v>
+        <v>574373</v>
       </c>
       <c r="R26" t="n">
         <v>7088729</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342434</v>
+        <v>128342847</v>
       </c>
       <c r="B27" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574373</v>
+        <v>574354</v>
       </c>
       <c r="R27" t="n">
-        <v>7088729</v>
+        <v>7088881</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342847</v>
+        <v>128341564</v>
       </c>
       <c r="B28" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574354</v>
+        <v>574445</v>
       </c>
       <c r="R28" t="n">
-        <v>7088881</v>
+        <v>7088593</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128341564</v>
+        <v>128342274</v>
       </c>
       <c r="B29" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574445</v>
+        <v>574276</v>
       </c>
       <c r="R29" t="n">
-        <v>7088593</v>
+        <v>7088904</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3477,9 +3477,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3494,44 +3504,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128342274</v>
+        <v>128342391</v>
       </c>
       <c r="B30" t="n">
-        <v>92756</v>
+        <v>91628</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3541,13 +3551,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574276</v>
+        <v>574371</v>
       </c>
       <c r="R30" t="n">
-        <v>7088904</v>
+        <v>7088729</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3574,19 +3584,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
         <v>128342815</v>
       </c>
       <c r="B32" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>128342782</v>
       </c>
       <c r="B34" t="n">
-        <v>92772</v>
+        <v>92773</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4001,32 +4001,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128342578</v>
+        <v>128341248</v>
       </c>
       <c r="B35" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,13 +4036,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574309</v>
+        <v>574418</v>
       </c>
       <c r="R35" t="n">
-        <v>7088787</v>
+        <v>7088658</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4069,9 +4069,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4086,44 +4096,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128342574</v>
+        <v>128341663</v>
       </c>
       <c r="B36" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4133,10 +4143,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574308</v>
+        <v>574444</v>
       </c>
       <c r="R36" t="n">
-        <v>7088789</v>
+        <v>7088610</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4195,10 +4205,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128341248</v>
+        <v>128342804</v>
       </c>
       <c r="B37" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4230,13 +4240,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574418</v>
+        <v>574290</v>
       </c>
       <c r="R37" t="n">
-        <v>7088658</v>
+        <v>7088881</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4263,19 +4273,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4290,22 +4290,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128341663</v>
+        <v>128342012</v>
       </c>
       <c r="B38" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574444</v>
+        <v>574415</v>
       </c>
       <c r="R38" t="n">
-        <v>7088610</v>
+        <v>7088716</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128342804</v>
+        <v>128341929</v>
       </c>
       <c r="B39" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574290</v>
+        <v>574406</v>
       </c>
       <c r="R39" t="n">
-        <v>7088881</v>
+        <v>7088725</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128342012</v>
+        <v>128342574</v>
       </c>
       <c r="B40" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574415</v>
+        <v>574308</v>
       </c>
       <c r="R40" t="n">
-        <v>7088716</v>
+        <v>7088789</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128341929</v>
+        <v>128342578</v>
       </c>
       <c r="B41" t="n">
-        <v>92756</v>
+        <v>79708</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574406</v>
+        <v>574309</v>
       </c>
       <c r="R41" t="n">
-        <v>7088725</v>
+        <v>7088787</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4693,7 +4693,7 @@
         <v>128341959</v>
       </c>
       <c r="B42" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>128342904</v>
       </c>
       <c r="B43" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128342466</v>
+        <v>128342664</v>
       </c>
       <c r="B46" t="n">
-        <v>92772</v>
+        <v>57689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,37 +5119,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574352</v>
+        <v>574390</v>
       </c>
       <c r="R46" t="n">
-        <v>7088735</v>
+        <v>7088731</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5176,9 +5181,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5193,22 +5213,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128341946</v>
+        <v>128342466</v>
       </c>
       <c r="B47" t="n">
-        <v>79708</v>
+        <v>92773</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,21 +5236,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5260,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574406</v>
+        <v>574352</v>
       </c>
       <c r="R47" t="n">
-        <v>7088724</v>
+        <v>7088735</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5302,10 +5322,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128342664</v>
+        <v>128341946</v>
       </c>
       <c r="B48" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5313,42 +5333,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574390</v>
+        <v>574406</v>
       </c>
       <c r="R48" t="n">
-        <v>7088731</v>
+        <v>7088724</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5375,24 +5390,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5407,12 +5407,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5422,7 +5422,7 @@
         <v>128342898</v>
       </c>
       <c r="B49" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342358</v>
+        <v>128342880</v>
       </c>
       <c r="B50" t="n">
-        <v>90499</v>
+        <v>79708</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5527,21 +5527,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574372</v>
+        <v>574359</v>
       </c>
       <c r="R50" t="n">
-        <v>7088765</v>
+        <v>7088849</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,32 +5613,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342880</v>
+        <v>128342246</v>
       </c>
       <c r="B51" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574359</v>
+        <v>574397</v>
       </c>
       <c r="R51" t="n">
-        <v>7088849</v>
+        <v>7088752</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5710,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128342246</v>
+        <v>128342358</v>
       </c>
       <c r="B52" t="n">
-        <v>92756</v>
+        <v>90499</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574397</v>
+        <v>574372</v>
       </c>
       <c r="R52" t="n">
-        <v>7088752</v>
+        <v>7088765</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128341658</v>
+        <v>128342561</v>
       </c>
       <c r="B53" t="n">
-        <v>78755</v>
+        <v>79708</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5818,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574445</v>
+        <v>574312</v>
       </c>
       <c r="R53" t="n">
-        <v>7088595</v>
+        <v>7088790</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342751</v>
+        <v>128342351</v>
       </c>
       <c r="B54" t="n">
-        <v>78755</v>
+        <v>92761</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574291</v>
+        <v>574372</v>
       </c>
       <c r="R54" t="n">
-        <v>7088844</v>
+        <v>7088765</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,32 +6001,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341543</v>
+        <v>128342438</v>
       </c>
       <c r="B55" t="n">
-        <v>80230</v>
+        <v>78846</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574373</v>
       </c>
       <c r="R55" t="n">
-        <v>7088593</v>
+        <v>7088729</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342561</v>
+        <v>128341658</v>
       </c>
       <c r="B56" t="n">
-        <v>79708</v>
+        <v>78755</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6109,21 +6109,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574312</v>
+        <v>574445</v>
       </c>
       <c r="R56" t="n">
-        <v>7088790</v>
+        <v>7088595</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342438</v>
+        <v>128342751</v>
       </c>
       <c r="B57" t="n">
-        <v>78846</v>
+        <v>78755</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6206,21 +6206,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574373</v>
+        <v>574291</v>
       </c>
       <c r="R57" t="n">
-        <v>7088729</v>
+        <v>7088844</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,32 +6292,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128342351</v>
+        <v>128341543</v>
       </c>
       <c r="B58" t="n">
-        <v>92760</v>
+        <v>80230</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4365</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574372</v>
+        <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088765</v>
+        <v>7088593</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6392,7 +6392,7 @@
         <v>128341588</v>
       </c>
       <c r="B59" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         <v>128342667</v>
       </c>
       <c r="B60" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6593,32 +6593,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342812</v>
+        <v>128342771</v>
       </c>
       <c r="B61" t="n">
-        <v>80223</v>
+        <v>90499</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6628,10 +6628,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574292</v>
+        <v>574281</v>
       </c>
       <c r="R61" t="n">
-        <v>7088883</v>
+        <v>7088848</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6690,32 +6690,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128342771</v>
+        <v>128342812</v>
       </c>
       <c r="B62" t="n">
-        <v>90499</v>
+        <v>80223</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1962</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574281</v>
+        <v>574292</v>
       </c>
       <c r="R62" t="n">
-        <v>7088848</v>
+        <v>7088883</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6790,7 +6790,7 @@
         <v>128341312</v>
       </c>
       <c r="B63" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>128341482</v>
       </c>
       <c r="B64" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>128342400</v>
       </c>
       <c r="B66" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>128341715</v>
       </c>
       <c r="B67" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128342397</v>
       </c>
       <c r="B69" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         <v>128341813</v>
       </c>
       <c r="B72" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         <v>128342337</v>
       </c>
       <c r="B73" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>128342186</v>
       </c>
       <c r="B76" t="n">
-        <v>92171</v>
+        <v>92172</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342191</v>
+        <v>128342785</v>
       </c>
       <c r="B5" t="n">
-        <v>92751</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,13 +1011,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574279</v>
+        <v>574275</v>
       </c>
       <c r="R5" t="n">
-        <v>7088861</v>
+        <v>7088862</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,19 +1044,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,57 +1061,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128342785</v>
+        <v>128342842</v>
       </c>
       <c r="B6" t="n">
-        <v>79708</v>
+        <v>56880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574275</v>
+        <v>574354</v>
       </c>
       <c r="R6" t="n">
-        <v>7088862</v>
+        <v>7088880</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,53 +1175,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342842</v>
+        <v>128342191</v>
       </c>
       <c r="B7" t="n">
-        <v>56880</v>
+        <v>92751</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574354</v>
+        <v>574279</v>
       </c>
       <c r="R7" t="n">
-        <v>7088880</v>
+        <v>7088861</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1253,9 +1243,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,44 +1270,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128342525</v>
+        <v>128341140</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574323</v>
+        <v>574438</v>
       </c>
       <c r="R8" t="n">
-        <v>7088778</v>
+        <v>7088595</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,9 +1350,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,44 +1377,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341140</v>
+        <v>128341860</v>
       </c>
       <c r="B9" t="n">
-        <v>92757</v>
+        <v>78846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574438</v>
+        <v>574328</v>
       </c>
       <c r="R9" t="n">
-        <v>7088595</v>
+        <v>7088763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1459,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1459,7 +1469,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,22 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341860</v>
+        <v>128341697</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,34 +1507,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574328</v>
+        <v>574383</v>
       </c>
       <c r="R10" t="n">
-        <v>7088763</v>
+        <v>7088749</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1571,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1566,7 +1581,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,22 +1601,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128341697</v>
+        <v>128342525</v>
       </c>
       <c r="B11" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1604,42 +1624,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574383</v>
+        <v>574323</v>
       </c>
       <c r="R11" t="n">
-        <v>7088749</v>
+        <v>7088778</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1666,24 +1681,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128341749</v>
+        <v>128342361</v>
       </c>
       <c r="B12" t="n">
-        <v>78846</v>
+        <v>92751</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574358</v>
+        <v>574230</v>
       </c>
       <c r="R12" t="n">
-        <v>7088744</v>
+        <v>7088918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128342806</v>
+        <v>128342299</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>92773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574452</v>
+        <v>574373</v>
       </c>
       <c r="R13" t="n">
-        <v>7088593</v>
+        <v>7088753</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,19 +1885,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1912,22 +1902,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128342361</v>
+        <v>128341749</v>
       </c>
       <c r="B14" t="n">
-        <v>92751</v>
+        <v>78846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574230</v>
+        <v>574358</v>
       </c>
       <c r="R14" t="n">
-        <v>7088918</v>
+        <v>7088744</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +1984,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2004,7 +1994,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342299</v>
+        <v>128342806</v>
       </c>
       <c r="B15" t="n">
-        <v>92773</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574373</v>
+        <v>574452</v>
       </c>
       <c r="R15" t="n">
-        <v>7088753</v>
+        <v>7088593</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2099,9 +2089,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,44 +2116,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128342757</v>
+        <v>128341807</v>
       </c>
       <c r="B16" t="n">
-        <v>92757</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574291</v>
+        <v>574435</v>
       </c>
       <c r="R16" t="n">
-        <v>7088843</v>
+        <v>7088661</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,32 +2225,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341886</v>
+        <v>128341724</v>
       </c>
       <c r="B17" t="n">
-        <v>92757</v>
+        <v>79708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574321</v>
+        <v>574435</v>
       </c>
       <c r="R17" t="n">
-        <v>7088769</v>
+        <v>7088666</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2293,19 +2293,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2310,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341807</v>
+        <v>128341740</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574435</v>
+        <v>574418</v>
       </c>
       <c r="R18" t="n">
-        <v>7088661</v>
+        <v>7088654</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2429,32 +2419,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341724</v>
+        <v>128342757</v>
       </c>
       <c r="B19" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2464,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574435</v>
+        <v>574291</v>
       </c>
       <c r="R19" t="n">
-        <v>7088666</v>
+        <v>7088843</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2526,32 +2516,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341740</v>
+        <v>128341886</v>
       </c>
       <c r="B20" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,13 +2551,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574418</v>
+        <v>574321</v>
       </c>
       <c r="R20" t="n">
-        <v>7088654</v>
+        <v>7088769</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2594,9 +2584,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,12 +2611,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128342521</v>
+        <v>128342284</v>
       </c>
       <c r="B22" t="n">
-        <v>78846</v>
+        <v>79708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574324</v>
+        <v>574388</v>
       </c>
       <c r="R22" t="n">
-        <v>7088797</v>
+        <v>7088762</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128342284</v>
+        <v>128342521</v>
       </c>
       <c r="B23" t="n">
-        <v>79708</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574388</v>
+        <v>574324</v>
       </c>
       <c r="R23" t="n">
-        <v>7088762</v>
+        <v>7088797</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,32 +2924,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342655</v>
+        <v>128342754</v>
       </c>
       <c r="B24" t="n">
-        <v>90267</v>
+        <v>79708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574282</v>
+        <v>574291</v>
       </c>
       <c r="R24" t="n">
-        <v>7088807</v>
+        <v>7088845</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342754</v>
+        <v>128342655</v>
       </c>
       <c r="B25" t="n">
-        <v>79708</v>
+        <v>90267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574291</v>
+        <v>574282</v>
       </c>
       <c r="R25" t="n">
-        <v>7088845</v>
+        <v>7088807</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342434</v>
+        <v>128342391</v>
       </c>
       <c r="B26" t="n">
-        <v>92757</v>
+        <v>91628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574373</v>
+        <v>574371</v>
       </c>
       <c r="R26" t="n">
         <v>7088729</v>
@@ -3215,7 +3215,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342847</v>
+        <v>128342434</v>
       </c>
       <c r="B27" t="n">
         <v>92757</v>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574354</v>
+        <v>574373</v>
       </c>
       <c r="R27" t="n">
-        <v>7088881</v>
+        <v>7088729</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128341564</v>
+        <v>128342847</v>
       </c>
       <c r="B28" t="n">
         <v>92757</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574445</v>
+        <v>574354</v>
       </c>
       <c r="R28" t="n">
-        <v>7088593</v>
+        <v>7088881</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342274</v>
+        <v>128341564</v>
       </c>
       <c r="B29" t="n">
         <v>92757</v>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574276</v>
+        <v>574445</v>
       </c>
       <c r="R29" t="n">
-        <v>7088904</v>
+        <v>7088593</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3477,19 +3477,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3504,44 +3494,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128342391</v>
+        <v>128342274</v>
       </c>
       <c r="B30" t="n">
-        <v>91628</v>
+        <v>92757</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,13 +3541,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574371</v>
+        <v>574276</v>
       </c>
       <c r="R30" t="n">
-        <v>7088729</v>
+        <v>7088904</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3584,9 +3574,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128341248</v>
+        <v>128341663</v>
       </c>
       <c r="B35" t="n">
         <v>92757</v>
@@ -4036,13 +4036,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574418</v>
+        <v>574444</v>
       </c>
       <c r="R35" t="n">
-        <v>7088658</v>
+        <v>7088610</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4069,19 +4069,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4096,19 +4086,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128341663</v>
+        <v>128342804</v>
       </c>
       <c r="B36" t="n">
         <v>92757</v>
@@ -4143,10 +4133,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574444</v>
+        <v>574290</v>
       </c>
       <c r="R36" t="n">
-        <v>7088610</v>
+        <v>7088881</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4205,7 +4195,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128342804</v>
+        <v>128342012</v>
       </c>
       <c r="B37" t="n">
         <v>92757</v>
@@ -4240,10 +4230,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574290</v>
+        <v>574415</v>
       </c>
       <c r="R37" t="n">
-        <v>7088881</v>
+        <v>7088716</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4302,7 +4292,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128342012</v>
+        <v>128341929</v>
       </c>
       <c r="B38" t="n">
         <v>92757</v>
@@ -4337,10 +4327,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574415</v>
+        <v>574406</v>
       </c>
       <c r="R38" t="n">
-        <v>7088716</v>
+        <v>7088725</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4399,32 +4389,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128341929</v>
+        <v>128342574</v>
       </c>
       <c r="B39" t="n">
-        <v>92757</v>
+        <v>78755</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4434,10 +4424,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574406</v>
+        <v>574308</v>
       </c>
       <c r="R39" t="n">
-        <v>7088725</v>
+        <v>7088789</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4486,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128342574</v>
+        <v>128341248</v>
       </c>
       <c r="B40" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,13 +4521,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574308</v>
+        <v>574418</v>
       </c>
       <c r="R40" t="n">
-        <v>7088789</v>
+        <v>7088658</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4564,9 +4554,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4581,12 +4581,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128342664</v>
+        <v>128342466</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>92773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,42 +5119,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574390</v>
+        <v>574352</v>
       </c>
       <c r="R46" t="n">
-        <v>7088731</v>
+        <v>7088735</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5181,24 +5176,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5213,22 +5193,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128342466</v>
+        <v>128342664</v>
       </c>
       <c r="B47" t="n">
-        <v>92773</v>
+        <v>57689</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5236,37 +5216,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574352</v>
+        <v>574390</v>
       </c>
       <c r="R47" t="n">
-        <v>7088735</v>
+        <v>7088731</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5293,9 +5278,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5310,12 +5310,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5807,10 +5807,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128342561</v>
+        <v>128342751</v>
       </c>
       <c r="B53" t="n">
-        <v>79708</v>
+        <v>78755</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5818,21 +5818,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574312</v>
+        <v>574291</v>
       </c>
       <c r="R53" t="n">
-        <v>7088790</v>
+        <v>7088844</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342351</v>
+        <v>128342561</v>
       </c>
       <c r="B54" t="n">
-        <v>92761</v>
+        <v>79708</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574372</v>
+        <v>574312</v>
       </c>
       <c r="R54" t="n">
-        <v>7088765</v>
+        <v>7088790</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,32 +6001,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128342438</v>
+        <v>128341543</v>
       </c>
       <c r="B55" t="n">
-        <v>78846</v>
+        <v>80230</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574373</v>
+        <v>574445</v>
       </c>
       <c r="R55" t="n">
-        <v>7088729</v>
+        <v>7088593</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128341658</v>
+        <v>128342351</v>
       </c>
       <c r="B56" t="n">
-        <v>78755</v>
+        <v>92761</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574445</v>
+        <v>574372</v>
       </c>
       <c r="R56" t="n">
-        <v>7088595</v>
+        <v>7088765</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342751</v>
+        <v>128342438</v>
       </c>
       <c r="B57" t="n">
-        <v>78755</v>
+        <v>78846</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6206,21 +6206,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574291</v>
+        <v>574373</v>
       </c>
       <c r="R57" t="n">
-        <v>7088844</v>
+        <v>7088729</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,32 +6292,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341543</v>
+        <v>128341658</v>
       </c>
       <c r="B58" t="n">
-        <v>80230</v>
+        <v>78755</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6330,7 +6330,7 @@
         <v>574445</v>
       </c>
       <c r="R58" t="n">
-        <v>7088593</v>
+        <v>7088595</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7530,10 +7530,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128341109</v>
+        <v>128341878</v>
       </c>
       <c r="B70" t="n">
-        <v>57689</v>
+        <v>79708</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7541,39 +7541,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574429</v>
+        <v>574329</v>
       </c>
       <c r="R70" t="n">
-        <v>7088591</v>
+        <v>7088770</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7605,7 +7600,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7615,12 +7610,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7635,22 +7625,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128341878</v>
+        <v>128341109</v>
       </c>
       <c r="B71" t="n">
-        <v>79708</v>
+        <v>57689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7658,34 +7648,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>574329</v>
+        <v>574429</v>
       </c>
       <c r="R71" t="n">
-        <v>7088770</v>
+        <v>7088591</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,7 +7712,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -7727,7 +7722,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7742,12 +7742,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342277</v>
+        <v>128342785</v>
       </c>
       <c r="B2" t="n">
-        <v>78755</v>
+        <v>79735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574382</v>
+        <v>574275</v>
       </c>
       <c r="R2" t="n">
-        <v>7088759</v>
+        <v>7088862</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -775,7 +775,7 @@
         <v>128341917</v>
       </c>
       <c r="B3" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342930</v>
+        <v>128342191</v>
       </c>
       <c r="B4" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574400</v>
+        <v>574279</v>
       </c>
       <c r="R4" t="n">
-        <v>7088743</v>
+        <v>7088861</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,9 +947,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342785</v>
+        <v>128342930</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>92800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574275</v>
+        <v>574400</v>
       </c>
       <c r="R5" t="n">
-        <v>7088862</v>
+        <v>7088743</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1086,7 @@
         <v>128342842</v>
       </c>
       <c r="B6" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342191</v>
+        <v>128342277</v>
       </c>
       <c r="B7" t="n">
-        <v>92751</v>
+        <v>78782</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1196,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,13 +1220,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574279</v>
+        <v>574382</v>
       </c>
       <c r="R7" t="n">
-        <v>7088861</v>
+        <v>7088759</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1243,19 +1253,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,44 +1270,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128341140</v>
+        <v>128342525</v>
       </c>
       <c r="B8" t="n">
-        <v>92757</v>
+        <v>79735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574438</v>
+        <v>574323</v>
       </c>
       <c r="R8" t="n">
-        <v>7088595</v>
+        <v>7088778</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,19 +1350,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:54</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,12 +1367,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1392,7 +1382,7 @@
         <v>128341860</v>
       </c>
       <c r="B9" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,50 +1486,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128341697</v>
+        <v>128341140</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>92784</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574383</v>
+        <v>574438</v>
       </c>
       <c r="R10" t="n">
-        <v>7088749</v>
+        <v>7088595</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,7 +1556,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1581,12 +1566,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, äldre och färska spår</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128342525</v>
+        <v>128341697</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,37 +1604,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574323</v>
+        <v>574383</v>
       </c>
       <c r="R11" t="n">
-        <v>7088778</v>
+        <v>7088749</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1681,9 +1666,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, äldre och färska spår</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128342361</v>
+        <v>128341749</v>
       </c>
       <c r="B12" t="n">
-        <v>92751</v>
+        <v>78873</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574230</v>
+        <v>574358</v>
       </c>
       <c r="R12" t="n">
-        <v>7088918</v>
+        <v>7088744</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128342299</v>
+        <v>128342806</v>
       </c>
       <c r="B13" t="n">
-        <v>92773</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574373</v>
+        <v>574452</v>
       </c>
       <c r="R13" t="n">
-        <v>7088753</v>
+        <v>7088593</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1885,9 +1885,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128341749</v>
+        <v>128342361</v>
       </c>
       <c r="B14" t="n">
-        <v>78846</v>
+        <v>92778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574358</v>
+        <v>574230</v>
       </c>
       <c r="R14" t="n">
-        <v>7088744</v>
+        <v>7088918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1984,7 +1994,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1994,7 +2004,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342806</v>
+        <v>128342299</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>92800</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,13 +2066,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574452</v>
+        <v>574373</v>
       </c>
       <c r="R15" t="n">
-        <v>7088593</v>
+        <v>7088753</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2089,19 +2099,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,22 +2116,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128341807</v>
+        <v>128341724</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,7 +2166,7 @@
         <v>574435</v>
       </c>
       <c r="R16" t="n">
-        <v>7088661</v>
+        <v>7088666</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128341724</v>
+        <v>128341740</v>
       </c>
       <c r="B17" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574435</v>
+        <v>574418</v>
       </c>
       <c r="R17" t="n">
-        <v>7088666</v>
+        <v>7088654</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341740</v>
+        <v>128341807</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,21 +2333,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,10 +2357,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574418</v>
+        <v>574435</v>
       </c>
       <c r="R18" t="n">
-        <v>7088654</v>
+        <v>7088661</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2419,45 +2419,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128342757</v>
+        <v>128341646</v>
       </c>
       <c r="B19" t="n">
-        <v>92757</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574291</v>
+        <v>574445</v>
       </c>
       <c r="R19" t="n">
-        <v>7088843</v>
+        <v>7088594</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2490,6 +2495,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128341886</v>
+        <v>128342757</v>
       </c>
       <c r="B20" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,13 +2561,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574321</v>
+        <v>574291</v>
       </c>
       <c r="R20" t="n">
-        <v>7088769</v>
+        <v>7088843</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2584,19 +2594,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,65 +2611,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341646</v>
+        <v>128341886</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>92784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574445</v>
+        <v>574321</v>
       </c>
       <c r="R21" t="n">
-        <v>7088594</v>
+        <v>7088769</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2696,14 +2691,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,22 +2718,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128342284</v>
+        <v>128342521</v>
       </c>
       <c r="B22" t="n">
-        <v>79708</v>
+        <v>78873</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574388</v>
+        <v>574324</v>
       </c>
       <c r="R22" t="n">
-        <v>7088762</v>
+        <v>7088797</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2827,10 +2827,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128342521</v>
+        <v>128342284</v>
       </c>
       <c r="B23" t="n">
-        <v>78846</v>
+        <v>79735</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574324</v>
+        <v>574388</v>
       </c>
       <c r="R23" t="n">
-        <v>7088797</v>
+        <v>7088762</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2924,32 +2924,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342754</v>
+        <v>128342655</v>
       </c>
       <c r="B24" t="n">
-        <v>79708</v>
+        <v>90294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574291</v>
+        <v>574282</v>
       </c>
       <c r="R24" t="n">
-        <v>7088845</v>
+        <v>7088807</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342655</v>
+        <v>128342754</v>
       </c>
       <c r="B25" t="n">
-        <v>90267</v>
+        <v>79735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574282</v>
+        <v>574291</v>
       </c>
       <c r="R25" t="n">
-        <v>7088807</v>
+        <v>7088845</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342391</v>
+        <v>128342434</v>
       </c>
       <c r="B26" t="n">
-        <v>91628</v>
+        <v>92784</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574371</v>
+        <v>574373</v>
       </c>
       <c r="R26" t="n">
-        <v>7088729</v>
+        <v>7088730</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,10 +3215,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342434</v>
+        <v>128342847</v>
       </c>
       <c r="B27" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574373</v>
+        <v>574354</v>
       </c>
       <c r="R27" t="n">
-        <v>7088729</v>
+        <v>7088881</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,10 +3312,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128342847</v>
+        <v>128341564</v>
       </c>
       <c r="B28" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574354</v>
+        <v>574445</v>
       </c>
       <c r="R28" t="n">
-        <v>7088881</v>
+        <v>7088593</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3409,10 +3409,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128341564</v>
+        <v>128342274</v>
       </c>
       <c r="B29" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574445</v>
+        <v>574276</v>
       </c>
       <c r="R29" t="n">
-        <v>7088593</v>
+        <v>7088904</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3477,9 +3477,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3494,44 +3504,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128342274</v>
+        <v>128342391</v>
       </c>
       <c r="B30" t="n">
-        <v>92757</v>
+        <v>91655</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3541,13 +3551,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574276</v>
+        <v>574371</v>
       </c>
       <c r="R30" t="n">
-        <v>7088904</v>
+        <v>7088729</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3574,19 +3584,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3601,12 +3601,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3616,7 +3616,7 @@
         <v>128341678</v>
       </c>
       <c r="B31" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3710,32 +3710,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128342815</v>
+        <v>128341686</v>
       </c>
       <c r="B32" t="n">
-        <v>92757</v>
+        <v>90526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574292</v>
+        <v>574445</v>
       </c>
       <c r="R32" t="n">
-        <v>7088883</v>
+        <v>7088630</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128341686</v>
+        <v>128342782</v>
       </c>
       <c r="B33" t="n">
-        <v>90499</v>
+        <v>92800</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,21 +3818,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574445</v>
+        <v>574280</v>
       </c>
       <c r="R33" t="n">
-        <v>7088630</v>
+        <v>7088852</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -3904,32 +3904,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128342782</v>
+        <v>128342815</v>
       </c>
       <c r="B34" t="n">
-        <v>92773</v>
+        <v>92784</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574280</v>
+        <v>574292</v>
       </c>
       <c r="R34" t="n">
-        <v>7088852</v>
+        <v>7088883</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4001,32 +4001,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128341663</v>
+        <v>128342578</v>
       </c>
       <c r="B35" t="n">
-        <v>92757</v>
+        <v>79735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574444</v>
+        <v>574309</v>
       </c>
       <c r="R35" t="n">
-        <v>7088610</v>
+        <v>7088787</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4101,7 +4101,7 @@
         <v>128342804</v>
       </c>
       <c r="B36" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4195,32 +4195,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128342012</v>
+        <v>128342574</v>
       </c>
       <c r="B37" t="n">
-        <v>92757</v>
+        <v>78782</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4230,10 +4230,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574415</v>
+        <v>574308</v>
       </c>
       <c r="R37" t="n">
-        <v>7088716</v>
+        <v>7088789</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128341929</v>
+        <v>128341248</v>
       </c>
       <c r="B38" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4327,13 +4327,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574406</v>
+        <v>574418</v>
       </c>
       <c r="R38" t="n">
-        <v>7088725</v>
+        <v>7088658</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4360,9 +4360,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4377,44 +4387,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128342574</v>
+        <v>128341663</v>
       </c>
       <c r="B39" t="n">
-        <v>78755</v>
+        <v>92784</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4424,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574308</v>
+        <v>574444</v>
       </c>
       <c r="R39" t="n">
-        <v>7088789</v>
+        <v>7088610</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4486,10 +4496,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128341248</v>
+        <v>128342012</v>
       </c>
       <c r="B40" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4521,13 +4531,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574418</v>
+        <v>574415</v>
       </c>
       <c r="R40" t="n">
-        <v>7088658</v>
+        <v>7088716</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4554,19 +4564,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4581,44 +4581,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128342578</v>
+        <v>128341929</v>
       </c>
       <c r="B41" t="n">
-        <v>79708</v>
+        <v>92784</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574309</v>
+        <v>574406</v>
       </c>
       <c r="R41" t="n">
-        <v>7088787</v>
+        <v>7088725</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4693,7 +4693,7 @@
         <v>128341959</v>
       </c>
       <c r="B42" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4797,48 +4797,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128342904</v>
+        <v>128341748</v>
       </c>
       <c r="B43" t="n">
-        <v>92757</v>
+        <v>57716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574370</v>
+        <v>574361</v>
       </c>
       <c r="R43" t="n">
-        <v>7088775</v>
+        <v>7088768</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4865,9 +4870,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4882,65 +4902,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128341748</v>
+        <v>128342904</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>92784</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574361</v>
+        <v>574370</v>
       </c>
       <c r="R44" t="n">
-        <v>7088768</v>
+        <v>7088775</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4967,24 +4982,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,22 +4999,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128341581</v>
+        <v>128341946</v>
       </c>
       <c r="B45" t="n">
-        <v>78755</v>
+        <v>79735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574445</v>
+        <v>574406</v>
       </c>
       <c r="R45" t="n">
-        <v>7088593</v>
+        <v>7088724</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5111,7 +5111,7 @@
         <v>128342466</v>
       </c>
       <c r="B46" t="n">
-        <v>92773</v>
+        <v>92800</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5205,10 +5205,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128342664</v>
+        <v>128341581</v>
       </c>
       <c r="B47" t="n">
-        <v>57689</v>
+        <v>78782</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,42 +5216,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>574390</v>
+        <v>574445</v>
       </c>
       <c r="R47" t="n">
-        <v>7088731</v>
+        <v>7088593</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5278,24 +5273,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>18:14</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5310,22 +5290,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128341946</v>
+        <v>128342664</v>
       </c>
       <c r="B48" t="n">
-        <v>79708</v>
+        <v>57716</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5333,37 +5313,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>574406</v>
+        <v>574390</v>
       </c>
       <c r="R48" t="n">
-        <v>7088724</v>
+        <v>7088731</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5390,9 +5375,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5407,44 +5407,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128342898</v>
+        <v>128342880</v>
       </c>
       <c r="B49" t="n">
-        <v>91432</v>
+        <v>79735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574369</v>
+        <v>574359</v>
       </c>
       <c r="R49" t="n">
-        <v>7088771</v>
+        <v>7088849</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5516,10 +5516,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342880</v>
+        <v>128342358</v>
       </c>
       <c r="B50" t="n">
-        <v>79708</v>
+        <v>90526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5527,21 +5527,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574359</v>
+        <v>574372</v>
       </c>
       <c r="R50" t="n">
-        <v>7088849</v>
+        <v>7088765</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5616,7 +5616,7 @@
         <v>128342246</v>
       </c>
       <c r="B51" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5710,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128342358</v>
+        <v>128342898</v>
       </c>
       <c r="B52" t="n">
-        <v>90499</v>
+        <v>91459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574372</v>
+        <v>574369</v>
       </c>
       <c r="R52" t="n">
-        <v>7088765</v>
+        <v>7088771</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128342751</v>
+        <v>128342351</v>
       </c>
       <c r="B53" t="n">
-        <v>78755</v>
+        <v>92788</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>4365</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574291</v>
+        <v>574372</v>
       </c>
       <c r="R53" t="n">
-        <v>7088844</v>
+        <v>7088765</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5907,7 +5907,7 @@
         <v>128342561</v>
       </c>
       <c r="B54" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>128341543</v>
       </c>
       <c r="B55" t="n">
-        <v>80230</v>
+        <v>80257</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6098,32 +6098,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128342351</v>
+        <v>128342438</v>
       </c>
       <c r="B56" t="n">
-        <v>92761</v>
+        <v>78873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>574372</v>
+        <v>574373</v>
       </c>
       <c r="R56" t="n">
-        <v>7088765</v>
+        <v>7088730</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128342438</v>
+        <v>128341658</v>
       </c>
       <c r="B57" t="n">
-        <v>78846</v>
+        <v>78782</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6206,21 +6206,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>574373</v>
+        <v>574445</v>
       </c>
       <c r="R57" t="n">
-        <v>7088729</v>
+        <v>7088595</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6292,10 +6292,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128341658</v>
+        <v>128342751</v>
       </c>
       <c r="B58" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6327,10 +6327,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R58" t="n">
-        <v>7088595</v>
+        <v>7088844</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6389,32 +6389,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128341588</v>
+        <v>128342771</v>
       </c>
       <c r="B59" t="n">
-        <v>92757</v>
+        <v>90526</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574445</v>
+        <v>574281</v>
       </c>
       <c r="R59" t="n">
-        <v>7088594</v>
+        <v>7088848</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128342667</v>
+        <v>128342812</v>
       </c>
       <c r="B60" t="n">
-        <v>92757</v>
+        <v>80250</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574390</v>
+        <v>574292</v>
       </c>
       <c r="R60" t="n">
-        <v>7088726</v>
+        <v>7088883</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6554,19 +6554,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6581,44 +6571,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128342771</v>
+        <v>128341588</v>
       </c>
       <c r="B61" t="n">
-        <v>90499</v>
+        <v>92784</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6628,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574281</v>
+        <v>574445</v>
       </c>
       <c r="R61" t="n">
-        <v>7088848</v>
+        <v>7088594</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6690,10 +6680,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128342812</v>
+        <v>128342667</v>
       </c>
       <c r="B62" t="n">
-        <v>80223</v>
+        <v>92784</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6701,21 +6691,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6725,13 +6715,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574292</v>
+        <v>574390</v>
       </c>
       <c r="R62" t="n">
-        <v>7088883</v>
+        <v>7088726</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6758,9 +6748,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6775,12 +6775,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6790,7 +6790,7 @@
         <v>128341312</v>
       </c>
       <c r="B63" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>128341482</v>
       </c>
       <c r="B64" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342176</v>
+        <v>128342400</v>
       </c>
       <c r="B65" t="n">
-        <v>57689</v>
+        <v>92977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,42 +7016,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574286</v>
+        <v>574381</v>
       </c>
       <c r="R65" t="n">
-        <v>7088863</v>
+        <v>7088725</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7078,24 +7073,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7110,22 +7090,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128342400</v>
+        <v>128341715</v>
       </c>
       <c r="B66" t="n">
-        <v>92950</v>
+        <v>92977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7157,10 +7137,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574381</v>
+        <v>574446</v>
       </c>
       <c r="R66" t="n">
-        <v>7088725</v>
+        <v>7088674</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7219,10 +7199,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128341715</v>
+        <v>128342176</v>
       </c>
       <c r="B67" t="n">
-        <v>92950</v>
+        <v>57716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7230,37 +7210,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574446</v>
+        <v>574286</v>
       </c>
       <c r="R67" t="n">
-        <v>7088674</v>
+        <v>7088863</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7287,9 +7272,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7304,12 +7304,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7319,7 +7319,7 @@
         <v>128342808</v>
       </c>
       <c r="B68" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128342397</v>
       </c>
       <c r="B69" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7533,7 +7533,7 @@
         <v>128341878</v>
       </c>
       <c r="B70" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>128341109</v>
       </c>
       <c r="B71" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7754,32 +7754,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128341813</v>
+        <v>128342408</v>
       </c>
       <c r="B72" t="n">
-        <v>92757</v>
+        <v>79735</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7789,10 +7789,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>574445</v>
+        <v>574379</v>
       </c>
       <c r="R72" t="n">
-        <v>7088668</v>
+        <v>7088725</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7854,7 +7854,7 @@
         <v>128342337</v>
       </c>
       <c r="B73" t="n">
-        <v>92751</v>
+        <v>92778</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7958,32 +7958,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128342408</v>
+        <v>128341813</v>
       </c>
       <c r="B74" t="n">
-        <v>79708</v>
+        <v>92784</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574379</v>
+        <v>574445</v>
       </c>
       <c r="R74" t="n">
-        <v>7088725</v>
+        <v>7088668</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8058,7 +8058,7 @@
         <v>128341787</v>
       </c>
       <c r="B75" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>128342186</v>
       </c>
       <c r="B76" t="n">
-        <v>92172</v>
+        <v>92199</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>128355111</v>
       </c>
       <c r="B77" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 36484-2025 artfynd.xlsx
+++ b/artfynd/A 36484-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128342785</v>
+        <v>128342277</v>
       </c>
       <c r="B2" t="n">
-        <v>79735</v>
+        <v>78782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574275</v>
+        <v>574382</v>
       </c>
       <c r="R2" t="n">
-        <v>7088862</v>
+        <v>7088759</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128341917</v>
+        <v>128342930</v>
       </c>
       <c r="B3" t="n">
-        <v>78873</v>
+        <v>92800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574334</v>
+        <v>574400</v>
       </c>
       <c r="R3" t="n">
-        <v>7088809</v>
+        <v>7088743</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,19 +840,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128342191</v>
+        <v>128342785</v>
       </c>
       <c r="B4" t="n">
-        <v>92778</v>
+        <v>79735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574279</v>
+        <v>574275</v>
       </c>
       <c r="R4" t="n">
-        <v>7088861</v>
+        <v>7088862</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +937,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128342930</v>
+        <v>128341917</v>
       </c>
       <c r="B5" t="n">
-        <v>92800</v>
+        <v>78873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574400</v>
+        <v>574334</v>
       </c>
       <c r="R5" t="n">
-        <v>7088743</v>
+        <v>7088809</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,9 +1034,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1061,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128342842</v>
+        <v>128342191</v>
       </c>
       <c r="B6" t="n">
-        <v>56907</v>
+        <v>92778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574354</v>
+        <v>574279</v>
       </c>
       <c r="R6" t="n">
-        <v>7088880</v>
+        <v>7088861</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1156,9 +1141,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,57 +1168,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128342277</v>
+        <v>128342842</v>
       </c>
       <c r="B7" t="n">
-        <v>78782</v>
+        <v>56907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574382</v>
+        <v>574354</v>
       </c>
       <c r="R7" t="n">
-        <v>7088759</v>
+        <v>7088880</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,10 +1282,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128342525</v>
+        <v>128341860</v>
       </c>
       <c r="B8" t="n">
-        <v>79735</v>
+        <v>78873</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,21 +1293,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,13 +1317,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574323</v>
+        <v>574328</v>
       </c>
       <c r="R8" t="n">
-        <v>7088778</v>
+        <v>7088763</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,9 +1350,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1367,22 +1377,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128341860</v>
+        <v>128342525</v>
       </c>
       <c r="B9" t="n">
-        <v>78873</v>
+        <v>79735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1390,21 +1400,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1414,13 +1424,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574328</v>
+        <v>574323</v>
       </c>
       <c r="R9" t="n">
-        <v>7088763</v>
+        <v>7088778</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1447,19 +1457,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1474,12 +1474,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128342361</v>
+        <v>128342299</v>
       </c>
       <c r="B14" t="n">
-        <v>92778</v>
+        <v>92800</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574230</v>
+        <v>574373</v>
       </c>
       <c r="R14" t="n">
-        <v>7088918</v>
+        <v>7088753</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1992,19 +1992,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2019,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128342299</v>
+        <v>128342361</v>
       </c>
       <c r="B15" t="n">
-        <v>92800</v>
+        <v>92778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,13 +2056,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574373</v>
+        <v>574230</v>
       </c>
       <c r="R15" t="n">
-        <v>7088753</v>
+        <v>7088918</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2099,9 +2089,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,12 +2116,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128341807</v>
+        <v>128341646</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2333,34 +2333,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574435</v>
+        <v>574445</v>
       </c>
       <c r="R18" t="n">
-        <v>7088661</v>
+        <v>7088594</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2393,6 +2398,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2419,50 +2429,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128341646</v>
+        <v>128342757</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>92784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574445</v>
+        <v>574291</v>
       </c>
       <c r="R19" t="n">
-        <v>7088594</v>
+        <v>7088843</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2495,11 +2500,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,7 +2526,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128342757</v>
+        <v>128341886</v>
       </c>
       <c r="B20" t="n">
         <v>92784</v>
@@ -2561,13 +2561,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574291</v>
+        <v>574321</v>
       </c>
       <c r="R20" t="n">
-        <v>7088843</v>
+        <v>7088769</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2594,9 +2594,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2611,44 +2621,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128341886</v>
+        <v>128341807</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2658,13 +2668,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574321</v>
+        <v>574435</v>
       </c>
       <c r="R21" t="n">
-        <v>7088769</v>
+        <v>7088661</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2691,19 +2701,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,12 +2718,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2924,32 +2924,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128342655</v>
+        <v>128342754</v>
       </c>
       <c r="B24" t="n">
-        <v>90294</v>
+        <v>79735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574282</v>
+        <v>574291</v>
       </c>
       <c r="R24" t="n">
-        <v>7088807</v>
+        <v>7088845</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128342754</v>
+        <v>128342655</v>
       </c>
       <c r="B25" t="n">
-        <v>79735</v>
+        <v>90294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574291</v>
+        <v>574282</v>
       </c>
       <c r="R25" t="n">
-        <v>7088845</v>
+        <v>7088807</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3118,32 +3118,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128342434</v>
+        <v>128341678</v>
       </c>
       <c r="B26" t="n">
-        <v>92784</v>
+        <v>78782</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574373</v>
+        <v>574449</v>
       </c>
       <c r="R26" t="n">
-        <v>7088730</v>
+        <v>7088616</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3215,32 +3215,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128342847</v>
+        <v>128342391</v>
       </c>
       <c r="B27" t="n">
-        <v>92784</v>
+        <v>91655</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574354</v>
+        <v>574371</v>
       </c>
       <c r="R27" t="n">
-        <v>7088881</v>
+        <v>7088729</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128341564</v>
+        <v>128342847</v>
       </c>
       <c r="B28" t="n">
         <v>92784</v>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574445</v>
+        <v>574354</v>
       </c>
       <c r="R28" t="n">
-        <v>7088593</v>
+        <v>7088881</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128342274</v>
+        <v>128341564</v>
       </c>
       <c r="B29" t="n">
         <v>92784</v>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574276</v>
+        <v>574445</v>
       </c>
       <c r="R29" t="n">
-        <v>7088904</v>
+        <v>7088593</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3477,19 +3477,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:53</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3504,44 +3494,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128342391</v>
+        <v>128342274</v>
       </c>
       <c r="B30" t="n">
-        <v>91655</v>
+        <v>92784</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3551,13 +3541,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574371</v>
+        <v>574276</v>
       </c>
       <c r="R30" t="n">
-        <v>7088729</v>
+        <v>7088904</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3584,9 +3574,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3601,44 +3601,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128341678</v>
+        <v>128342434</v>
       </c>
       <c r="B31" t="n">
-        <v>78782</v>
+        <v>92784</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574449</v>
+        <v>574373</v>
       </c>
       <c r="R31" t="n">
-        <v>7088616</v>
+        <v>7088729</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4001,32 +4001,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128342578</v>
+        <v>128341248</v>
       </c>
       <c r="B35" t="n">
-        <v>79735</v>
+        <v>92784</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4036,13 +4036,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574309</v>
+        <v>574418</v>
       </c>
       <c r="R35" t="n">
-        <v>7088787</v>
+        <v>7088658</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4069,9 +4069,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4086,12 +4096,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4195,32 +4205,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128342574</v>
+        <v>128341663</v>
       </c>
       <c r="B37" t="n">
-        <v>78782</v>
+        <v>92784</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4230,10 +4240,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574308</v>
+        <v>574444</v>
       </c>
       <c r="R37" t="n">
-        <v>7088789</v>
+        <v>7088610</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4292,7 +4302,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128341248</v>
+        <v>128342012</v>
       </c>
       <c r="B38" t="n">
         <v>92784</v>
@@ -4327,13 +4337,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574418</v>
+        <v>574415</v>
       </c>
       <c r="R38" t="n">
-        <v>7088658</v>
+        <v>7088716</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4360,19 +4370,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:02</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4387,19 +4387,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128341663</v>
+        <v>128341929</v>
       </c>
       <c r="B39" t="n">
         <v>92784</v>
@@ -4434,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574444</v>
+        <v>574406</v>
       </c>
       <c r="R39" t="n">
-        <v>7088610</v>
+        <v>7088725</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4496,32 +4496,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128342012</v>
+        <v>128342574</v>
       </c>
       <c r="B40" t="n">
-        <v>92784</v>
+        <v>78782</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574415</v>
+        <v>574308</v>
       </c>
       <c r="R40" t="n">
-        <v>7088716</v>
+        <v>7088789</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4593,32 +4593,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128341929</v>
+        <v>128342578</v>
       </c>
       <c r="B41" t="n">
-        <v>92784</v>
+        <v>79735</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4628,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574406</v>
+        <v>574309</v>
       </c>
       <c r="R41" t="n">
-        <v>7088725</v>
+        <v>7088787</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4690,45 +4690,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128341959</v>
+        <v>128341748</v>
       </c>
       <c r="B42" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574292</v>
+        <v>574361</v>
       </c>
       <c r="R42" t="n">
-        <v>7088836</v>
+        <v>7088768</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4760,7 +4765,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4770,7 +4775,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4785,65 +4795,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128341748</v>
+        <v>128342904</v>
       </c>
       <c r="B43" t="n">
-        <v>57716</v>
+        <v>92784</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574361</v>
+        <v>574370</v>
       </c>
       <c r="R43" t="n">
-        <v>7088768</v>
+        <v>7088775</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4870,24 +4875,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4902,19 +4892,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128342904</v>
+        <v>128341959</v>
       </c>
       <c r="B44" t="n">
         <v>92784</v>
@@ -4949,13 +4939,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574370</v>
+        <v>574292</v>
       </c>
       <c r="R44" t="n">
-        <v>7088775</v>
+        <v>7088836</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4982,9 +4972,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4999,22 +4999,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128341946</v>
+        <v>128342466</v>
       </c>
       <c r="B45" t="n">
-        <v>79735</v>
+        <v>92800</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>574406</v>
+        <v>574352</v>
       </c>
       <c r="R45" t="n">
-        <v>7088724</v>
+        <v>7088735</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128342466</v>
+        <v>128341946</v>
       </c>
       <c r="B46" t="n">
-        <v>92800</v>
+        <v>79735</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,21 +5119,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>574352</v>
+        <v>574406</v>
       </c>
       <c r="R46" t="n">
-        <v>7088735</v>
+        <v>7088724</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128342880</v>
+        <v>128342358</v>
       </c>
       <c r="B49" t="n">
-        <v>79735</v>
+        <v>90526</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5430,21 +5430,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>574359</v>
+        <v>574372</v>
       </c>
       <c r="R49" t="n">
-        <v>7088849</v>
+        <v>7088765</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5516,32 +5516,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128342358</v>
+        <v>128342246</v>
       </c>
       <c r="B50" t="n">
-        <v>90526</v>
+        <v>92784</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>574372</v>
+        <v>574397</v>
       </c>
       <c r="R50" t="n">
-        <v>7088765</v>
+        <v>7088752</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128342246</v>
+        <v>128342898</v>
       </c>
       <c r="B51" t="n">
-        <v>92784</v>
+        <v>91459</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5624,21 +5624,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>574397</v>
+        <v>574369</v>
       </c>
       <c r="R51" t="n">
-        <v>7088752</v>
+        <v>7088771</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5710,32 +5710,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128342898</v>
+        <v>128342880</v>
       </c>
       <c r="B52" t="n">
-        <v>91459</v>
+        <v>79735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>574369</v>
+        <v>574359</v>
       </c>
       <c r="R52" t="n">
-        <v>7088771</v>
+        <v>7088849</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5807,32 +5807,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128342351</v>
+        <v>128342561</v>
       </c>
       <c r="B53" t="n">
-        <v>92788</v>
+        <v>79735</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>574372</v>
+        <v>574312</v>
       </c>
       <c r="R53" t="n">
-        <v>7088765</v>
+        <v>7088790</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128342561</v>
+        <v>128341543</v>
       </c>
       <c r="B54" t="n">
-        <v>79735</v>
+        <v>80257</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>574312</v>
+        <v>574445</v>
       </c>
       <c r="R54" t="n">
-        <v>7088790</v>
+        <v>7088593</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6001,32 +6001,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128341543</v>
+        <v>128342351</v>
       </c>
       <c r="B55" t="n">
-        <v>80257</v>
+        <v>92788</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6464</v>
+        <v>4365</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>574445</v>
+        <v>574372</v>
       </c>
       <c r="R55" t="n">
-        <v>7088593</v>
+        <v>7088765</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6136,7 +6136,7 @@
         <v>574373</v>
       </c>
       <c r="R56" t="n">
-        <v>7088730</v>
+        <v>7088729</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6389,32 +6389,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128342771</v>
+        <v>128342667</v>
       </c>
       <c r="B59" t="n">
-        <v>90526</v>
+        <v>92784</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6424,13 +6424,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>574281</v>
+        <v>574390</v>
       </c>
       <c r="R59" t="n">
-        <v>7088848</v>
+        <v>7088726</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6457,9 +6457,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6474,22 +6484,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128342812</v>
+        <v>128341588</v>
       </c>
       <c r="B60" t="n">
-        <v>80250</v>
+        <v>92784</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6497,21 +6507,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6521,10 +6531,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>574292</v>
+        <v>574445</v>
       </c>
       <c r="R60" t="n">
-        <v>7088883</v>
+        <v>7088594</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -6583,32 +6593,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128341588</v>
+        <v>128342771</v>
       </c>
       <c r="B61" t="n">
-        <v>92784</v>
+        <v>90526</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6618,10 +6628,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>574445</v>
+        <v>574281</v>
       </c>
       <c r="R61" t="n">
-        <v>7088594</v>
+        <v>7088848</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6680,10 +6690,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128342667</v>
+        <v>128342812</v>
       </c>
       <c r="B62" t="n">
-        <v>92784</v>
+        <v>80250</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6691,21 +6701,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6715,13 +6725,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>574390</v>
+        <v>574292</v>
       </c>
       <c r="R62" t="n">
-        <v>7088726</v>
+        <v>7088883</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6748,19 +6758,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>18:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6775,12 +6775,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128342400</v>
+        <v>128342176</v>
       </c>
       <c r="B65" t="n">
-        <v>92977</v>
+        <v>57716</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7016,37 +7016,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>574381</v>
+        <v>574286</v>
       </c>
       <c r="R65" t="n">
-        <v>7088725</v>
+        <v>7088863</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7073,9 +7078,24 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7090,19 +7110,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128341715</v>
+        <v>128342400</v>
       </c>
       <c r="B66" t="n">
         <v>92977</v>
@@ -7137,10 +7157,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>574446</v>
+        <v>574381</v>
       </c>
       <c r="R66" t="n">
-        <v>7088674</v>
+        <v>7088725</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7199,10 +7219,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128342176</v>
+        <v>128341715</v>
       </c>
       <c r="B67" t="n">
-        <v>57716</v>
+        <v>92977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7210,42 +7230,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Långvattentjärnen, Långvattentjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>574286</v>
+        <v>574446</v>
       </c>
       <c r="R67" t="n">
-        <v>7088863</v>
+        <v>7088674</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7272,24 +7287,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7304,12 +7304,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7423,32 +7423,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128342397</v>
+        <v>128341878</v>
       </c>
       <c r="B69" t="n">
-        <v>92784</v>
+        <v>79735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>574294</v>
+        <v>574329</v>
       </c>
       <c r="R69" t="n">
-        <v>7088921</v>
+        <v>7088770</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7518,44 +7518,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128341878</v>
+        <v>128342397</v>
       </c>
       <c r="B70" t="n">
-        <v>79735</v>
+        <v>92784</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7565,10 +7565,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>574329</v>
+        <v>574294</v>
       </c>
       <c r="R70" t="n">
-        <v>7088770</v>
+        <v>7088921</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7625,12 +7625,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7851,32 +7851,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128342337</v>
+        <v>128341813</v>
       </c>
       <c r="B73" t="n">
-        <v>92778</v>
+        <v>92784</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7886,13 +7886,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>574241</v>
+        <v>574445</v>
       </c>
       <c r="R73" t="n">
-        <v>7088939</v>
+        <v>7088668</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7919,19 +7919,9 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7946,44 +7936,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128341813</v>
+        <v>128342337</v>
       </c>
       <c r="B74" t="n">
-        <v>92784</v>
+        <v>92778</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7993,13 +7983,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>574445</v>
+        <v>574241</v>
       </c>
       <c r="R74" t="n">
-        <v>7088668</v>
+        <v>7088939</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8026,9 +8016,19 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8043,12 +8043,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
